--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Módulo Q — display de QUANTIDADE (3 dígitos) + botão com LED, um por endereço de alto giro (andares 0 a 3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Módulo E+Q — display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos 2 blocos de alto giro dos andares 4-5 (esquerdo/direito) e em cada zona de baixo giro.</t>
+    <t xml:space="preserve">Módulo E+Q — display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (1 por andar em cada lado: 4 por estação) e em cada zona de baixo giro.</t>
   </si>
   <si>
     <t xml:space="preserve">Nó de coluna — microcontrolador por coluna (prédio) do alto giro que liga os Módulos Q daquela coluna ao barramento RS-485.</t>
@@ -561,7 +561,7 @@
     <t xml:space="preserve">Coluna D (Piloto) = quantidade de estações nas linhas de total. Fonte: wms_endereco (cd_esteira 1 e 2), exportado em 23/10/2026; rua 90 (Marketing/Almoxarifado) desconsiderada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Regras: Alto giro = prédios 001-010; andares 4-5 viram 2 blocos E+Q (prédios 1-5 / 6-10). Baixo giro = demais prédios (fundo, 015 e esquinas), 1 zona E+Q a cada 4 prédios.</t>
+    <t xml:space="preserve">Regras: Alto giro = prédios 001-010; andares 4-5 com 4 displays E+Q por estação (A4 e A5 nos lados 001-005 e 006-010). Baixo giro = demais prédios (corredor, 015 e esquinas), 1 zona E+Q a cada 4 prédios.</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -2404,15 +2404,15 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">'A-Interno'!F13</f>
-        <v>10443.4012151639</v>
+        <v>10993.9714446721</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">'A-Interno'!G13</f>
-        <v>187235.880303279</v>
+        <v>199238.884893443</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/Estações!$O$43</f>
-        <v>4680.89700758197</v>
+        <v>4980.97212233607</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2424,15 +2424,15 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">'A-Interno'!F30</f>
-        <v>10354.4612151639</v>
+        <v>10873.0314446721</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">'A-Interno'!G30</f>
-        <v>185656.760303279</v>
+        <v>196955.764893443</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/Estações!$O$43</f>
-        <v>4641.41900758197</v>
+        <v>4923.89412233607</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,15 +2444,15 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">'A-Interno'!F24</f>
-        <v>13875.3279636302</v>
+        <v>14565.6204017273</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">'A-Interno'!G24</f>
-        <v>254686.776499598</v>
+        <v>269763.669678719</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/Estações!$O$43</f>
-        <v>6367.16941248994</v>
+        <v>6744.09174196797</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2464,15 +2464,15 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">'A-Terceiros'!F10</f>
-        <v>31822.4277219551</v>
+        <v>32808.1033114633</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">'A-Terceiros'!G10</f>
-        <v>326284.963278119</v>
+        <v>347860.285788283</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/Estações!$O$43</f>
-        <v>8157.12408195298</v>
+        <v>8696.50714470708</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2484,15 +2484,15 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">'A-Terceiros'!F20</f>
-        <v>40650.4697219551</v>
+        <v>43195.6421514633</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">'A-Terceiros'!G20</f>
-        <v>796445.526248119</v>
+        <v>852329.779238283</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">D8/Estações!$O$43</f>
-        <v>19911.138156203</v>
+        <v>21308.2444809571</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2504,15 +2504,15 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">'B-RFID'!F10</f>
-        <v>15205.4074319329</v>
+        <v>15895.69987003</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">'B-RFID'!G10</f>
-        <v>279129.135927001</v>
+        <v>294206.029106122</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/Estações!$O$43</f>
-        <v>6978.22839817501</v>
+        <v>7355.15072765304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2524,15 +2524,15 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">'B-RFID'!F15</f>
-        <v>15048.1306804494</v>
+        <v>15738.4231185465</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'B-RFID'!G15</f>
-        <v>278142.830835982</v>
+        <v>293219.724015103</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">D10/Estações!$O$43</f>
-        <v>6953.57077089954</v>
+        <v>7330.49310037757</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3039,7 +3039,7 @@
         <v>20</v>
       </c>
       <c r="H2" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2" s="21" t="n">
         <v>82</v>
@@ -3055,11 +3055,11 @@
       </c>
       <c r="M2" s="22" t="n">
         <f aca="false">H2+J2</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N2" s="22" t="n">
         <f aca="false">K2+M2+2</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O2" s="21" t="n">
         <v>1</v>
@@ -3088,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3" s="21" t="n">
         <v>156</v>
@@ -3104,11 +3104,11 @@
       </c>
       <c r="M3" s="22" t="n">
         <f aca="false">H3+J3</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N3" s="22" t="n">
         <f aca="false">K3+M3+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O3" s="21" t="n">
         <v>1</v>
@@ -3137,7 +3137,7 @@
         <v>20</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="21" t="n">
         <v>160</v>
@@ -3153,11 +3153,11 @@
       </c>
       <c r="M4" s="22" t="n">
         <f aca="false">H4+J4</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N4" s="22" t="n">
         <f aca="false">K4+M4+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O4" s="21" t="n">
         <v>1</v>
@@ -3186,7 +3186,7 @@
         <v>20</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="21" t="n">
         <v>160</v>
@@ -3202,11 +3202,11 @@
       </c>
       <c r="M5" s="22" t="n">
         <f aca="false">H5+J5</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N5" s="22" t="n">
         <f aca="false">K5+M5+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O5" s="21" t="n">
         <v>1</v>
@@ -3235,7 +3235,7 @@
         <v>20</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" s="21" t="n">
         <v>160</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="M6" s="22" t="n">
         <f aca="false">H6+J6</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N6" s="22" t="n">
         <f aca="false">K6+M6+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O6" s="21" t="n">
         <v>1</v>
@@ -3284,7 +3284,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="21" t="n">
         <v>160</v>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="M7" s="22" t="n">
         <f aca="false">H7+J7</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N7" s="22" t="n">
         <f aca="false">K7+M7+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O7" s="21" t="n">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" s="21" t="n">
         <v>192</v>
@@ -3349,11 +3349,11 @@
       </c>
       <c r="M8" s="22" t="n">
         <f aca="false">H8+J8</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N8" s="22" t="n">
         <f aca="false">K8+M8+2</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O8" s="21" t="n">
         <v>1</v>
@@ -3382,7 +3382,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" s="21" t="n">
         <v>188</v>
@@ -3398,11 +3398,11 @@
       </c>
       <c r="M9" s="22" t="n">
         <f aca="false">H9+J9</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N9" s="22" t="n">
         <f aca="false">K9+M9+2</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O9" s="21" t="n">
         <v>1</v>
@@ -3431,7 +3431,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" s="21" t="n">
         <v>160</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="M10" s="22" t="n">
         <f aca="false">H10+J10</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N10" s="22" t="n">
         <f aca="false">K10+M10+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O10" s="21" t="n">
         <v>1</v>
@@ -3480,7 +3480,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" s="21" t="n">
         <v>160</v>
@@ -3496,11 +3496,11 @@
       </c>
       <c r="M11" s="22" t="n">
         <f aca="false">H11+J11</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N11" s="22" t="n">
         <f aca="false">K11+M11+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O11" s="21" t="n">
         <v>1</v>
@@ -3529,7 +3529,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" s="21" t="n">
         <v>160</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="M12" s="22" t="n">
         <f aca="false">H12+J12</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N12" s="22" t="n">
         <f aca="false">K12+M12+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O12" s="21" t="n">
         <v>1</v>
@@ -3578,7 +3578,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>160</v>
@@ -3594,11 +3594,11 @@
       </c>
       <c r="M13" s="22" t="n">
         <f aca="false">H13+J13</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N13" s="22" t="n">
         <f aca="false">K13+M13+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O13" s="21" t="n">
         <v>1</v>
@@ -3627,7 +3627,7 @@
         <v>10</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>192</v>
@@ -3643,11 +3643,11 @@
       </c>
       <c r="M14" s="22" t="n">
         <f aca="false">H14+J14</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N14" s="22" t="n">
         <f aca="false">K14+M14+2</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O14" s="21" t="n">
         <v>1</v>
@@ -3676,7 +3676,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" s="21" t="n">
         <v>188</v>
@@ -3692,11 +3692,11 @@
       </c>
       <c r="M15" s="22" t="n">
         <f aca="false">H15+J15</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N15" s="22" t="n">
         <f aca="false">K15+M15+2</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O15" s="21" t="n">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         <v>16</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="21" t="n">
         <v>160</v>
@@ -3741,11 +3741,11 @@
       </c>
       <c r="M16" s="22" t="n">
         <f aca="false">H16+J16</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N16" s="22" t="n">
         <f aca="false">K16+M16+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O16" s="21" t="n">
         <v>1</v>
@@ -3774,7 +3774,7 @@
         <v>20</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>160</v>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="M17" s="22" t="n">
         <f aca="false">H17+J17</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17" s="22" t="n">
         <f aca="false">K17+M17+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O17" s="21" t="n">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I18" s="21" t="n">
         <v>160</v>
@@ -3839,11 +3839,11 @@
       </c>
       <c r="M18" s="22" t="n">
         <f aca="false">H18+J18</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N18" s="22" t="n">
         <f aca="false">K18+M18+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O18" s="21" t="n">
         <v>1</v>
@@ -3872,7 +3872,7 @@
         <v>20</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" s="21" t="n">
         <v>160</v>
@@ -3888,11 +3888,11 @@
       </c>
       <c r="M19" s="22" t="n">
         <f aca="false">H19+J19</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N19" s="22" t="n">
         <f aca="false">K19+M19+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O19" s="21" t="n">
         <v>1</v>
@@ -3921,7 +3921,7 @@
         <v>10</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I20" s="21" t="n">
         <v>160</v>
@@ -3937,11 +3937,11 @@
       </c>
       <c r="M20" s="22" t="n">
         <f aca="false">H20+J20</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N20" s="22" t="n">
         <f aca="false">K20+M20+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O20" s="21" t="n">
         <v>1</v>
@@ -3970,7 +3970,7 @@
         <v>10</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" s="21" t="n">
         <v>4</v>
@@ -3986,11 +3986,11 @@
       </c>
       <c r="M21" s="22" t="n">
         <f aca="false">H21+J21</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21" s="22" t="n">
         <f aca="false">K21+M21+2</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O21" s="21" t="n">
         <v>1</v>
@@ -4019,7 +4019,7 @@
         <v>13</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" s="21" t="n">
         <v>128</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="M22" s="22" t="n">
         <f aca="false">H22+J22</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N22" s="22" t="n">
         <f aca="false">K22+M22+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O22" s="21" t="n">
         <v>1</v>
@@ -4068,7 +4068,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I23" s="21" t="n">
         <v>131</v>
@@ -4084,11 +4084,11 @@
       </c>
       <c r="M23" s="22" t="n">
         <f aca="false">H23+J23</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N23" s="22" t="n">
         <f aca="false">K23+M23+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O23" s="21" t="n">
         <v>1</v>
@@ -4117,7 +4117,7 @@
         <v>15</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24" s="21" t="n">
         <v>131</v>
@@ -4133,11 +4133,11 @@
       </c>
       <c r="M24" s="22" t="n">
         <f aca="false">H24+J24</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N24" s="22" t="n">
         <f aca="false">K24+M24+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O24" s="21" t="n">
         <v>1</v>
@@ -4166,7 +4166,7 @@
         <v>15</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I25" s="21" t="n">
         <v>131</v>
@@ -4182,11 +4182,11 @@
       </c>
       <c r="M25" s="22" t="n">
         <f aca="false">H25+J25</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N25" s="22" t="n">
         <f aca="false">K25+M25+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O25" s="21" t="n">
         <v>1</v>
@@ -4215,7 +4215,7 @@
         <v>13</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I26" s="21" t="n">
         <v>131</v>
@@ -4231,11 +4231,11 @@
       </c>
       <c r="M26" s="22" t="n">
         <f aca="false">H26+J26</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N26" s="22" t="n">
         <f aca="false">K26+M26+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O26" s="21" t="n">
         <v>1</v>
@@ -4264,7 +4264,7 @@
         <v>15</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I27" s="21" t="n">
         <v>131</v>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="M27" s="22" t="n">
         <f aca="false">H27+J27</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N27" s="22" t="n">
         <f aca="false">K27+M27+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O27" s="21" t="n">
         <v>1</v>
@@ -4313,7 +4313,7 @@
         <v>15</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28" s="21" t="n">
         <v>230</v>
@@ -4329,11 +4329,11 @@
       </c>
       <c r="M28" s="22" t="n">
         <f aca="false">H28+J28</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N28" s="22" t="n">
         <f aca="false">K28+M28+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O28" s="21" t="n">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>15</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29" s="21" t="n">
         <v>227</v>
@@ -4378,11 +4378,11 @@
       </c>
       <c r="M29" s="22" t="n">
         <f aca="false">H29+J29</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N29" s="22" t="n">
         <f aca="false">K29+M29+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O29" s="21" t="n">
         <v>1</v>
@@ -4411,7 +4411,7 @@
         <v>13</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I30" s="21" t="n">
         <v>131</v>
@@ -4427,11 +4427,11 @@
       </c>
       <c r="M30" s="22" t="n">
         <f aca="false">H30+J30</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N30" s="22" t="n">
         <f aca="false">K30+M30+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O30" s="21" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
         <v>15</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31" s="21" t="n">
         <v>131</v>
@@ -4476,11 +4476,11 @@
       </c>
       <c r="M31" s="22" t="n">
         <f aca="false">H31+J31</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N31" s="22" t="n">
         <f aca="false">K31+M31+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O31" s="21" t="n">
         <v>1</v>
@@ -4509,7 +4509,7 @@
         <v>11</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" s="21" t="n">
         <v>131</v>
@@ -4525,11 +4525,11 @@
       </c>
       <c r="M32" s="22" t="n">
         <f aca="false">H32+J32</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N32" s="22" t="n">
         <f aca="false">K32+M32+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O32" s="21" t="n">
         <v>1</v>
@@ -4558,7 +4558,7 @@
         <v>15</v>
       </c>
       <c r="H33" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="21" t="n">
         <v>131</v>
@@ -4574,11 +4574,11 @@
       </c>
       <c r="M33" s="22" t="n">
         <f aca="false">H33+J33</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N33" s="22" t="n">
         <f aca="false">K33+M33+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O33" s="21" t="n">
         <v>1</v>
@@ -4607,7 +4607,7 @@
         <v>9</v>
       </c>
       <c r="H34" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" s="21" t="n">
         <v>230</v>
@@ -4623,11 +4623,11 @@
       </c>
       <c r="M34" s="22" t="n">
         <f aca="false">H34+J34</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N34" s="22" t="n">
         <f aca="false">K34+M34+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O34" s="21" t="n">
         <v>1</v>
@@ -4656,7 +4656,7 @@
         <v>15</v>
       </c>
       <c r="H35" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I35" s="21" t="n">
         <v>227</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="M35" s="22" t="n">
         <f aca="false">H35+J35</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N35" s="22" t="n">
         <f aca="false">K35+M35+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O35" s="21" t="n">
         <v>1</v>
@@ -4705,7 +4705,7 @@
         <v>13</v>
       </c>
       <c r="H36" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="21" t="n">
         <v>131</v>
@@ -4721,11 +4721,11 @@
       </c>
       <c r="M36" s="22" t="n">
         <f aca="false">H36+J36</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N36" s="22" t="n">
         <f aca="false">K36+M36+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O36" s="21" t="n">
         <v>1</v>
@@ -4754,7 +4754,7 @@
         <v>15</v>
       </c>
       <c r="H37" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="21" t="n">
         <v>131</v>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="M37" s="22" t="n">
         <f aca="false">H37+J37</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N37" s="22" t="n">
         <f aca="false">K37+M37+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O37" s="21" t="n">
         <v>1</v>
@@ -4803,7 +4803,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" s="21" t="n">
         <v>131</v>
@@ -4819,11 +4819,11 @@
       </c>
       <c r="M38" s="22" t="n">
         <f aca="false">H38+J38</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N38" s="22" t="n">
         <f aca="false">K38+M38+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O38" s="21" t="n">
         <v>1</v>
@@ -4852,7 +4852,7 @@
         <v>15</v>
       </c>
       <c r="H39" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" s="21" t="n">
         <v>131</v>
@@ -4868,11 +4868,11 @@
       </c>
       <c r="M39" s="22" t="n">
         <f aca="false">H39+J39</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N39" s="22" t="n">
         <f aca="false">K39+M39+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O39" s="21" t="n">
         <v>1</v>
@@ -4901,7 +4901,7 @@
         <v>7</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" s="21" t="n">
         <v>131</v>
@@ -4917,11 +4917,11 @@
       </c>
       <c r="M40" s="22" t="n">
         <f aca="false">H40+J40</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N40" s="22" t="n">
         <f aca="false">K40+M40+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O40" s="21" t="n">
         <v>1</v>
@@ -4950,7 +4950,7 @@
         <v>15</v>
       </c>
       <c r="H41" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41" s="21" t="n">
         <v>131</v>
@@ -4966,11 +4966,11 @@
       </c>
       <c r="M41" s="22" t="n">
         <f aca="false">H41+J41</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N41" s="22" t="n">
         <f aca="false">K41+M41+2</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O41" s="21" t="n">
         <v>1</v>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="H43" s="25" t="n">
         <f aca="false">SUM(H2:H41)</f>
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="I43" s="25" t="n">
         <f aca="false">SUM(I2:I41)</f>
@@ -5018,11 +5018,11 @@
       </c>
       <c r="M43" s="25" t="n">
         <f aca="false">SUM(M2:M41)</f>
-        <v>328</v>
+        <v>408</v>
       </c>
       <c r="N43" s="25" t="n">
         <f aca="false">SUM(N2:N41)</f>
-        <v>808</v>
+        <v>888</v>
       </c>
       <c r="O43" s="25" t="n">
         <f aca="false">SUM(O2:O41)</f>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="H44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",H2:H41)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",I2:I41)</f>
@@ -5071,11 +5071,11 @@
       </c>
       <c r="M44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",M2:M41)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",N2:N41)</f>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",O2:O41)</f>
@@ -7285,11 +7285,11 @@
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$14),0)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$14),0)</f>
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="E5" s="33" t="n">
         <f aca="false">Composição!$F$27</f>
@@ -7297,11 +7297,11 @@
       </c>
       <c r="F5" s="27" t="n">
         <f aca="false">C5*E5</f>
-        <v>2231.1</v>
+        <v>2726.9</v>
       </c>
       <c r="G5" s="27" t="n">
         <f aca="false">D5*E5</f>
-        <v>44745.95</v>
+        <v>55653.55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,11 +7341,11 @@
       </c>
       <c r="C7" s="37" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$15</f>
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Estações!$N$43*Premissas!$B$15</f>
-        <v>2424</v>
+        <v>2664</v>
       </c>
       <c r="E7" s="33" t="n">
         <f aca="false">Preços!$D$13</f>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">C7*E7</f>
-        <v>483.702295081967</v>
+        <v>532.072524590164</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">D7*E7</f>
-        <v>9770.78636065574</v>
+        <v>10738.1909508197</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7369,11 +7369,11 @@
       </c>
       <c r="C8" s="37" t="n">
         <f aca="false">Estações!$N$44*2</f>
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Estações!$N$43*2</f>
-        <v>1616</v>
+        <v>1776</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">Preços!$D$12</f>
@@ -7381,11 +7381,11 @@
       </c>
       <c r="F8" s="27" t="n">
         <f aca="false">C8*E8</f>
-        <v>64</v>
+        <v>70.4</v>
       </c>
       <c r="G8" s="27" t="n">
         <f aca="false">D8*E8</f>
-        <v>1292.8</v>
+        <v>1420.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7510,11 +7510,11 @@
       <c r="E13" s="35"/>
       <c r="F13" s="36" t="n">
         <f aca="false">SUM(F3:F12)</f>
-        <v>10443.4012151639</v>
+        <v>10993.9714446721</v>
       </c>
       <c r="G13" s="36" t="n">
         <f aca="false">SUM(G3:G12)</f>
-        <v>187235.880303279</v>
+        <v>199238.884893443</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7587,11 +7587,11 @@
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C5*Premissas!$B$10</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">D5*Premissas!$B$10</f>
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="E18" s="33" t="n">
         <f aca="false">Premissas!$B$7</f>
@@ -7599,11 +7599,11 @@
       </c>
       <c r="F18" s="27" t="n">
         <f aca="false">C18*E18</f>
-        <v>628.749938650307</v>
+        <v>768.472147239264</v>
       </c>
       <c r="G18" s="27" t="n">
         <f aca="false">D18*E18</f>
-        <v>12609.9293251534</v>
+        <v>15683.8179141104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7697,20 +7697,20 @@
       <c r="B22" s="35"/>
       <c r="C22" s="38" t="n">
         <f aca="false">SUM(C16:C21)</f>
-        <v>98.25</v>
+        <v>102.25</v>
       </c>
       <c r="D22" s="38" t="n">
         <f aca="false">SUM(D16:D21)</f>
-        <v>1931</v>
+        <v>2019</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="36" t="n">
         <f aca="false">SUM(F16:F21)</f>
-        <v>3431.92674846626</v>
+        <v>3571.64895705522</v>
       </c>
       <c r="G22" s="36" t="n">
         <f aca="false">SUM(G16:G21)</f>
-        <v>67450.896196319</v>
+        <v>70524.7847852761</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7723,11 +7723,11 @@
       <c r="E24" s="35"/>
       <c r="F24" s="36" t="n">
         <f aca="false">F13+F22</f>
-        <v>13875.3279636302</v>
+        <v>14565.6204017273</v>
       </c>
       <c r="G24" s="36" t="n">
         <f aca="false">G13+G22</f>
-        <v>254686.776499598</v>
+        <v>269763.669678719</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7744,11 +7744,11 @@
       </c>
       <c r="C27" s="37" t="n">
         <f aca="false">-(C4+C5+C6)</f>
-        <v>-43</v>
+        <v>-47</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">-(D4+D5+D6)</f>
-        <v>-845</v>
+        <v>-933</v>
       </c>
       <c r="E27" s="33" t="n">
         <f aca="false">Preços!$D$9</f>
@@ -7756,11 +7756,11 @@
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">C27*E27</f>
-        <v>-344</v>
+        <v>-376</v>
       </c>
       <c r="G27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>-6760</v>
+        <v>-7464</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,11 +7829,11 @@
       <c r="E30" s="35"/>
       <c r="F30" s="36" t="n">
         <f aca="false">F13+SUM(F27:F29)</f>
-        <v>10354.4612151639</v>
+        <v>10873.0314446721</v>
       </c>
       <c r="G30" s="36" t="n">
         <f aca="false">G13+SUM(G27:G29)</f>
-        <v>185656.760303279</v>
+        <v>196955.764893443</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C4" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$14),0)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$14),0)</f>
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="E4" s="33" t="n">
         <f aca="false">Preços!$D$34+Preços!$D$15+Preços!$D$10</f>
@@ -7973,11 +7973,11 @@
       </c>
       <c r="F4" s="27" t="n">
         <f aca="false">C4*E4</f>
-        <v>4189.07412</v>
+        <v>5119.97948</v>
       </c>
       <c r="G4" s="27" t="n">
         <f aca="false">D4*E4</f>
-        <v>84014.20874</v>
+        <v>104494.12666</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8017,11 +8017,11 @@
       </c>
       <c r="C6" s="37" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*Premissas!$B$15</f>
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">(Estações!$F$43+Estações!$M$43)*Premissas!$B$15</f>
-        <v>4824</v>
+        <v>5064</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">Preços!$D$13+2*Preços!$D$12/Premissas!$B$15</f>
@@ -8029,11 +8029,11 @@
       </c>
       <c r="F6" s="27" t="n">
         <f aca="false">C6*E6</f>
-        <v>1095.40459016393</v>
+        <v>1150.17481967213</v>
       </c>
       <c r="G6" s="27" t="n">
         <f aca="false">D6*E6</f>
-        <v>22017.6322622951</v>
+        <v>23113.036852459</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8123,11 +8123,11 @@
       <c r="E10" s="35"/>
       <c r="F10" s="36" t="n">
         <f aca="false">SUM(F3:F9)</f>
-        <v>31822.4277219551</v>
+        <v>32808.1033114633</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">SUM(G3:G9)</f>
-        <v>326284.963278119</v>
+        <v>347860.285788283</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8172,11 +8172,11 @@
       </c>
       <c r="C14" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$14),0)</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D14" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$14),0)</f>
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="E14" s="33" t="n">
         <f aca="false">Preços!$D$31</f>
@@ -8184,11 +8184,11 @@
       </c>
       <c r="F14" s="27" t="n">
         <f aca="false">C14*E14</f>
-        <v>11206.8099</v>
+        <v>13697.2121</v>
       </c>
       <c r="G14" s="27" t="n">
         <f aca="false">D14*E14</f>
-        <v>224758.79855</v>
+        <v>279547.64695</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8256,11 +8256,11 @@
       </c>
       <c r="C17" s="37" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*Premissas!$B$15</f>
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">(Estações!$F$43+Estações!$M$43)*Premissas!$B$15</f>
-        <v>4824</v>
+        <v>5064</v>
       </c>
       <c r="E17" s="33" t="n">
         <f aca="false">Preços!$D$13+2*Preços!$D$12/Premissas!$B$15</f>
@@ -8268,11 +8268,11 @@
       </c>
       <c r="F17" s="27" t="n">
         <f aca="false">C17*E17</f>
-        <v>1095.40459016393</v>
+        <v>1150.17481967213</v>
       </c>
       <c r="G17" s="27" t="n">
         <f aca="false">D17*E17</f>
-        <v>22017.6322622951</v>
+        <v>23113.036852459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8336,11 +8336,11 @@
       <c r="E20" s="35"/>
       <c r="F20" s="36" t="n">
         <f aca="false">SUM(F13:F19)</f>
-        <v>40650.4697219551</v>
+        <v>43195.6421514633</v>
       </c>
       <c r="G20" s="36" t="n">
         <f aca="false">SUM(G13:G19)</f>
-        <v>796445.526248119</v>
+        <v>852329.779238283</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8416,11 +8416,11 @@
       <c r="E3" s="13"/>
       <c r="F3" s="33" t="n">
         <f aca="false">'A-Interno'!F24</f>
-        <v>13875.3279636302</v>
+        <v>14565.6204017273</v>
       </c>
       <c r="G3" s="33" t="n">
         <f aca="false">'A-Interno'!G24</f>
-        <v>254686.776499598</v>
+        <v>269763.669678719</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8550,11 +8550,11 @@
       <c r="E10" s="35"/>
       <c r="F10" s="36" t="n">
         <f aca="false">F3+F4+F5+F8+F9</f>
-        <v>15205.4074319329</v>
+        <v>15895.69987003</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">G3+G4+G5+G8+G9</f>
-        <v>279129.135927001</v>
+        <v>294206.029106122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8628,11 +8628,11 @@
       <c r="E15" s="35"/>
       <c r="F15" s="36" t="n">
         <f aca="false">F3+F4+F5+F13+F14</f>
-        <v>15048.1306804494</v>
+        <v>15738.4231185465</v>
       </c>
       <c r="G15" s="36" t="n">
         <f aca="false">G3+G4+G5+G13+G14</f>
-        <v>278142.830835982</v>
+        <v>293219.724015103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Módulo Q — display de QUANTIDADE (3 dígitos) + botão com LED, um por endereço de alto giro (andares 0 a 3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Módulo E+Q — display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (1 por andar em cada lado: 4 por estação) e em cada zona de baixo giro.</t>
+    <t xml:space="preserve">Módulo E+Q — display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (1 por andar em cada lado: 4 por estação) e em cada zona de baixo giro (4 zonas por lado do corredor, na altura dos olhos).</t>
   </si>
   <si>
     <t xml:space="preserve">Nó de coluna — microcontrolador por coluna (prédio) do alto giro que liga os Módulos Q daquela coluna ao barramento RS-485.</t>
@@ -561,7 +561,7 @@
     <t xml:space="preserve">Coluna D (Piloto) = quantidade de estações nas linhas de total. Fonte: wms_endereco (cd_esteira 1 e 2), exportado em 23/10/2026; rua 90 (Marketing/Almoxarifado) desconsiderada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Regras: Alto giro = prédios 001-010; andares 4-5 com 4 displays E+Q por estação (A4 e A5 nos lados 001-005 e 006-010). Baixo giro = demais prédios (corredor, 015 e esquinas), 1 zona E+Q a cada 4 prédios.</t>
+    <t xml:space="preserve">Regras: Alto giro = prédios 001-010; andares 4-5 com 4 displays E+Q por estação (A4 e A5 nos lados 001-005 e 006-010). Baixo giro = demais prédios (corredor, 015 e esquinas): 4 zonas E+Q por lado do corredor; esquinas com zonas de 4 prédios.</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -2404,15 +2404,15 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">'A-Interno'!F13</f>
-        <v>10993.9714446721</v>
+        <v>11668.4916741803</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">'A-Interno'!G13</f>
-        <v>199238.884893443</v>
+        <v>210828.961811475</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/Estações!$O$43</f>
-        <v>4980.97212233607</v>
+        <v>5270.72404528689</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2424,15 +2424,15 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">'A-Interno'!F30</f>
-        <v>10873.0314446721</v>
+        <v>11507.5516741803</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">'A-Interno'!G30</f>
-        <v>196955.764893443</v>
+        <v>207865.841811475</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/Estações!$O$43</f>
-        <v>4923.89412233607</v>
+        <v>5196.64604528689</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,15 +2444,15 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">'A-Interno'!F24</f>
-        <v>14565.6204017273</v>
+        <v>15414.7933919717</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">'A-Interno'!G24</f>
-        <v>269763.669678719</v>
+        <v>284322.843529267</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/Estações!$O$43</f>
-        <v>6744.09174196797</v>
+        <v>7108.07108823167</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2464,15 +2464,15 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">'A-Terceiros'!F10</f>
-        <v>32808.1033114633</v>
+        <v>34026.5052409715</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">'A-Terceiros'!G10</f>
-        <v>347860.285788283</v>
+        <v>368696.351606316</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/Estações!$O$43</f>
-        <v>8696.50714470708</v>
+        <v>9217.4087901579</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2484,15 +2484,15 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">'A-Terceiros'!F20</f>
-        <v>43195.6421514633</v>
+        <v>46363.4151309715</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">'A-Terceiros'!G20</f>
-        <v>852329.779238283</v>
+        <v>906305.152906316</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">D8/Estações!$O$43</f>
-        <v>21308.2444809571</v>
+        <v>22657.6288226579</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2504,15 +2504,15 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">'B-RFID'!F10</f>
-        <v>15895.69987003</v>
+        <v>16744.8728602744</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">'B-RFID'!G10</f>
-        <v>294206.029106122</v>
+        <v>308765.20295667</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/Estações!$O$43</f>
-        <v>7355.15072765304</v>
+        <v>7719.13007391674</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2524,15 +2524,15 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">'B-RFID'!F15</f>
-        <v>15738.4231185465</v>
+        <v>16587.5961087909</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'B-RFID'!G15</f>
-        <v>293219.724015103</v>
+        <v>307778.897865651</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">D10/Estações!$O$43</f>
-        <v>7330.49310037757</v>
+        <v>7694.47244664127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,7 +3045,7 @@
         <v>82</v>
       </c>
       <c r="J2" s="21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="21" t="n">
         <v>10</v>
@@ -3055,11 +3055,11 @@
       </c>
       <c r="M2" s="22" t="n">
         <f aca="false">H2+J2</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" s="22" t="n">
         <f aca="false">K2+M2+2</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2" s="21" t="n">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>156</v>
       </c>
       <c r="J3" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" s="21" t="n">
         <v>10</v>
@@ -3104,11 +3104,11 @@
       </c>
       <c r="M3" s="22" t="n">
         <f aca="false">H3+J3</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N3" s="22" t="n">
         <f aca="false">K3+M3+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O3" s="21" t="n">
         <v>1</v>
@@ -3143,7 +3143,7 @@
         <v>160</v>
       </c>
       <c r="J4" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" s="21" t="n">
         <v>10</v>
@@ -3153,11 +3153,11 @@
       </c>
       <c r="M4" s="22" t="n">
         <f aca="false">H4+J4</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N4" s="22" t="n">
         <f aca="false">K4+M4+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O4" s="21" t="n">
         <v>1</v>
@@ -3192,7 +3192,7 @@
         <v>160</v>
       </c>
       <c r="J5" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="21" t="n">
         <v>10</v>
@@ -3202,11 +3202,11 @@
       </c>
       <c r="M5" s="22" t="n">
         <f aca="false">H5+J5</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N5" s="22" t="n">
         <f aca="false">K5+M5+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O5" s="21" t="n">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>160</v>
       </c>
       <c r="J6" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" s="21" t="n">
         <v>10</v>
@@ -3251,11 +3251,11 @@
       </c>
       <c r="M6" s="22" t="n">
         <f aca="false">H6+J6</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N6" s="22" t="n">
         <f aca="false">K6+M6+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O6" s="21" t="n">
         <v>1</v>
@@ -3290,7 +3290,7 @@
         <v>160</v>
       </c>
       <c r="J7" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K7" s="21" t="n">
         <v>10</v>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="M7" s="22" t="n">
         <f aca="false">H7+J7</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N7" s="22" t="n">
         <f aca="false">K7+M7+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O7" s="21" t="n">
         <v>1</v>
@@ -3339,7 +3339,7 @@
         <v>192</v>
       </c>
       <c r="J8" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K8" s="21" t="n">
         <v>10</v>
@@ -3349,11 +3349,11 @@
       </c>
       <c r="M8" s="22" t="n">
         <f aca="false">H8+J8</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N8" s="22" t="n">
         <f aca="false">K8+M8+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O8" s="21" t="n">
         <v>1</v>
@@ -3388,7 +3388,7 @@
         <v>188</v>
       </c>
       <c r="J9" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K9" s="21" t="n">
         <v>10</v>
@@ -3398,11 +3398,11 @@
       </c>
       <c r="M9" s="22" t="n">
         <f aca="false">H9+J9</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N9" s="22" t="n">
         <f aca="false">K9+M9+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O9" s="21" t="n">
         <v>1</v>
@@ -3437,7 +3437,7 @@
         <v>160</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>10</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="M10" s="22" t="n">
         <f aca="false">H10+J10</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N10" s="22" t="n">
         <f aca="false">K10+M10+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O10" s="21" t="n">
         <v>1</v>
@@ -3486,7 +3486,7 @@
         <v>160</v>
       </c>
       <c r="J11" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K11" s="21" t="n">
         <v>10</v>
@@ -3496,11 +3496,11 @@
       </c>
       <c r="M11" s="22" t="n">
         <f aca="false">H11+J11</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N11" s="22" t="n">
         <f aca="false">K11+M11+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O11" s="21" t="n">
         <v>1</v>
@@ -3535,7 +3535,7 @@
         <v>160</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K12" s="21" t="n">
         <v>10</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="M12" s="22" t="n">
         <f aca="false">H12+J12</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N12" s="22" t="n">
         <f aca="false">K12+M12+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O12" s="21" t="n">
         <v>1</v>
@@ -3584,7 +3584,7 @@
         <v>160</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K13" s="21" t="n">
         <v>10</v>
@@ -3594,11 +3594,11 @@
       </c>
       <c r="M13" s="22" t="n">
         <f aca="false">H13+J13</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N13" s="22" t="n">
         <f aca="false">K13+M13+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O13" s="21" t="n">
         <v>1</v>
@@ -3633,7 +3633,7 @@
         <v>192</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14" s="21" t="n">
         <v>10</v>
@@ -3643,11 +3643,11 @@
       </c>
       <c r="M14" s="22" t="n">
         <f aca="false">H14+J14</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N14" s="22" t="n">
         <f aca="false">K14+M14+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O14" s="21" t="n">
         <v>1</v>
@@ -3682,7 +3682,7 @@
         <v>188</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K15" s="21" t="n">
         <v>10</v>
@@ -3692,11 +3692,11 @@
       </c>
       <c r="M15" s="22" t="n">
         <f aca="false">H15+J15</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N15" s="22" t="n">
         <f aca="false">K15+M15+2</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O15" s="21" t="n">
         <v>1</v>
@@ -3731,7 +3731,7 @@
         <v>160</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16" s="21" t="n">
         <v>10</v>
@@ -3741,11 +3741,11 @@
       </c>
       <c r="M16" s="22" t="n">
         <f aca="false">H16+J16</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N16" s="22" t="n">
         <f aca="false">K16+M16+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O16" s="21" t="n">
         <v>1</v>
@@ -3780,7 +3780,7 @@
         <v>160</v>
       </c>
       <c r="J17" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K17" s="21" t="n">
         <v>10</v>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="M17" s="22" t="n">
         <f aca="false">H17+J17</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N17" s="22" t="n">
         <f aca="false">K17+M17+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O17" s="21" t="n">
         <v>1</v>
@@ -3829,7 +3829,7 @@
         <v>160</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K18" s="21" t="n">
         <v>10</v>
@@ -3839,11 +3839,11 @@
       </c>
       <c r="M18" s="22" t="n">
         <f aca="false">H18+J18</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N18" s="22" t="n">
         <f aca="false">K18+M18+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O18" s="21" t="n">
         <v>1</v>
@@ -3878,7 +3878,7 @@
         <v>160</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K19" s="21" t="n">
         <v>10</v>
@@ -3888,11 +3888,11 @@
       </c>
       <c r="M19" s="22" t="n">
         <f aca="false">H19+J19</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N19" s="22" t="n">
         <f aca="false">K19+M19+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O19" s="21" t="n">
         <v>1</v>
@@ -3927,7 +3927,7 @@
         <v>160</v>
       </c>
       <c r="J20" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="21" t="n">
         <v>10</v>
@@ -3937,11 +3937,11 @@
       </c>
       <c r="M20" s="22" t="n">
         <f aca="false">H20+J20</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N20" s="22" t="n">
         <f aca="false">K20+M20+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O20" s="21" t="n">
         <v>1</v>
@@ -4025,7 +4025,7 @@
         <v>128</v>
       </c>
       <c r="J22" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="21" t="n">
         <v>10</v>
@@ -4035,11 +4035,11 @@
       </c>
       <c r="M22" s="22" t="n">
         <f aca="false">H22+J22</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N22" s="22" t="n">
         <f aca="false">K22+M22+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O22" s="21" t="n">
         <v>1</v>
@@ -4074,7 +4074,7 @@
         <v>131</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K23" s="21" t="n">
         <v>10</v>
@@ -4084,11 +4084,11 @@
       </c>
       <c r="M23" s="22" t="n">
         <f aca="false">H23+J23</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N23" s="22" t="n">
         <f aca="false">K23+M23+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O23" s="21" t="n">
         <v>1</v>
@@ -4123,7 +4123,7 @@
         <v>131</v>
       </c>
       <c r="J24" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K24" s="21" t="n">
         <v>10</v>
@@ -4133,11 +4133,11 @@
       </c>
       <c r="M24" s="22" t="n">
         <f aca="false">H24+J24</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N24" s="22" t="n">
         <f aca="false">K24+M24+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O24" s="21" t="n">
         <v>1</v>
@@ -4172,7 +4172,7 @@
         <v>131</v>
       </c>
       <c r="J25" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K25" s="21" t="n">
         <v>10</v>
@@ -4182,11 +4182,11 @@
       </c>
       <c r="M25" s="22" t="n">
         <f aca="false">H25+J25</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N25" s="22" t="n">
         <f aca="false">K25+M25+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O25" s="21" t="n">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>131</v>
       </c>
       <c r="J26" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K26" s="21" t="n">
         <v>10</v>
@@ -4231,11 +4231,11 @@
       </c>
       <c r="M26" s="22" t="n">
         <f aca="false">H26+J26</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N26" s="22" t="n">
         <f aca="false">K26+M26+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O26" s="21" t="n">
         <v>1</v>
@@ -4270,7 +4270,7 @@
         <v>131</v>
       </c>
       <c r="J27" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="21" t="n">
         <v>10</v>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="M27" s="22" t="n">
         <f aca="false">H27+J27</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N27" s="22" t="n">
         <f aca="false">K27+M27+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O27" s="21" t="n">
         <v>1</v>
@@ -4319,7 +4319,7 @@
         <v>230</v>
       </c>
       <c r="J28" s="21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="21" t="n">
         <v>10</v>
@@ -4329,11 +4329,11 @@
       </c>
       <c r="M28" s="22" t="n">
         <f aca="false">H28+J28</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N28" s="22" t="n">
         <f aca="false">K28+M28+2</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O28" s="21" t="n">
         <v>1</v>
@@ -4368,7 +4368,7 @@
         <v>227</v>
       </c>
       <c r="J29" s="21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K29" s="21" t="n">
         <v>10</v>
@@ -4378,11 +4378,11 @@
       </c>
       <c r="M29" s="22" t="n">
         <f aca="false">H29+J29</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N29" s="22" t="n">
         <f aca="false">K29+M29+2</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O29" s="21" t="n">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>131</v>
       </c>
       <c r="J30" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K30" s="21" t="n">
         <v>10</v>
@@ -4427,11 +4427,11 @@
       </c>
       <c r="M30" s="22" t="n">
         <f aca="false">H30+J30</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N30" s="22" t="n">
         <f aca="false">K30+M30+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O30" s="21" t="n">
         <v>1</v>
@@ -4466,7 +4466,7 @@
         <v>131</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K31" s="21" t="n">
         <v>10</v>
@@ -4476,11 +4476,11 @@
       </c>
       <c r="M31" s="22" t="n">
         <f aca="false">H31+J31</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N31" s="22" t="n">
         <f aca="false">K31+M31+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O31" s="21" t="n">
         <v>1</v>
@@ -4515,7 +4515,7 @@
         <v>131</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K32" s="21" t="n">
         <v>10</v>
@@ -4525,11 +4525,11 @@
       </c>
       <c r="M32" s="22" t="n">
         <f aca="false">H32+J32</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N32" s="22" t="n">
         <f aca="false">K32+M32+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O32" s="21" t="n">
         <v>1</v>
@@ -4564,7 +4564,7 @@
         <v>131</v>
       </c>
       <c r="J33" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K33" s="21" t="n">
         <v>10</v>
@@ -4574,11 +4574,11 @@
       </c>
       <c r="M33" s="22" t="n">
         <f aca="false">H33+J33</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N33" s="22" t="n">
         <f aca="false">K33+M33+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O33" s="21" t="n">
         <v>1</v>
@@ -4613,7 +4613,7 @@
         <v>230</v>
       </c>
       <c r="J34" s="21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K34" s="21" t="n">
         <v>10</v>
@@ -4623,11 +4623,11 @@
       </c>
       <c r="M34" s="22" t="n">
         <f aca="false">H34+J34</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N34" s="22" t="n">
         <f aca="false">K34+M34+2</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O34" s="21" t="n">
         <v>1</v>
@@ -4662,7 +4662,7 @@
         <v>227</v>
       </c>
       <c r="J35" s="21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K35" s="21" t="n">
         <v>10</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="M35" s="22" t="n">
         <f aca="false">H35+J35</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N35" s="22" t="n">
         <f aca="false">K35+M35+2</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O35" s="21" t="n">
         <v>1</v>
@@ -4711,7 +4711,7 @@
         <v>131</v>
       </c>
       <c r="J36" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K36" s="21" t="n">
         <v>10</v>
@@ -4721,11 +4721,11 @@
       </c>
       <c r="M36" s="22" t="n">
         <f aca="false">H36+J36</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N36" s="22" t="n">
         <f aca="false">K36+M36+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O36" s="21" t="n">
         <v>1</v>
@@ -4760,7 +4760,7 @@
         <v>131</v>
       </c>
       <c r="J37" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K37" s="21" t="n">
         <v>10</v>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="M37" s="22" t="n">
         <f aca="false">H37+J37</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N37" s="22" t="n">
         <f aca="false">K37+M37+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O37" s="21" t="n">
         <v>1</v>
@@ -4809,7 +4809,7 @@
         <v>131</v>
       </c>
       <c r="J38" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K38" s="21" t="n">
         <v>10</v>
@@ -4819,11 +4819,11 @@
       </c>
       <c r="M38" s="22" t="n">
         <f aca="false">H38+J38</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N38" s="22" t="n">
         <f aca="false">K38+M38+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O38" s="21" t="n">
         <v>1</v>
@@ -4858,7 +4858,7 @@
         <v>131</v>
       </c>
       <c r="J39" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K39" s="21" t="n">
         <v>10</v>
@@ -4868,11 +4868,11 @@
       </c>
       <c r="M39" s="22" t="n">
         <f aca="false">H39+J39</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N39" s="22" t="n">
         <f aca="false">K39+M39+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O39" s="21" t="n">
         <v>1</v>
@@ -4907,7 +4907,7 @@
         <v>131</v>
       </c>
       <c r="J40" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K40" s="21" t="n">
         <v>10</v>
@@ -4917,11 +4917,11 @@
       </c>
       <c r="M40" s="22" t="n">
         <f aca="false">H40+J40</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N40" s="22" t="n">
         <f aca="false">K40+M40+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O40" s="21" t="n">
         <v>1</v>
@@ -4956,7 +4956,7 @@
         <v>131</v>
       </c>
       <c r="J41" s="21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K41" s="21" t="n">
         <v>10</v>
@@ -4966,11 +4966,11 @@
       </c>
       <c r="M41" s="22" t="n">
         <f aca="false">H41+J41</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N41" s="22" t="n">
         <f aca="false">K41+M41+2</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O41" s="21" t="n">
         <v>1</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="J43" s="25" t="n">
         <f aca="false">SUM(J2:J41)</f>
-        <v>248</v>
+        <v>325</v>
       </c>
       <c r="K43" s="25" t="n">
         <f aca="false">SUM(K2:K41)</f>
@@ -5018,11 +5018,11 @@
       </c>
       <c r="M43" s="25" t="n">
         <f aca="false">SUM(M2:M41)</f>
-        <v>408</v>
+        <v>485</v>
       </c>
       <c r="N43" s="25" t="n">
         <f aca="false">SUM(N2:N41)</f>
-        <v>888</v>
+        <v>965</v>
       </c>
       <c r="O43" s="25" t="n">
         <f aca="false">SUM(O2:O41)</f>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="J44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",J2:J41)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",K2:K41)</f>
@@ -5071,11 +5071,11 @@
       </c>
       <c r="M44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",M2:M41)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",N2:N41)</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O44" s="25" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",O2:O41)</f>
@@ -7285,11 +7285,11 @@
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$14),0)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D5" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$14),0)</f>
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="E5" s="33" t="n">
         <f aca="false">Composição!$F$27</f>
@@ -7297,11 +7297,11 @@
       </c>
       <c r="F5" s="27" t="n">
         <f aca="false">C5*E5</f>
-        <v>2726.9</v>
+        <v>3346.65</v>
       </c>
       <c r="G5" s="27" t="n">
         <f aca="false">D5*E5</f>
-        <v>55653.55</v>
+        <v>66189.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7341,11 +7341,11 @@
       </c>
       <c r="C7" s="37" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$15</f>
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="false">Estações!$N$43*Premissas!$B$15</f>
-        <v>2664</v>
+        <v>2895</v>
       </c>
       <c r="E7" s="33" t="n">
         <f aca="false">Preços!$D$13</f>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="F7" s="27" t="n">
         <f aca="false">C7*E7</f>
-        <v>532.072524590164</v>
+        <v>580.442754098361</v>
       </c>
       <c r="G7" s="27" t="n">
         <f aca="false">D7*E7</f>
-        <v>10738.1909508197</v>
+        <v>11669.3178688525</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7369,11 +7369,11 @@
       </c>
       <c r="C8" s="37" t="n">
         <f aca="false">Estações!$N$44*2</f>
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D8" s="37" t="n">
         <f aca="false">Estações!$N$43*2</f>
-        <v>1776</v>
+        <v>1930</v>
       </c>
       <c r="E8" s="33" t="n">
         <f aca="false">Preços!$D$12</f>
@@ -7381,11 +7381,11 @@
       </c>
       <c r="F8" s="27" t="n">
         <f aca="false">C8*E8</f>
-        <v>70.4</v>
+        <v>76.8</v>
       </c>
       <c r="G8" s="27" t="n">
         <f aca="false">D8*E8</f>
-        <v>1420.8</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7510,11 +7510,11 @@
       <c r="E13" s="35"/>
       <c r="F13" s="36" t="n">
         <f aca="false">SUM(F3:F12)</f>
-        <v>10993.9714446721</v>
+        <v>11668.4916741803</v>
       </c>
       <c r="G13" s="36" t="n">
         <f aca="false">SUM(G3:G12)</f>
-        <v>199238.884893443</v>
+        <v>210828.961811475</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7587,11 +7587,11 @@
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C5*Premissas!$B$10</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">D5*Premissas!$B$10</f>
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="E18" s="33" t="n">
         <f aca="false">Premissas!$B$7</f>
@@ -7599,11 +7599,11 @@
       </c>
       <c r="F18" s="27" t="n">
         <f aca="false">C18*E18</f>
-        <v>768.472147239264</v>
+        <v>943.12490797546</v>
       </c>
       <c r="G18" s="27" t="n">
         <f aca="false">D18*E18</f>
-        <v>15683.8179141104</v>
+        <v>18652.9148466258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7697,20 +7697,20 @@
       <c r="B22" s="35"/>
       <c r="C22" s="38" t="n">
         <f aca="false">SUM(C16:C21)</f>
-        <v>102.25</v>
+        <v>107.25</v>
       </c>
       <c r="D22" s="38" t="n">
         <f aca="false">SUM(D16:D21)</f>
-        <v>2019</v>
+        <v>2104</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="36" t="n">
         <f aca="false">SUM(F16:F21)</f>
-        <v>3571.64895705522</v>
+        <v>3746.30171779141</v>
       </c>
       <c r="G22" s="36" t="n">
         <f aca="false">SUM(G16:G21)</f>
-        <v>70524.7847852761</v>
+        <v>73493.8817177914</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7723,11 +7723,11 @@
       <c r="E24" s="35"/>
       <c r="F24" s="36" t="n">
         <f aca="false">F13+F22</f>
-        <v>14565.6204017273</v>
+        <v>15414.7933919717</v>
       </c>
       <c r="G24" s="36" t="n">
         <f aca="false">G13+G22</f>
-        <v>269763.669678719</v>
+        <v>284322.843529267</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7744,11 +7744,11 @@
       </c>
       <c r="C27" s="37" t="n">
         <f aca="false">-(C4+C5+C6)</f>
-        <v>-47</v>
+        <v>-52</v>
       </c>
       <c r="D27" s="37" t="n">
         <f aca="false">-(D4+D5+D6)</f>
-        <v>-933</v>
+        <v>-1018</v>
       </c>
       <c r="E27" s="33" t="n">
         <f aca="false">Preços!$D$9</f>
@@ -7756,11 +7756,11 @@
       </c>
       <c r="F27" s="27" t="n">
         <f aca="false">C27*E27</f>
-        <v>-376</v>
+        <v>-416</v>
       </c>
       <c r="G27" s="27" t="n">
         <f aca="false">D27*E27</f>
-        <v>-7464</v>
+        <v>-8144</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,11 +7829,11 @@
       <c r="E30" s="35"/>
       <c r="F30" s="36" t="n">
         <f aca="false">F13+SUM(F27:F29)</f>
-        <v>10873.0314446721</v>
+        <v>11507.5516741803</v>
       </c>
       <c r="G30" s="36" t="n">
         <f aca="false">G13+SUM(G27:G29)</f>
-        <v>196955.764893443</v>
+        <v>207865.841811475</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C4" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$14),0)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D4" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$14),0)</f>
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="E4" s="33" t="n">
         <f aca="false">Preços!$D$34+Preços!$D$15+Preços!$D$10</f>
@@ -7973,11 +7973,11 @@
       </c>
       <c r="F4" s="27" t="n">
         <f aca="false">C4*E4</f>
-        <v>5119.97948</v>
+        <v>6283.61118</v>
       </c>
       <c r="G4" s="27" t="n">
         <f aca="false">D4*E4</f>
-        <v>104494.12666</v>
+        <v>124275.86556</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8017,11 +8017,11 @@
       </c>
       <c r="C6" s="37" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*Premissas!$B$15</f>
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D6" s="37" t="n">
         <f aca="false">(Estações!$F$43+Estações!$M$43)*Premissas!$B$15</f>
-        <v>5064</v>
+        <v>5295</v>
       </c>
       <c r="E6" s="33" t="n">
         <f aca="false">Preços!$D$13+2*Preços!$D$12/Premissas!$B$15</f>
@@ -8029,11 +8029,11 @@
       </c>
       <c r="F6" s="27" t="n">
         <f aca="false">C6*E6</f>
-        <v>1150.17481967213</v>
+        <v>1204.94504918033</v>
       </c>
       <c r="G6" s="27" t="n">
         <f aca="false">D6*E6</f>
-        <v>23113.036852459</v>
+        <v>24167.3637704918</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8123,11 +8123,11 @@
       <c r="E10" s="35"/>
       <c r="F10" s="36" t="n">
         <f aca="false">SUM(F3:F9)</f>
-        <v>32808.1033114633</v>
+        <v>34026.5052409715</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">SUM(G3:G9)</f>
-        <v>347860.285788283</v>
+        <v>368696.351606316</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8172,11 +8172,11 @@
       </c>
       <c r="C14" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$14),0)</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D14" s="37" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$14),0)</f>
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="E14" s="33" t="n">
         <f aca="false">Preços!$D$31</f>
@@ -8184,11 +8184,11 @@
       </c>
       <c r="F14" s="27" t="n">
         <f aca="false">C14*E14</f>
-        <v>13697.2121</v>
+        <v>16810.21485</v>
       </c>
       <c r="G14" s="27" t="n">
         <f aca="false">D14*E14</f>
-        <v>279547.64695</v>
+        <v>332468.6937</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8256,11 +8256,11 @@
       </c>
       <c r="C17" s="37" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*Premissas!$B$15</f>
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D17" s="37" t="n">
         <f aca="false">(Estações!$F$43+Estações!$M$43)*Premissas!$B$15</f>
-        <v>5064</v>
+        <v>5295</v>
       </c>
       <c r="E17" s="33" t="n">
         <f aca="false">Preços!$D$13+2*Preços!$D$12/Premissas!$B$15</f>
@@ -8268,11 +8268,11 @@
       </c>
       <c r="F17" s="27" t="n">
         <f aca="false">C17*E17</f>
-        <v>1150.17481967213</v>
+        <v>1204.94504918033</v>
       </c>
       <c r="G17" s="27" t="n">
         <f aca="false">D17*E17</f>
-        <v>23113.036852459</v>
+        <v>24167.3637704918</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8336,11 +8336,11 @@
       <c r="E20" s="35"/>
       <c r="F20" s="36" t="n">
         <f aca="false">SUM(F13:F19)</f>
-        <v>43195.6421514633</v>
+        <v>46363.4151309715</v>
       </c>
       <c r="G20" s="36" t="n">
         <f aca="false">SUM(G13:G19)</f>
-        <v>852329.779238283</v>
+        <v>906305.152906316</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8416,11 +8416,11 @@
       <c r="E3" s="13"/>
       <c r="F3" s="33" t="n">
         <f aca="false">'A-Interno'!F24</f>
-        <v>14565.6204017273</v>
+        <v>15414.7933919717</v>
       </c>
       <c r="G3" s="33" t="n">
         <f aca="false">'A-Interno'!G24</f>
-        <v>269763.669678719</v>
+        <v>284322.843529267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8550,11 +8550,11 @@
       <c r="E10" s="35"/>
       <c r="F10" s="36" t="n">
         <f aca="false">F3+F4+F5+F8+F9</f>
-        <v>15895.69987003</v>
+        <v>16744.8728602744</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">G3+G4+G5+G8+G9</f>
-        <v>294206.029106122</v>
+        <v>308765.20295667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8628,11 +8628,11 @@
       <c r="E15" s="35"/>
       <c r="F15" s="36" t="n">
         <f aca="false">F3+F4+F5+F13+F14</f>
-        <v>15738.4231185465</v>
+        <v>16587.5961087909</v>
       </c>
       <c r="G15" s="36" t="n">
         <f aca="false">G3+G4+G5+G13+G14</f>
-        <v>293219.724015103</v>
+        <v>307778.897865651</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="433">
   <si>
-    <t xml:space="preserve">Orçamento — Projeto Pick-to-Light (Flow Rack)</t>
+    <t xml:space="preserve">Orçamento do projeto Pick-to-Light (flow rack)</t>
   </si>
   <si>
     <t xml:space="preserve">Arquitetura A (coletor + concentrador + displays) e Arquitetura B (identificação por RFID)</t>
@@ -40,13 +40,13 @@
     <t xml:space="preserve">COMO USAR</t>
   </si>
   <si>
-    <t xml:space="preserve">• Células em AZUL são entradas editáveis (quantidades, preços, premissas). Células em PRETO são fórmulas — não editar.</t>
+    <t xml:space="preserve">• Células em AZUL são entradas editáveis (quantidades, preços, premissas). Células em PRETO são fórmulas: não editar.</t>
   </si>
   <si>
     <t xml:space="preserve">• Células com fundo AMARELO são premissas/estimativas que precisam de cotação ou confirmação.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Aba 'Estações': números de endereços por estação, extraídos de wms_endereco (esteiras 1 e 2) em 23/10/2026. Corrija qualquer número direto ali — todo o orçamento recalcula.</t>
+    <t xml:space="preserve">• Aba 'Estações': números de endereços por estação, extraídos de wms_endereco (esteiras 1 e 2) em 23/10/2026. Corrija qualquer número direto ali: todo o orçamento recalcula.</t>
   </si>
   <si>
     <t xml:space="preserve">• Coluna 'Piloto' (S/N) na aba 'Estações' define quais estações entram no cenário piloto (padrão: 05 e 27).</t>
@@ -58,52 +58,52 @@
     <t xml:space="preserve">ABAS</t>
   </si>
   <si>
-    <t xml:space="preserve">Premissas — câmbio, fator de importação, custo-hora, horas de montagem/instalação, reserva técnica, frota de caixas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estações — dimensionamento por estação (40 estações: 20 Medicamento + 20 Perfumaria).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preços — catálogo de peças com fonte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composição — lista de materiais (BOM) de cada tipo de módulo e custo unitário.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-Interno — Arquitetura A com produção interna: peças, peças + mão de obra, variante 5 V.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-Terceiros — Arquitetura A com produção de terceiros: (T1) placa própria montada por EMS e (T2) PTL comercial importado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B-RFID — Arquitetura B: mesma infraestrutura de displays + identificação RFID (B1 pulseira, B2 leitor fixo).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software — esforço estimado de desenvolvimento (horas) para as duas arquiteturas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumo — comparativo de todos os cenários: Piloto x Operação completa.</t>
+    <t xml:space="preserve">Premissas: câmbio, fator de importação, custo-hora, horas de montagem/instalação, reserva técnica, frota de caixas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estações: dimensionamento por estação (40 estações: 20 Medicamento + 20 Perfumaria).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preços: catálogo de peças com fonte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composição: lista de materiais (BOM) de cada tipo de módulo e custo unitário.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Interno: Arquitetura A com produção interna: peças, peças + mão de obra, variante 5 V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Terceiros: Arquitetura A com produção de terceiros: (T1) placa própria montada por EMS e (T2) PTL comercial importado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B-RFID: Arquitetura B: mesma infraestrutura de displays + identificação RFID (B1 pulseira, B2 leitor fixo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software: esforço estimado de desenvolvimento (horas) para as duas arquiteturas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumo: comparativo de todos os cenários: Piloto x Operação completa.</t>
   </si>
   <si>
     <t xml:space="preserve">TERMOS</t>
   </si>
   <si>
-    <t xml:space="preserve">Módulo Q — display de QUANTIDADE (3 dígitos) + botão com LED, um por endereço de alto giro (andares 0 a 3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Módulo E+Q — display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (1 por andar em cada lado: 4 por estação) e em cada zona de baixo giro (4 zonas por lado do corredor, na altura dos olhos).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nó de coluna — microcontrolador por coluna (prédio) do alto giro que liga os Módulos Q daquela coluna ao barramento RS-485.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrador — controlador da estação (Ethernet cabeada), recebe a caixa do serviço PTL e comanda os barramentos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zona de baixo giro — 1 display E+Q a cada 4 prédios do fundo (inclui prédio 015 na 1ª zona e prédios de esquina).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumo do orçamento — Pick-to-Light</t>
+    <t xml:space="preserve">Módulo Q: display de QUANTIDADE (3 dígitos) + botão com LED, um por endereço de alto giro (andares 0 a 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Módulo E+Q: display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (1 por andar em cada lado: 4 por estação) e em cada zona de baixo giro (4 zonas por lado do corredor, na altura dos olhos).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nó de coluna: microcontrolador por coluna (prédio) do alto giro que liga os Módulos Q daquela coluna ao barramento RS-485.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrador: controlador da estação (Ethernet cabeada), recebe a caixa do serviço PTL e comanda os barramentos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zona de baixo giro: 4 zonas por lado do corredor, cada uma com 1 display E+Q na altura dos olhos (o prédio 015 entra na zona D1; esquinas têm zonas de 4 prédios).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumo do orçamento, Pick-to-Light</t>
   </si>
   <si>
     <t xml:space="preserve">Piloto: estações marcadas 'S' na aba Estações (padrão 05 e 27). Valores de hardware; software na última linha.</t>
@@ -121,52 +121,52 @@
     <t xml:space="preserve">Operação completa (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Por estação — completo (R$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A — Interno, só peças (12 V)</t>
+    <t xml:space="preserve">Por estação, completo (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A interno, só peças (12 V)</t>
   </si>
   <si>
     <t xml:space="preserve">Peças para toda a operação, montagem própria</t>
   </si>
   <si>
-    <t xml:space="preserve">A — Interno, só peças (variante 5 V)</t>
+    <t xml:space="preserve">A interno, só peças (variante 5 V)</t>
   </si>
   <si>
     <t xml:space="preserve">Sem reguladores, fonte 5 V, mais cabo de força</t>
   </si>
   <si>
-    <t xml:space="preserve">A — Interno, peças + mão de obra</t>
+    <t xml:space="preserve">A interno, peças + mão de obra</t>
   </si>
   <si>
     <t xml:space="preserve">Montagem, instalação e comissionamento internos</t>
   </si>
   <si>
-    <t xml:space="preserve">A — Terceiros T1 (PCB própria via EMS)</t>
+    <t xml:space="preserve">A terceiros, T1 (PCB própria via EMS)</t>
   </si>
   <si>
     <t xml:space="preserve">Placas próprias fabricadas/montadas por terceiros + instalação</t>
   </si>
   <si>
-    <t xml:space="preserve">A — Terceiros T2 (PTL comercial importado)</t>
+    <t xml:space="preserve">A terceiros, T2 (PTL comercial importado)</t>
   </si>
   <si>
     <t xml:space="preserve">Hardware PTL pronto + instalação</t>
   </si>
   <si>
-    <t xml:space="preserve">B1 — RFID com pulseira</t>
+    <t xml:space="preserve">B1, RFID com pulseira</t>
   </si>
   <si>
     <t xml:space="preserve">Displays (A interno) + tags + pulseiras NFC</t>
   </si>
   <si>
-    <t xml:space="preserve">B2 — RFID com leitor fixo na estação</t>
+    <t xml:space="preserve">B2, RFID com leitor fixo na estação</t>
   </si>
   <si>
     <t xml:space="preserve">Displays (A interno) + tags + leitor fixo e painel</t>
   </si>
   <si>
-    <t xml:space="preserve">Opcional — guia de coluna no baixo giro</t>
+    <t xml:space="preserve">Opcional, guia de coluna no baixo giro</t>
   </si>
   <si>
     <t xml:space="preserve">1 LED por prédio do fundo</t>
@@ -202,7 +202,7 @@
     <t xml:space="preserve">R$/US$</t>
   </si>
   <si>
-    <t xml:space="preserve">renovainvest.com.br/dolar-hoje — 23/10/2026 12h11</t>
+    <t xml:space="preserve">renovainvest.com.br/dolar-hoje, 23/10/2026 12h11</t>
   </si>
   <si>
     <t xml:space="preserve">Fator de importação (frete + impostos + despacho) sobre o valor FOB</t>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">Fórmula: salário × encargos ÷ horas</t>
   </si>
   <si>
-    <t xml:space="preserve">Montagem — Módulo Q</t>
+    <t xml:space="preserve">Montagem, Módulo Q</t>
   </si>
   <si>
     <t xml:space="preserve">h/un</t>
@@ -256,19 +256,19 @@
     <t xml:space="preserve">Estimativa: display + botão + carcaça + teste</t>
   </si>
   <si>
-    <t xml:space="preserve">Montagem — Nó de coluna</t>
+    <t xml:space="preserve">Montagem, Nó de coluna</t>
   </si>
   <si>
     <t xml:space="preserve">Estimativa: placa base, soldas, gravação de firmware, teste</t>
   </si>
   <si>
-    <t xml:space="preserve">Montagem — Módulo E+Q</t>
+    <t xml:space="preserve">Montagem, Módulo E+Q</t>
   </si>
   <si>
     <t xml:space="preserve">Estimativa</t>
   </si>
   <si>
-    <t xml:space="preserve">Montagem — Concentrador (gabinete completo)</t>
+    <t xml:space="preserve">Montagem, Concentrador (gabinete completo)</t>
   </si>
   <si>
     <t xml:space="preserve">Instalação por estação (canaletas, módulos, cabos)</t>
@@ -358,7 +358,7 @@
     <t xml:space="preserve">R$/m</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa — cotar</t>
+    <t xml:space="preserve">Estimativa, cotar</t>
   </si>
   <si>
     <t xml:space="preserve">Rua (estação)</t>
@@ -552,10 +552,10 @@
     <t xml:space="preserve">45</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL — operação completa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL — piloto (Piloto = S)</t>
+    <t xml:space="preserve">Total da operação completa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total do piloto (Piloto = S)</t>
   </si>
   <si>
     <t xml:space="preserve">Coluna D (Piloto) = quantidade de estações nas linhas de total. Fonte: wms_endereco (cd_esteira 1 e 2), exportado em 23/10/2026; rua 90 (Marketing/Almoxarifado) desconsiderada.</t>
@@ -585,10 +585,10 @@
     <t xml:space="preserve">P01</t>
   </si>
   <si>
-    <t xml:space="preserve">Display 7 segmentos 4 dígitos TM1637 (usa 3 dígitos — quantidade)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usinainfo — Módulo Display TM1637 4 dígitos vermelho — 23/10/2026 (Pix)</t>
+    <t xml:space="preserve">Display 7 segmentos 4 dígitos TM1637 (usa 3 dígitos, quantidade)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usinainfo, Módulo Display TM1637 4 dígitos vermelho, 23/10/2026 (Pix)</t>
   </si>
   <si>
     <t xml:space="preserve">Cotado</t>
@@ -600,7 +600,7 @@
     <t xml:space="preserve">Display 7 segmentos 8 dígitos MAX7219 (endereço)</t>
   </si>
   <si>
-    <t xml:space="preserve">Usinainfo — Display MAX7219 8 dígitos SPI — 23/10/2026 (Pix)</t>
+    <t xml:space="preserve">Usinainfo, Display MAX7219 8 dígitos SPI, 23/10/2026 (Pix)</t>
   </si>
   <si>
     <t xml:space="preserve">P03</t>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">Microcontrolador Raspberry Pi Pico (RP2040)</t>
   </si>
   <si>
-    <t xml:space="preserve">MakerHero — Raspberry Pi Pico — 23/10/2026</t>
+    <t xml:space="preserve">MakerHero, Raspberry Pi Pico, 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">P04</t>
@@ -618,7 +618,7 @@
     <t xml:space="preserve">Módulo transceptor RS-485 (MAX485)</t>
   </si>
   <si>
-    <t xml:space="preserve">Saravati — Módulo conversor TTL/RS485 MAX485 — 23/10/2026</t>
+    <t xml:space="preserve">Saravati, Módulo conversor TTL/RS485 MAX485, 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">P05</t>
@@ -627,7 +627,7 @@
     <t xml:space="preserve">Placa do concentrador RP2040 + Ethernet W5500 (W5500-EVB-Pico)</t>
   </si>
   <si>
-    <t xml:space="preserve">SparkFun DEV-19958 US$ 12,50 — 23/10/2026; convertido com câmbio × fator de importação</t>
+    <t xml:space="preserve">SparkFun DEV-19958 US$ 12,50, 23/10/2026; convertido com câmbio × fator de importação</t>
   </si>
   <si>
     <t xml:space="preserve">Cotado (US$)</t>
@@ -639,16 +639,16 @@
     <t xml:space="preserve">Fonte Mean Well LRS-150-12 (12 V / 12,5 A / 150 W)</t>
   </si>
   <si>
-    <t xml:space="preserve">MCEIG (fontesmeanwell.com.br) — 23/10/2026</t>
+    <t xml:space="preserve">MCEIG (fontesmeanwell.com.br), 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">P07</t>
   </si>
   <si>
-    <t xml:space="preserve">Fonte Mean Well LRS-150-5 (5 V / 26 A) — variante 5 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimativa (mesma família da LRS-150-12) — cotar</t>
+    <t xml:space="preserve">Fonte Mean Well LRS-150-5 (5 V / 26 A), variante 5 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimativa (mesma família da LRS-150-12), cotar</t>
   </si>
   <si>
     <t xml:space="preserve">P08</t>
@@ -657,7 +657,7 @@
     <t xml:space="preserve">Regulador step-down 12 V → 5 V (mini, 3 A)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa de mercado — cotar</t>
+    <t xml:space="preserve">Estimativa de mercado, cotar</t>
   </si>
   <si>
     <t xml:space="preserve">P09</t>
@@ -678,7 +678,7 @@
     <t xml:space="preserve">Plug RJ45 Cat5e (macho)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa (pote com 100) — cotar</t>
+    <t xml:space="preserve">Estimativa (pote com 100), cotar</t>
   </si>
   <si>
     <t xml:space="preserve">P12</t>
@@ -687,7 +687,7 @@
     <t xml:space="preserve">Cabo Cat5e (por metro)</t>
   </si>
   <si>
-    <t xml:space="preserve">KaBuM — Cabo Cat5e Fortrek FK500C 305 m R$ 1.229,41 (Pix) — 23/10/2026</t>
+    <t xml:space="preserve">KaBuM, Cabo Cat5e Fortrek FK500C 305 m R$ 1.229,41 (Pix), 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">P13</t>
@@ -714,7 +714,7 @@
     <t xml:space="preserve">Gabinete do concentrador ventilado (caixa IP54 + cooler 40 mm 12 V + filtro)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa — cotar (ambiente com poeira e calor)</t>
+    <t xml:space="preserve">Estimativa, cotar (ambiente com poeira e calor)</t>
   </si>
   <si>
     <t xml:space="preserve">P17</t>
@@ -732,7 +732,7 @@
     <t xml:space="preserve">Canaleta / perfil de fixação dos módulos (por metro)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa (canaleta PVC 20×10 mm em barra de 2 m) — cotar</t>
+    <t xml:space="preserve">Estimativa (canaleta PVC 20×10 mm em barra de 2 m), cotar</t>
   </si>
   <si>
     <t xml:space="preserve">P19</t>
@@ -747,13 +747,13 @@
     <t xml:space="preserve">Switch 24 portas Gigabit TP-Link TL-SG1024DE</t>
   </si>
   <si>
-    <t xml:space="preserve">KaBuM — 23/10/2026 (Pix)</t>
+    <t xml:space="preserve">KaBuM, 23/10/2026 (Pix)</t>
   </si>
   <si>
     <t xml:space="preserve">P21</t>
   </si>
   <si>
-    <t xml:space="preserve">Fita LED endereçável WS2812 — guia de coluna (por LED) [opcional]</t>
+    <t xml:space="preserve">Fita LED endereçável WS2812, guia de coluna (por LED) [opcional]</t>
   </si>
   <si>
     <t xml:space="preserve">LED</t>
@@ -765,7 +765,7 @@
     <t xml:space="preserve">Tag NFC NTAG213 adesiva 13,56 MHz</t>
   </si>
   <si>
-    <t xml:space="preserve">Loja RFID — lote 100 un R$ 237,41 à vista — 23/10/2026</t>
+    <t xml:space="preserve">Loja RFID, lote 100 un R$ 237,41 à vista, 23/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">P23</t>
@@ -780,7 +780,7 @@
     <t xml:space="preserve">ESP32-C3 Super Mini (pulseira)</t>
   </si>
   <si>
-    <t xml:space="preserve">Usinainfo — 23/10/2026 (Pix)</t>
+    <t xml:space="preserve">Usinainfo, 23/10/2026 (Pix)</t>
   </si>
   <si>
     <t xml:space="preserve">P25</t>
@@ -789,7 +789,7 @@
     <t xml:space="preserve">Módulo leitor NFC PN532 (43×40 mm, com cartão e chaveiro)</t>
   </si>
   <si>
-    <t xml:space="preserve">MakerHero — Kit Módulo Leitor RFID NFC PN532 — 23/10/2026 (Pix)</t>
+    <t xml:space="preserve">MakerHero, Kit Módulo Leitor RFID NFC PN532, 23/10/2026 (Pix)</t>
   </si>
   <si>
     <t xml:space="preserve">P26</t>
@@ -807,7 +807,7 @@
     <t xml:space="preserve">P28</t>
   </si>
   <si>
-    <t xml:space="preserve">Display LCD 20×4 I2C (painel da estação — Arq. B2)</t>
+    <t xml:space="preserve">Display LCD 20×4 I2C (painel da estação, Arq. B2)</t>
   </si>
   <si>
     <t xml:space="preserve">P29</t>
@@ -816,7 +816,7 @@
     <t xml:space="preserve">Módulo PTL comercial 3 dígitos + botão (RS-485)</t>
   </si>
   <si>
-    <t xml:space="preserve">Alibaba — Sophia T-P3: US$ 32 (1-299 un) / US$ 28 (300+) — 23/10/2026; média US$ 30</t>
+    <t xml:space="preserve">Alibaba, Sophia T-P3: US$ 32 (1-299 un) / US$ 28 (300+), 23/10/2026; média US$ 30</t>
   </si>
   <si>
     <t xml:space="preserve">P30</t>
@@ -825,7 +825,7 @@
     <t xml:space="preserve">Módulo PTL comercial endereço + quantidade (display alfanumérico)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa (não há preço público) — solicitar cotação a fornecedores</t>
+    <t xml:space="preserve">Estimativa (não há preço público), solicitar cotação a fornecedores</t>
   </si>
   <si>
     <t xml:space="preserve">P31</t>
@@ -834,13 +834,13 @@
     <t xml:space="preserve">Controlador/gateway PTL comercial por estação</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa (não há preço público) — solicitar cotação</t>
+    <t xml:space="preserve">Estimativa (não há preço público), solicitar cotação</t>
   </si>
   <si>
     <t xml:space="preserve">P32</t>
   </si>
   <si>
-    <t xml:space="preserve">PCB própria montada por EMS — Módulo Q (MCU + display 0,56" + botão + 2× RJ45)</t>
+    <t xml:space="preserve">PCB própria montada por EMS, Módulo Q (MCU + display 0,56" + botão + 2× RJ45)</t>
   </si>
   <si>
     <t xml:space="preserve">Estimativa com base na tabela de montagem JLCPCB (jlcpcb.com/help/article/pcb-assembly-price) + componentes</t>
@@ -849,7 +849,7 @@
     <t xml:space="preserve">P33</t>
   </si>
   <si>
-    <t xml:space="preserve">PCB própria montada por EMS — Módulo E+Q</t>
+    <t xml:space="preserve">PCB própria montada por EMS, Módulo E+Q</t>
   </si>
   <si>
     <t xml:space="preserve">Estimativa (idem)</t>
@@ -858,7 +858,7 @@
     <t xml:space="preserve">P34</t>
   </si>
   <si>
-    <t xml:space="preserve">PCB própria montada por EMS — Concentrador (MCU + Ethernet + 2× RS-485)</t>
+    <t xml:space="preserve">PCB própria montada por EMS, Concentrador (MCU + Ethernet + 2× RS-485)</t>
   </si>
   <si>
     <t xml:space="preserve">P35</t>
@@ -870,25 +870,25 @@
     <t xml:space="preserve">projeto</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa — solicitar orçamento a design house</t>
+    <t xml:space="preserve">Estimativa, solicitar orçamento a design house</t>
   </si>
   <si>
     <t xml:space="preserve">P36</t>
   </si>
   <si>
-    <t xml:space="preserve">Leitor RFID UHF de pulso comercial (FEIG HyWEAR Compact) — referência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">atlasRFIDstore — US$ 997 — 22/10/2026 (UHF; não lê tags NFC)</t>
+    <t xml:space="preserve">Leitor RFID UHF de pulso comercial (FEIG HyWEAR Compact), referência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atlasRFIDstore, US$ 997, 22/10/2026 (UHF; não lê tags NFC)</t>
   </si>
   <si>
     <t xml:space="preserve">P37</t>
   </si>
   <si>
-    <t xml:space="preserve">Leitor HF/NFC fixo industrial (USB/RS-232) — alternativa comercial ao PN532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimativa — cotar (ex.: ACS ACR122U ou similar)</t>
+    <t xml:space="preserve">Leitor HF/NFC fixo industrial (USB/RS-232), alternativa comercial ao PN532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimativa, cotar (ex.: ACS ACR122U ou similar)</t>
   </si>
   <si>
     <t xml:space="preserve">Conjunto</t>
@@ -906,49 +906,49 @@
     <t xml:space="preserve">Módulo Q</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Módulo Q</t>
+    <t xml:space="preserve">Custo unitário, Módulo Q</t>
   </si>
   <si>
     <t xml:space="preserve">Nó de coluna</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Nó de coluna</t>
+    <t xml:space="preserve">Custo unitário, Nó de coluna</t>
   </si>
   <si>
     <t xml:space="preserve">Módulo E+Q</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Módulo E+Q</t>
+    <t xml:space="preserve">Custo unitário, Módulo E+Q</t>
   </si>
   <si>
     <t xml:space="preserve">Concentrador 12 V</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Concentrador 12 V</t>
+    <t xml:space="preserve">Custo unitário, Concentrador 12 V</t>
   </si>
   <si>
     <t xml:space="preserve">Concentrador 5 V</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Concentrador 5 V</t>
+    <t xml:space="preserve">Custo unitário, Concentrador 5 V</t>
   </si>
   <si>
     <t xml:space="preserve">Pulseira RFID (B1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Pulseira RFID (B1)</t>
+    <t xml:space="preserve">Custo unitário, Pulseira RFID (B1)</t>
   </si>
   <si>
     <t xml:space="preserve">Leitor fixo + painel (B2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Leitor fixo + painel (B2)</t>
+    <t xml:space="preserve">Custo unitário, Leitor fixo + painel (B2)</t>
   </si>
   <si>
     <t xml:space="preserve">Tag por caixa (B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo unitário — Tag por caixa (B)</t>
+    <t xml:space="preserve">Custo unitário, Tag por caixa (B)</t>
   </si>
   <si>
     <t xml:space="preserve">Variante 5 V: os módulos e nós não usam regulador step-down (P08); o custo é descontado na aba A-Interno.</t>
@@ -969,7 +969,7 @@
     <t xml:space="preserve">Total completo (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Arquitetura A — produção e montagem interna (12 V)</t>
+    <t xml:space="preserve">Arquitetura A, produção e montagem interna (12 V)</t>
   </si>
   <si>
     <t xml:space="preserve">Módulos Q (alto giro 0-3)</t>
@@ -1029,7 +1029,7 @@
     <t xml:space="preserve">estações ÷ portas por switch (arredondado para cima)</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBTOTAL PEÇAS — Arquitetura A (12 V)</t>
+    <t xml:space="preserve">SUBTOTAL PEÇAS, Arquitetura A (12 V)</t>
   </si>
   <si>
     <t xml:space="preserve">Mão de obra interna</t>
@@ -1068,7 +1068,7 @@
     <t xml:space="preserve">SUBTOTAL MÃO DE OBRA</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL — Arquitetura A interna (peças + mão de obra)</t>
+    <t xml:space="preserve">TOTAL, Arquitetura A interna (peças + mão de obra)</t>
   </si>
   <si>
     <t xml:space="preserve">Variante 5 V (peças)</t>
@@ -1089,10 +1089,10 @@
     <t xml:space="preserve">(+) Cabo de força extra para injeção de 5 V (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBTOTAL PEÇAS — variante 5 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opcional — guia de coluna no baixo giro (1 LED por prédio do fundo)</t>
+    <t xml:space="preserve">SUBTOTAL PEÇAS, variante 5 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcional, guia de coluna no baixo giro (1 LED por prédio do fundo)</t>
   </si>
   <si>
     <t xml:space="preserve">LEDs guia de coluna</t>
@@ -1101,16 +1101,16 @@
     <t xml:space="preserve">prédios do fundo × (1 + reserva)</t>
   </si>
   <si>
-    <t xml:space="preserve">T1 — Placas próprias fabricadas e montadas por EMS (cada módulo com seu microcontrolador)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Módulo Q — PCB montada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Módulo E+Q — PCB montada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrador — PCB montada + fonte + gabinete</t>
+    <t xml:space="preserve">T1, Placas próprias fabricadas e montadas por EMS (cada módulo com seu microcontrolador)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Módulo Q, PCB montada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Módulo E+Q, PCB montada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrador, PCB montada + fonte + gabinete</t>
   </si>
   <si>
     <t xml:space="preserve">estações × (1 + reserva)</t>
@@ -1140,10 +1140,10 @@
     <t xml:space="preserve">estações × (h instalação + h testes)</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL T1 — PCB própria (EMS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T2 — Sistema PTL comercial importado (hardware pronto; software de integração continua interno)</t>
+    <t xml:space="preserve">TOTAL T1, PCB própria (EMS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2, Sistema PTL comercial importado (hardware pronto; software de integração continua interno)</t>
   </si>
   <si>
     <t xml:space="preserve">Módulos PTL 3 dígitos (alto giro 0-3)</t>
@@ -1164,7 +1164,7 @@
     <t xml:space="preserve">módulos em cadeia</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL T2 — PTL comercial importado</t>
+    <t xml:space="preserve">TOTAL T2, PTL comercial importado</t>
   </si>
   <si>
     <t xml:space="preserve">Valores em US$ convertidos por câmbio × fator de importação (aba Premissas). Itens de PTL comercial sem preço público devem ser cotados com fornecedores (ex.: ATOP, Aioi, fornecedores nacionais).</t>
@@ -1173,7 +1173,7 @@
     <t xml:space="preserve">Arquitetura B = infraestrutura de displays da Arquitetura A + identificação da caixa por RFID</t>
   </si>
   <si>
-    <t xml:space="preserve">Infraestrutura de displays (Arquitetura A interna — peças + mão de obra)</t>
+    <t xml:space="preserve">Infraestrutura de displays (Arquitetura A interna, peças + mão de obra)</t>
   </si>
   <si>
     <t xml:space="preserve">aba A-Interno</t>
@@ -1191,7 +1191,7 @@
     <t xml:space="preserve">30 s por caixa</t>
   </si>
   <si>
-    <t xml:space="preserve">B1 — Pulseira NFC (montagem própria)</t>
+    <t xml:space="preserve">B1, Pulseira NFC (montagem própria)</t>
   </si>
   <si>
     <t xml:space="preserve">Pulseiras NFC (ESP32-C3 + PN532 + bateria)</t>
@@ -1206,10 +1206,10 @@
     <t xml:space="preserve">1,5 h por pulseira</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL B1 — displays + tags + pulseiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2 — Leitor fixo na estação + painel (sem item no corpo do operador)</t>
+    <t xml:space="preserve">TOTAL B1, displays + tags + pulseiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2, Leitor fixo na estação + painel (sem item no corpo do operador)</t>
   </si>
   <si>
     <t xml:space="preserve">Leitor PN532 + LCD 20×4 + botão Fechar</t>
@@ -1224,13 +1224,13 @@
     <t xml:space="preserve">2 h por estação</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL B2 — displays + tags + leitor fixo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referência de mercado — leitor de pulso comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEIG HyWEAR (UHF) por operador — não lê NFC; exigiria tags UHF</t>
+    <t xml:space="preserve">TOTAL B2, displays + tags + leitor fixo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referência de mercado, leitor de pulso comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FEIG HyWEAR (UHF) por operador, não lê NFC; exigiria tags UHF</t>
   </si>
   <si>
     <t xml:space="preserve">Coletores MovFast já existentes não entram no custo (Arquitetura A). Na Arquitetura B eles deixam de ser necessários na separação, mas continuam disponíveis para as demais operações.</t>
@@ -1272,7 +1272,7 @@
     <t xml:space="preserve">Consulta da caixa e, se possível, liberação para a próxima estação</t>
   </si>
   <si>
-    <t xml:space="preserve">App coletor Android (A1 — app próprio)</t>
+    <t xml:space="preserve">App coletor Android (A1, app próprio)</t>
   </si>
   <si>
     <t xml:space="preserve">A</t>
@@ -1326,13 +1326,13 @@
     <t xml:space="preserve">Operação, manutenção e suporte</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL — Arquitetura A com app próprio (sem tela WMS e sem itens só da B)</t>
+    <t xml:space="preserve">TOTAL, Arquitetura A com app próprio (sem tela WMS e sem itens só da B)</t>
   </si>
   <si>
     <t xml:space="preserve">Com a tela no WMS (A2) no lugar do app, troque 160 h por 80 h.</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL — Arquitetura B</t>
+    <t xml:space="preserve">TOTAL, Arquitetura B</t>
   </si>
 </sst>
 </file>
@@ -2065,7 +2065,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
         <v>23</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
         <v>258</v>
       </c>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C2" s="32" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B2,Preços!$A:$A,0))</f>
-        <v>Display 7 segmentos 4 dígitos TM1637 (usa 3 dígitos — quantidade)</v>
+        <v>Display 7 segmentos 4 dígitos TM1637 (usa 3 dígitos, quantidade)</v>
       </c>
       <c r="D2" s="14" t="n">
         <v>1</v>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="C19" s="32" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B19,Preços!$A:$A,0))</f>
-        <v>Display 7 segmentos 4 dígitos TM1637 (usa 3 dígitos — quantidade)</v>
+        <v>Display 7 segmentos 4 dígitos TM1637 (usa 3 dígitos, quantidade)</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>1</v>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C40" s="32" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B40,Preços!$A:$A,0))</f>
-        <v>Fonte Mean Well LRS-150-5 (5 V / 26 A) — variante 5 V</v>
+        <v>Fonte Mean Well LRS-150-5 (5 V / 26 A), variante 5 V</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>1</v>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="C53" s="32" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B53,Preços!$A:$A,0))</f>
-        <v>Display LCD 20×4 I2C (painel da estação — Arq. B2)</v>
+        <v>Display LCD 20×4 I2C (painel da estação, Arq. B2)</v>
       </c>
       <c r="D53" s="14" t="n">
         <v>1</v>

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="549">
   <si>
     <t xml:space="preserve">Orçamento do projeto Pick-to-Light (flow rack)</t>
   </si>
@@ -109,7 +109,10 @@
     <t xml:space="preserve">O QUE MUDOU NA REVISÃO DE 26/10/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">• Canaleta calculada pelo layout real de cada estação (frente do alto giro + descidas por prédio + corredor do baixo giro), no lugar de 24 m fixos por estação (média passou para cerca de 42 m).</t>
+    <t xml:space="preserve">• Canaleta calculada pelo layout real de cada estação (frente do alto giro + descidas por prédio + 2 lados do corredor + travessia), com as medidas do desenho de 26/10/2026: estação de 2,5 m, corredor de 1,2 m, prateleiras de 50 cm × 2 m (cerca de 27 m por estação).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Concentrador atrás da estação: travessia de 6 m por cima das esteiras até o corredor.</t>
   </si>
   <si>
     <t xml:space="preserve">• Barramento: 1 cabo por nó/módulo E+Q + cabo de saída das 2 portas do concentrador (antes: +2 segmentos genéricos).</t>
@@ -442,13 +445,13 @@
     <t xml:space="preserve">Cabo de cada saída do concentrador até o 1º equipamento</t>
   </si>
   <si>
-    <t xml:space="preserve">2 saídas por estação</t>
+    <t xml:space="preserve">Média das 2 saídas: alto giro ≈ 2 m (logo atrás) e baixo giro ≈ 10 m (por cima das esteiras)</t>
   </si>
   <si>
     <t xml:space="preserve">Largura de um prédio do alto giro</t>
   </si>
   <si>
-    <t xml:space="preserve">Medida usada no layout/simulador</t>
+    <t xml:space="preserve">Desenho de 26/10/2026: 2,5 m de alto giro por estação (10 prédios)</t>
   </si>
   <si>
     <t xml:space="preserve">Linhas horizontais de canaleta na frente do alto giro</t>
@@ -466,13 +469,16 @@
     <t xml:space="preserve">Do nó até os módulos Q dos andares 0-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Largura de um prédio do baixo giro (corredor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 linha de canaleta na altura dos olhos ao longo de cada lado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travessia por estação (frente → corredor → concentrador)</t>
+    <t xml:space="preserve">Comprimento de prateleira por lado do corredor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desenho de 26/10/2026: prateleiras de 50 cm × 2 m; 1 linha de canaleta na altura dos olhos em cada lado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travessia por estação (concentrador atrás → por cima das esteiras → corredor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrador fica atrás da estação, do outro lado do alto giro</t>
   </si>
   <si>
     <t xml:space="preserve">Cabo de rede do switch até a estação</t>
@@ -1271,7 +1277,7 @@
     <t xml:space="preserve">Canaleta / perfil de fixação (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">prédios alto giro × (largura × linhas + descida) + prédios baixo giro × largura + travessia</t>
+    <t xml:space="preserve">prédios alto giro × (largura × linhas + descida) + 2 lados × corredor + travessia, por estação</t>
   </si>
   <si>
     <t xml:space="preserve">Fixações diversas</t>
@@ -1641,6 +1647,12 @@
   </si>
   <si>
     <t xml:space="preserve">Status das estações, módulos com falha, produtividade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface de controle: qual LED falhou + cadastro de LED por endereço (tela + botão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnóstico no firmware (sem resposta, display sem ACK, botão travado), modo cadastro e tabela ptl_mapa_led</t>
   </si>
   <si>
     <t xml:space="preserve">Implantação do servidor (VM, broker MQTT, backup, monitoração)</t>
@@ -2268,7 +2280,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B42"/>
+  <dimension ref="B2:B43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2427,12 +2439,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2462,14 +2474,19 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2488,7 +2505,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -2500,27 +2517,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C2" s="20" t="n">
         <v>240</v>
@@ -2530,15 +2547,15 @@
         <v>24907.8773006135</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>516</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>514</v>
       </c>
       <c r="C3" s="20" t="n">
         <v>120</v>
@@ -2548,15 +2565,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C4" s="20" t="n">
         <v>60</v>
@@ -2566,15 +2583,15 @@
         <v>6226.96932515337</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>160</v>
@@ -2584,15 +2601,15 @@
         <v>16605.2515337423</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>80</v>
@@ -2602,15 +2619,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>120</v>
@@ -2620,15 +2637,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>100</v>
@@ -2638,15 +2655,15 @@
         <v>10378.282208589</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>80</v>
@@ -2656,15 +2673,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>120</v>
@@ -2674,98 +2691,116 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C11" s="20" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D11" s="11" t="n">
         <f aca="false">C11*Premissas!$B$10</f>
-        <v>2490.78773006135</v>
+        <v>4151.31288343558</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D12" s="11" t="n">
         <f aca="false">C12*Premissas!$B$10</f>
-        <v>12453.9386503067</v>
+        <v>2490.78773006135</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C13" s="20" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D13" s="11" t="n">
         <f aca="false">C13*Premissas!$B$10</f>
+        <v>12453.9386503067</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <f aca="false">C14*Premissas!$B$10</f>
         <v>4151.31288343558</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>541</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="42" t="n">
-        <f aca="false">SUMIF(B2:B13,"A e B",C2:C13)+SUMIF(B2:B13,"A",C2:C13)</f>
-        <v>1104</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <f aca="false">C14*Premissas!$B$10</f>
-        <v>114576.235582822</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>542</v>
+      <c r="E14" s="9" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="42" t="n">
-        <f aca="false">SUMIF(B2:B13,"A e B",C2:C13)+SUMIF(B2:B13,"B",C2:C13)</f>
-        <v>1024</v>
+        <f aca="false">SUMIF(B2:B14,"A e B",C2:C14)+SUMIF(B2:B14,"A",C2:C14)</f>
+        <v>1144</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">C15*Premissas!$B$10</f>
-        <v>106273.609815951</v>
-      </c>
-      <c r="E15" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>544</v>
+        <v>118727.548466258</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="42" t="n">
+        <f aca="false">SUMIF(B2:B14,"A e B",C2:C14)+SUMIF(B2:B14,"B",C2:C14)</f>
+        <v>1064</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <f aca="false">C16*Premissas!$B$10</f>
+        <v>110424.922699387</v>
+      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -2796,208 +2831,208 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">'A-Interno'!F20</f>
-        <v>16706.6746879303</v>
+        <v>16430.7346879303</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">'A-Interno'!G20</f>
-        <v>266039.626644836</v>
+        <v>260373.406644836</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/Estações!$O$43</f>
-        <v>6650.9906661209</v>
+        <v>6509.3351661209</v>
       </c>
       <c r="F4" s="11" t="n">
         <f aca="false">D4*(1+Premissas!$B$28)</f>
-        <v>292643.58930932</v>
+        <v>286410.74730932</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">'A-Interno'!F39</f>
-        <v>16823.7206879303</v>
+        <v>16547.7806879303</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">'A-Interno'!G39</f>
-        <v>268636.226644836</v>
+        <v>262970.006644836</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/Estações!$O$43</f>
-        <v>6715.9056661209</v>
+        <v>6574.2501661209</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">D5*(1+Premissas!$B$28)</f>
-        <v>295499.84930932</v>
+        <v>289267.00730932</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">'A-Interno'!F33</f>
-        <v>22204.0874555377</v>
+        <v>21805.7508008138</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">'A-Interno'!G33</f>
-        <v>364093.924199192</v>
+        <v>355914.381111094</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/Estações!$O$43</f>
-        <v>9102.3481049798</v>
+        <v>8897.85952777734</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">D6*(1+Premissas!$B$28)</f>
-        <v>400503.316619111</v>
+        <v>391505.819222203</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">'A-Terceiros'!F13</f>
-        <v>38858.5059273539</v>
+        <v>38473.30927263</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">'A-Terceiros'!G13</f>
-        <v>412582.153955925</v>
+        <v>404672.430867827</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/Estações!$O$43</f>
-        <v>10314.5538488981</v>
+        <v>10116.8107716957</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">D7*(1+Premissas!$B$28)</f>
-        <v>453840.369351517</v>
+        <v>445139.673954609</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">'A-Terceiros'!F25</f>
-        <v>50447.3816806668</v>
+        <v>50062.1850259429</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">'A-Terceiros'!G25</f>
-        <v>936605.026199483</v>
+        <v>928695.303111385</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">D8/Estações!$O$43</f>
-        <v>23415.1256549871</v>
+        <v>23217.3825777846</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">D8*(1+Premissas!$B$28)</f>
-        <v>1030265.52881943</v>
+        <v>1021564.83342252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">'B-RFID'!F11</f>
-        <v>23964.0385802821</v>
+        <v>23565.7019255581</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">'B-RFID'!G11</f>
-        <v>397133.716755429</v>
+        <v>388954.173667331</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/Estações!$O$43</f>
-        <v>9928.34291888573</v>
+        <v>9723.85434168327</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">D9*(1+Premissas!$B$28)</f>
-        <v>436847.088430972</v>
+        <v>427849.591034064</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">'B-RFID'!F16</f>
-        <v>23542.4901723569</v>
+        <v>23144.153517633</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'B-RFID'!G16</f>
-        <v>390861.978535576</v>
+        <v>382682.435447478</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">D10/Estações!$O$43</f>
-        <v>9771.5494633894</v>
+        <v>9567.06088618694</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">D10*(1+Premissas!$B$28)</f>
-        <v>429948.176389134</v>
+        <v>420950.678992226</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">'A-Interno'!F42</f>
@@ -3018,68 +3053,68 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="13" t="str">
-        <f aca="false">"Horas: "&amp;TEXT(Software!C14,"#,##0")</f>
-        <v>Horas: 1,104</v>
+        <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
+        <v>Horas: 1,144</v>
       </c>
       <c r="D14" s="10" t="n">
-        <f aca="false">Software!D14</f>
-        <v>114576.235582822</v>
+        <f aca="false">Software!D15</f>
+        <v>118727.548466258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="13" t="str">
-        <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
-        <v>Horas: 1,024</v>
+        <f aca="false">"Horas: "&amp;TEXT(Software!C16,"#,##0")</f>
+        <v>Horas: 1,064</v>
       </c>
       <c r="D15" s="10" t="n">
-        <f aca="false">Software!D15</f>
-        <v>106273.609815951</v>
+        <f aca="false">Software!D16</f>
+        <v>110424.922699387</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="17" t="n">
         <f aca="false">F6+D14</f>
-        <v>515079.552201933</v>
+        <v>510233.367688461</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17" t="n">
         <f aca="false">F10+D15</f>
-        <v>536221.786205085</v>
+        <v>531375.601691612</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3109,621 +3144,621 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>5.0371</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="19" t="n">
         <v>1.9</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>2846.84</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>8458.3</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>2009.59</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>163</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">$B$4*$B$7/$B$8</f>
         <v>34.9305521472393</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">$B$5*$B$7/$B$8</f>
         <v>103.78282208589</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">$B$6*$B$7/$B$8</f>
         <v>24.6575460122699</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>0.75</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B14" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="20" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>0.15</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>0.35</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>0.08</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>16</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B26" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B27" s="22" t="n">
         <v>0.05</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B28" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B29" s="20" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="19" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" s="19" t="n">
         <v>1.2</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B34" s="19" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B35" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>50</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B37" s="20" t="n">
         <v>22</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B38" s="20" t="n">
         <v>80</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B39" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B40" s="20" t="n">
         <v>5000</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B41" s="19" t="n">
         <v>2.2</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B42" s="20" t="n">
         <v>30</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B43" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B44" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3761,63 +3796,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E2" s="25" t="n">
         <v>131</v>
@@ -3857,16 +3892,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C3" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E3" s="25" t="n">
         <v>201</v>
@@ -3906,16 +3941,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E4" s="25" t="n">
         <v>209</v>
@@ -3955,16 +3990,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C5" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>209</v>
@@ -4004,16 +4039,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>209</v>
@@ -4053,16 +4088,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C7" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E7" s="25" t="n">
         <v>205</v>
@@ -4102,16 +4137,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>241</v>
@@ -4151,16 +4186,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E9" s="25" t="n">
         <v>237</v>
@@ -4200,16 +4235,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C10" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E10" s="25" t="n">
         <v>205</v>
@@ -4249,16 +4284,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C11" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E11" s="25" t="n">
         <v>209</v>
@@ -4298,16 +4333,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C12" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E12" s="25" t="n">
         <v>203</v>
@@ -4347,16 +4382,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C13" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E13" s="25" t="n">
         <v>209</v>
@@ -4396,16 +4431,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E14" s="25" t="n">
         <v>231</v>
@@ -4445,16 +4480,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E15" s="25" t="n">
         <v>237</v>
@@ -4494,16 +4529,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E16" s="25" t="n">
         <v>205</v>
@@ -4543,16 +4578,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E17" s="25" t="n">
         <v>209</v>
@@ -4592,16 +4627,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C18" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E18" s="25" t="n">
         <v>203</v>
@@ -4641,16 +4676,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C19" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E19" s="25" t="n">
         <v>209</v>
@@ -4690,16 +4725,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C20" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E20" s="25" t="n">
         <v>199</v>
@@ -4739,16 +4774,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E21" s="25" t="n">
         <v>43</v>
@@ -4788,16 +4823,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>176</v>
@@ -4837,16 +4872,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E23" s="25" t="n">
         <v>181</v>
@@ -4886,16 +4921,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="23" t="s">
-        <v>210</v>
-      </c>
       <c r="C24" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E24" s="25" t="n">
         <v>181</v>
@@ -4935,16 +4970,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C25" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E25" s="25" t="n">
         <v>181</v>
@@ -4984,16 +5019,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C26" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E26" s="25" t="n">
         <v>179</v>
@@ -5033,16 +5068,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C27" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E27" s="25" t="n">
         <v>181</v>
@@ -5082,16 +5117,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E28" s="25" t="n">
         <v>280</v>
@@ -5131,16 +5166,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E29" s="25" t="n">
         <v>277</v>
@@ -5180,16 +5215,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C30" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E30" s="25" t="n">
         <v>179</v>
@@ -5229,16 +5264,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C31" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>181</v>
@@ -5278,16 +5313,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C32" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>177</v>
@@ -5327,16 +5362,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C33" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>181</v>
@@ -5376,16 +5411,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>274</v>
@@ -5425,16 +5460,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E35" s="25" t="n">
         <v>277</v>
@@ -5474,16 +5509,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C36" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E36" s="25" t="n">
         <v>179</v>
@@ -5523,16 +5558,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C37" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E37" s="25" t="n">
         <v>181</v>
@@ -5572,16 +5607,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C38" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E38" s="25" t="n">
         <v>177</v>
@@ -5621,16 +5656,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C39" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E39" s="25" t="n">
         <v>181</v>
@@ -5670,16 +5705,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C40" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="E40" s="25" t="n">
         <v>173</v>
@@ -5719,16 +5754,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E41" s="25" t="n">
         <v>181</v>
@@ -5768,7 +5803,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D43" s="28" t="n">
         <f aca="false">COUNTA(A2:A41)</f>
@@ -5821,7 +5856,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D44" s="28" t="n">
         <f aca="false">COUNTIF(D2:D41,"S")</f>
@@ -5874,17 +5909,17 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -5923,120 +5958,120 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D2" s="30" t="n">
         <v>9.98</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D3" s="30" t="n">
         <v>20.17</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>39.9</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>8.9</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">E6*Premissas!$B$2*Premissas!$B$3</f>
@@ -6046,147 +6081,147 @@
         <v>12.5</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D7" s="30" t="n">
         <v>189.98</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>185</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D9" s="33" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>18</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D11" s="33" t="n">
         <v>2.5</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>0.8</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">1229.41/305</f>
@@ -6194,357 +6229,357 @@
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D14" s="33" t="n">
         <v>5</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D15" s="33" t="n">
         <v>15</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D16" s="33" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>90</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>45</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="33" t="n">
         <v>9</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D20" s="33" t="n">
         <v>40</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>769.32</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D22" s="33" t="n">
         <v>0.9</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D23" s="30" t="n">
         <v>2.37</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D24" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D25" s="30" t="n">
         <v>29.89</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D26" s="30" t="n">
         <v>42.65</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D27" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D28" s="33" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D29" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">E30*Premissas!$B$2*Premissas!$B$3</f>
@@ -6554,21 +6589,21 @@
         <v>30</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">E31*Premissas!$B$2*Premissas!$B$3</f>
@@ -6578,21 +6613,21 @@
         <v>65</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">E32*Premissas!$B$2*Premissas!$B$3</f>
@@ -6602,21 +6637,21 @@
         <v>220</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">E33*Premissas!$B$2*Premissas!$B$3</f>
@@ -6626,21 +6661,21 @@
         <v>9</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">E34*Premissas!$B$2*Premissas!$B$3</f>
@@ -6650,21 +6685,21 @@
         <v>22</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">E35*Premissas!$B$2*Premissas!$B$3</f>
@@ -6674,42 +6709,42 @@
         <v>35</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D36" s="33" t="n">
         <v>15000</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">E37*Premissas!$B$2*Premissas!$B$3</f>
@@ -6719,42 +6754,42 @@
         <v>997</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D38" s="33" t="n">
         <v>350</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">913.31/100</f>
@@ -6762,178 +6797,178 @@
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D40" s="33" t="n">
         <v>12</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D41" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D42" s="30" t="n">
         <v>285.99</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D43" s="33" t="n">
         <v>700</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D44" s="30" t="n">
         <v>368.1</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D45" s="33" t="n">
         <v>550</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D46" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D47" s="33" t="n">
         <v>350</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6964,30 +6999,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C2" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B2,Preços!$A:$A,0))</f>
@@ -7007,10 +7042,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C3" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B3,Preços!$A:$A,0))</f>
@@ -7030,10 +7065,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C4" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B4,Preços!$A:$A,0))</f>
@@ -7053,10 +7088,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C5" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B5,Preços!$A:$A,0))</f>
@@ -7076,10 +7111,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C6" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B6,Preços!$A:$A,0))</f>
@@ -7099,10 +7134,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C7" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B7,Preços!$A:$A,0))</f>
@@ -7122,7 +7157,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -7135,10 +7170,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C10" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B10,Preços!$A:$A,0))</f>
@@ -7158,10 +7193,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C11" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B11,Preços!$A:$A,0))</f>
@@ -7181,10 +7216,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C12" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B12,Preços!$A:$A,0))</f>
@@ -7204,10 +7239,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C13" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B13,Preços!$A:$A,0))</f>
@@ -7227,10 +7262,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C14" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B14,Preços!$A:$A,0))</f>
@@ -7250,10 +7285,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C15" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B15,Preços!$A:$A,0))</f>
@@ -7273,7 +7308,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -7286,10 +7321,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C18" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B18,Preços!$A:$A,0))</f>
@@ -7309,10 +7344,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C19" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B19,Preços!$A:$A,0))</f>
@@ -7332,10 +7367,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C20" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B20,Preços!$A:$A,0))</f>
@@ -7355,10 +7390,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C21" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B21,Preços!$A:$A,0))</f>
@@ -7378,10 +7413,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C22" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B22,Preços!$A:$A,0))</f>
@@ -7401,10 +7436,10 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C23" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B23,Preços!$A:$A,0))</f>
@@ -7424,10 +7459,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C24" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B24,Preços!$A:$A,0))</f>
@@ -7447,10 +7482,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C25" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B25,Preços!$A:$A,0))</f>
@@ -7470,10 +7505,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C26" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B26,Preços!$A:$A,0))</f>
@@ -7493,7 +7528,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -7506,10 +7541,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C29" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B29,Preços!$A:$A,0))</f>
@@ -7529,10 +7564,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C30" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B30,Preços!$A:$A,0))</f>
@@ -7552,10 +7587,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C31" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B31,Preços!$A:$A,0))</f>
@@ -7575,10 +7610,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C32" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B32,Preços!$A:$A,0))</f>
@@ -7598,10 +7633,10 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C33" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B33,Preços!$A:$A,0))</f>
@@ -7621,10 +7656,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C34" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B34,Preços!$A:$A,0))</f>
@@ -7644,10 +7679,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C35" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B35,Preços!$A:$A,0))</f>
@@ -7667,10 +7702,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C36" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B36,Preços!$A:$A,0))</f>
@@ -7690,10 +7725,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C37" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B37,Preços!$A:$A,0))</f>
@@ -7713,10 +7748,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C38" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B38,Preços!$A:$A,0))</f>
@@ -7736,7 +7771,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7749,10 +7784,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C41" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B41,Preços!$A:$A,0))</f>
@@ -7772,10 +7807,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C42" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B42,Preços!$A:$A,0))</f>
@@ -7795,10 +7830,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C43" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B43,Preços!$A:$A,0))</f>
@@ -7818,10 +7853,10 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C44" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B44,Preços!$A:$A,0))</f>
@@ -7841,10 +7876,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C45" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B45,Preços!$A:$A,0))</f>
@@ -7864,10 +7899,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C46" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B46,Preços!$A:$A,0))</f>
@@ -7887,10 +7922,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C47" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B47,Preços!$A:$A,0))</f>
@@ -7910,10 +7945,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C48" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B48,Preços!$A:$A,0))</f>
@@ -7933,10 +7968,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C49" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B49,Preços!$A:$A,0))</f>
@@ -7956,7 +7991,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -7969,10 +8004,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C52" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B52,Preços!$A:$A,0))</f>
@@ -7992,10 +8027,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C53" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B53,Preços!$A:$A,0))</f>
@@ -8015,10 +8050,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C54" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B54,Preços!$A:$A,0))</f>
@@ -8038,10 +8073,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C55" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B55,Preços!$A:$A,0))</f>
@@ -8061,7 +8096,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -8074,10 +8109,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C58" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B58,Preços!$A:$A,0))</f>
@@ -8097,10 +8132,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C59" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B59,Preços!$A:$A,0))</f>
@@ -8120,10 +8155,10 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C60" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B60,Preços!$A:$A,0))</f>
@@ -8143,10 +8178,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C61" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B61,Preços!$A:$A,0))</f>
@@ -8166,10 +8201,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C62" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B62,Preços!$A:$A,0))</f>
@@ -8189,10 +8224,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C63" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B63,Preços!$A:$A,0))</f>
@@ -8212,10 +8247,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C64" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B64,Preços!$A:$A,0))</f>
@@ -8235,10 +8270,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C65" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B65,Preços!$A:$A,0))</f>
@@ -8258,10 +8293,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C66" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B66,Preços!$A:$A,0))</f>
@@ -8281,10 +8316,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C67" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B67,Preços!$A:$A,0))</f>
@@ -8304,10 +8339,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C68" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B68,Preços!$A:$A,0))</f>
@@ -8327,7 +8362,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -8340,10 +8375,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C71" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B71,Preços!$A:$A,0))</f>
@@ -8363,10 +8398,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C72" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B72,Preços!$A:$A,0))</f>
@@ -8386,7 +8421,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -8399,17 +8434,17 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -8442,38 +8477,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -8498,10 +8533,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$K$44*(1+Premissas!$B$26),0)</f>
@@ -8526,10 +8561,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -8554,10 +8589,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -8582,10 +8617,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -8610,10 +8645,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">Estações!$N$44*2+Estações!$O$44*4</f>
@@ -8638,18 +8673,18 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C9" s="39" t="n">
-        <f aca="false">Estações!$K$44*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$L$44*Premissas!$B$34+Estações!$O$44*Premissas!$B$35</f>
-        <v>83.2</v>
+        <f aca="false">Estações!$K$44*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$O$44*2*Premissas!$B$34+Estações!$O$44*Premissas!$B$35</f>
+        <v>54</v>
       </c>
       <c r="D9" s="39" t="n">
-        <f aca="false">Estações!$K$43*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$L$43*Premissas!$B$34+Estações!$O$43*Premissas!$B$35</f>
-        <v>1679.6</v>
+        <f aca="false">Estações!$K$43*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$O$43*2*Premissas!$B$34+Estações!$O$43*Premissas!$B$35</f>
+        <v>1080</v>
       </c>
       <c r="E9" s="37" t="n">
         <f aca="false">Preços!$D$19</f>
@@ -8657,19 +8692,19 @@
       </c>
       <c r="F9" s="31" t="n">
         <f aca="false">C9*E9</f>
-        <v>748.8</v>
+        <v>486</v>
       </c>
       <c r="G9" s="31" t="n">
         <f aca="false">D9*E9</f>
-        <v>15116.4</v>
+        <v>9720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -8694,10 +8729,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$36</f>
@@ -8722,10 +8757,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44/Premissas!$B$37,0)</f>
@@ -8750,10 +8785,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">C12</f>
@@ -8778,10 +8813,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">C12</f>
@@ -8806,10 +8841,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">C12*Premissas!$B$38</f>
@@ -8834,10 +8869,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$39,0)</f>
@@ -8862,10 +8897,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">1</f>
@@ -8890,10 +8925,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">1</f>
@@ -8918,10 +8953,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -8931,16 +8966,16 @@
       </c>
       <c r="F19" s="31" t="n">
         <f aca="false">E19*SUM(F3:F18)</f>
-        <v>795.555937520492</v>
+        <v>782.415937520492</v>
       </c>
       <c r="G19" s="31" t="n">
         <f aca="false">E19*SUM(G3:G18)</f>
-        <v>12668.5536497541</v>
+        <v>12398.7336497541</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -8948,24 +8983,24 @@
       <c r="E20" s="16"/>
       <c r="F20" s="38" t="n">
         <f aca="false">SUM(F3:F19)</f>
-        <v>16706.6746879303</v>
+        <v>16430.7346879303</v>
       </c>
       <c r="G20" s="38" t="n">
         <f aca="false">SUM(G3:G19)</f>
-        <v>266039.626644836</v>
+        <v>260373.406644836</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">C3*Premissas!$B$12</f>
@@ -8990,10 +9025,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C4*Premissas!$B$13</f>
@@ -9018,10 +9053,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C25" s="21" t="n">
         <f aca="false">C5*Premissas!$B$14</f>
@@ -9046,10 +9081,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C26" s="21" t="n">
         <f aca="false">C6*Premissas!$B$15</f>
@@ -9074,18 +9109,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C27" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$K$44*Premissas!$B$18+Estações!$M$44*Premissas!$B$19+C9*Premissas!$B$20)*Premissas!$B$22</f>
-        <v>56.484</v>
+        <v>52.98</v>
       </c>
       <c r="D27" s="21" t="n">
         <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$K$43*Premissas!$B$18+Estações!$M$43*Premissas!$B$19+D9*Premissas!$B$20)*Premissas!$B$22</f>
-        <v>1134.177</v>
+        <v>1062.225</v>
       </c>
       <c r="E27" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9093,19 +9128,19 @@
       </c>
       <c r="F27" s="31" t="n">
         <f aca="false">C27*E27</f>
-        <v>1973.01730748466</v>
+        <v>1850.62065276074</v>
       </c>
       <c r="G27" s="31" t="n">
         <f aca="false">D27*E27</f>
-        <v>39617.4288426994</v>
+        <v>37104.1057546012</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$21*Premissas!$B$22</f>
@@ -9130,10 +9165,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$23*Premissas!$B$24</f>
@@ -9158,10 +9193,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C30" s="21" t="n">
         <f aca="false">Premissas!$B$25</f>
@@ -9186,30 +9221,30 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="41" t="n">
         <f aca="false">SUM(C23:C30)</f>
-        <v>159.734</v>
+        <v>156.23</v>
       </c>
       <c r="D31" s="41" t="n">
         <f aca="false">SUM(D23:D30)</f>
-        <v>2854.177</v>
+        <v>2782.225</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="38" t="n">
         <f aca="false">SUM(F23:F30)</f>
-        <v>5497.41276760736</v>
+        <v>5375.01611288344</v>
       </c>
       <c r="G31" s="38" t="n">
         <f aca="false">SUM(G23:G30)</f>
-        <v>98054.2975543558</v>
+        <v>95540.9744662577</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -9217,24 +9252,24 @@
       <c r="E33" s="16"/>
       <c r="F33" s="38" t="n">
         <f aca="false">F20+F31</f>
-        <v>22204.0874555377</v>
+        <v>21805.7508008138</v>
       </c>
       <c r="G33" s="38" t="n">
         <f aca="false">G20+G31</f>
-        <v>364093.924199192</v>
+        <v>355914.381111094</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C36" s="39" t="n">
         <f aca="false">-(C4+C5+C6)</f>
@@ -9259,10 +9294,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C37" s="39" t="n">
         <f aca="false">C6</f>
@@ -9287,10 +9322,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C38" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$42</f>
@@ -9315,7 +9350,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -9323,24 +9358,24 @@
       <c r="E39" s="16"/>
       <c r="F39" s="38" t="n">
         <f aca="false">F20+SUM(F36:F38)</f>
-        <v>16823.7206879303</v>
+        <v>16547.7806879303</v>
       </c>
       <c r="G39" s="38" t="n">
         <f aca="false">G20+SUM(G36:G38)</f>
-        <v>268636.226644836</v>
+        <v>262970.006644836</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C42" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$L$44*(1+Premissas!$B$26),0)</f>
@@ -9393,38 +9428,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9449,10 +9484,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -9477,10 +9512,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -9505,10 +9540,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -9533,10 +9568,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
@@ -9561,29 +9596,29 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="37" t="n">
         <f aca="false">SUM('A-Interno'!F9:F18)</f>
-        <v>4577.76344262295</v>
+        <v>4314.96344262295</v>
       </c>
       <c r="G8" s="37" t="n">
         <f aca="false">SUM('A-Interno'!G9:G18)</f>
-        <v>36783.8713114754</v>
+        <v>31387.4713114754</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">1</f>
@@ -9608,10 +9643,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">(C3+C4+C5)*Premissas!$B$44</f>
@@ -9636,18 +9671,18 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>60.984</v>
+        <v>57.48</v>
       </c>
       <c r="D11" s="21" t="n">
         <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>1224.177</v>
+        <v>1152.225</v>
       </c>
       <c r="E11" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9655,19 +9690,19 @@
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">C11*E11</f>
-        <v>2130.20479214724</v>
+        <v>2007.80813742331</v>
       </c>
       <c r="G11" s="31" t="n">
         <f aca="false">D11*E11</f>
-        <v>42761.1785359509</v>
+        <v>40247.8554478528</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -9683,7 +9718,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -9691,24 +9726,24 @@
       <c r="E13" s="16"/>
       <c r="F13" s="38" t="n">
         <f aca="false">SUM(F3:F12)</f>
-        <v>38858.5059273539</v>
+        <v>38473.30927263</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">SUM(G3:G12)</f>
-        <v>412582.153955925</v>
+        <v>404672.430867827</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9733,10 +9768,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -9761,10 +9796,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -9789,10 +9824,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C19" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -9817,10 +9852,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C20" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -9845,10 +9880,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C21" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
@@ -9873,37 +9908,37 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="37" t="n">
         <f aca="false">SUM('A-Interno'!F9:F18)</f>
-        <v>4577.76344262295</v>
+        <v>4314.96344262295</v>
       </c>
       <c r="G22" s="37" t="n">
         <f aca="false">SUM('A-Interno'!G9:G18)</f>
-        <v>36783.8713114754</v>
+        <v>31387.4713114754</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>60.984</v>
+        <v>57.48</v>
       </c>
       <c r="D23" s="21" t="n">
         <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>1224.177</v>
+        <v>1152.225</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9911,19 +9946,19 @@
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">C23*E23</f>
-        <v>2130.20479214724</v>
+        <v>2007.80813742331</v>
       </c>
       <c r="G23" s="31" t="n">
         <f aca="false">D23*E23</f>
-        <v>42761.1785359509</v>
+        <v>40247.8554478528</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -9939,7 +9974,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -9947,16 +9982,16 @@
       <c r="E25" s="16"/>
       <c r="F25" s="38" t="n">
         <f aca="false">SUM(F16:F24)</f>
-        <v>50447.3816806668</v>
+        <v>50062.1850259429</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">SUM(G16:G24)</f>
-        <v>936605.026199483</v>
+        <v>928695.303111385</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -9988,57 +10023,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="37" t="n">
         <f aca="false">'A-Interno'!F33</f>
-        <v>22204.0874555377</v>
+        <v>21805.7508008138</v>
       </c>
       <c r="G3" s="37" t="n">
         <f aca="false">'A-Interno'!G33</f>
-        <v>364093.924199192</v>
+        <v>355914.381111094</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Premissas!$B$40*Estações!$O$44/Estações!$O$43,0)</f>
@@ -10063,10 +10098,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">C4*30/3600</f>
@@ -10091,15 +10126,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$41,0)</f>
@@ -10124,10 +10159,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10152,10 +10187,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">C8*1.5</f>
@@ -10180,7 +10215,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -10188,24 +10223,24 @@
       <c r="E11" s="16"/>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F3:F5)+SUM(F8:F10)</f>
-        <v>23964.0385802821</v>
+        <v>23565.7019255581</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G3:G5)+SUM(G8:G10)</f>
-        <v>397133.716755429</v>
+        <v>388954.173667331</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10230,10 +10265,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">C14*2</f>
@@ -10258,7 +10293,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -10266,19 +10301,19 @@
       <c r="E16" s="16"/>
       <c r="F16" s="38" t="n">
         <f aca="false">SUM(F3:F5)+SUM(F14:F15)</f>
-        <v>23542.4901723569</v>
+        <v>23144.153517633</v>
       </c>
       <c r="G16" s="38" t="n">
         <f aca="false">SUM(G3:G5)+SUM(G14:G15)</f>
-        <v>390861.978535576</v>
+        <v>382682.435447478</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">C8</f>
@@ -10303,7 +10338,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="555">
   <si>
     <t xml:space="preserve">Orçamento do projeto Pick-to-Light (flow rack)</t>
   </si>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Módulo Q: display de QUANTIDADE (3 dígitos) + botão com LED, um por endereço de alto giro (andares 0 a 3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Módulo E+Q: display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (A4 e A5 em cada lado: 4 por estação) e em cada zona de baixo giro (4 zonas por lado do corredor, na altura dos olhos).</t>
+    <t xml:space="preserve">Módulo E+Q: display de ENDEREÇO (8 dígitos) + QUANTIDADE (3 dígitos) + botão; usado nos andares 4 e 5 do alto giro (2 zonas por estação: P001–P005 e P006–P010, por baixo da esteira de separação) e em cada zona de baixo giro (2 zonas por lado do corredor, na altura dos olhos).</t>
   </si>
   <si>
     <t xml:space="preserve">Nó de coluna: microcontrolador por coluna (prédio) do alto giro que liga até 4 Módulos Q ao barramento RS-485 (nos dados, nenhum prédio tem mais de 4 endereços nos andares 0-3).</t>
@@ -103,7 +103,10 @@
     <t xml:space="preserve">Concentrador: controlador da estação (Ethernet cabeada), recebe a caixa do serviço PTL e comanda os 2 barramentos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Zona de baixo giro: 4 zonas por lado do corredor, cada uma com 1 display E+Q na altura dos olhos (o prédio 015 entra na zona D1; esquinas têm zonas de 4 prédios).</t>
+    <t xml:space="preserve">Zona de baixo giro: 2 zonas por lado do corredor (cerca de 6 prédios cada), cada uma com 1 display E+Q na altura dos olhos (o prédio 015 entra na zona D1; esquinas têm zonas de 4 prédios).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinal de baixo giro: luz âmbar ao lado da posição de pega que acende quando a caixa tem itens no corredor.</t>
   </si>
   <si>
     <t xml:space="preserve">O QUE MUDOU NA REVISÃO DE 26/10/2026</t>
@@ -143,6 +146,9 @@
   </si>
   <si>
     <t xml:space="preserve">• Câmbio atualizado (fechamento de 23/10/2026) e contingência de 10% no Resumo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Ajuste de 26/10/2026 (tarde): 2 displays E+Q nos andares 4-5 (antes 4) e 2 zonas por lado no baixo giro (antes 4), o que reduz os módulos E+Q de 485 para 251; sinal luminoso de baixo giro por estação.</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo do orçamento, Pick-to-Light</t>
@@ -565,7 +571,7 @@
   </si>
   <si>
     <t xml:space="preserve">E+Q alto giro
-4-5 (A4/A5)</t>
+4-5 (2 zonas)</t>
   </si>
   <si>
     <t xml:space="preserve">Baixo giro
@@ -743,7 +749,7 @@
     <t xml:space="preserve">Coluna D (Piloto) = quantidade de estações nas linhas de total. Fonte: wms_endereco (cd_esteira 1 e 2), exportado em 23/10/2026; rua 90 (Marketing/Almoxarifado) desconsiderada.</t>
   </si>
   <si>
-    <t xml:space="preserve">Regras: Alto giro = prédios 001-010; andares 4-5 com 4 displays E+Q por estação (A4 e A5 nos lados 001-005 e 006-010). Baixo giro = demais prédios (corredor, 015 e esquinas): 4 zonas E+Q por lado do corredor; esquinas com zonas de 4 prédios.</t>
+    <t xml:space="preserve">Regras: Alto giro = prédios 001-010; andares 4-5 com 2 displays E+Q por estação (zonas 001-005 e 006-010). Baixo giro = demais prédios (corredor, 015 e esquinas): 2 zonas E+Q por lado do corredor; esquinas com zonas de 4 prédios.</t>
   </si>
   <si>
     <t xml:space="preserve">Segmentos de barramento = 1 cabo de entrada por nó e por módulo E+Q (ligação em cadeia nas 2 portas do concentrador).</t>
@@ -1151,6 +1157,12 @@
     <t xml:space="preserve">Estimativa, cotar com a manutenção predial</t>
   </si>
   <si>
+    <t xml:space="preserve">P47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinal luminoso de baixo giro (sinaleiro LED âmbar 12 V 22 mm + haste + transistor no nó)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Conjunto</t>
   </si>
   <si>
@@ -1284,6 +1296,12 @@
   </si>
   <si>
     <t xml:space="preserve">1 kit por estação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinal luminoso de baixo giro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 por estação, ao lado da posição de pega</t>
   </si>
   <si>
     <t xml:space="preserve">Cabo de rede até a estação (m)</t>
@@ -2280,7 +2298,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B43"/>
+  <dimension ref="B2:B45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2401,7 +2419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
         <v>21</v>
       </c>
@@ -2422,19 +2440,19 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3"/>
+      <c r="B30" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="4" t="s">
+      <c r="B31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2444,12 +2462,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
         <v>30</v>
       </c>
@@ -2479,14 +2497,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2517,27 +2545,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C2" s="20" t="n">
         <v>240</v>
@@ -2547,15 +2575,15 @@
         <v>24907.8773006135</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C3" s="20" t="n">
         <v>120</v>
@@ -2565,15 +2593,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C4" s="20" t="n">
         <v>60</v>
@@ -2583,15 +2611,15 @@
         <v>6226.96932515337</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>160</v>
@@ -2601,15 +2629,15 @@
         <v>16605.2515337423</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>80</v>
@@ -2619,15 +2647,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>120</v>
@@ -2637,15 +2665,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>100</v>
@@ -2655,15 +2683,15 @@
         <v>10378.282208589</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>80</v>
@@ -2673,15 +2701,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>120</v>
@@ -2691,15 +2719,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>40</v>
@@ -2709,15 +2737,15 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>24</v>
@@ -2727,15 +2755,15 @@
         <v>2490.78773006135</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>120</v>
@@ -2745,15 +2773,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>40</v>
@@ -2763,12 +2791,12 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="42" t="n">
@@ -2780,12 +2808,12 @@
         <v>118727.548466258</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="42" t="n">
@@ -2800,7 +2828,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -2831,215 +2859,215 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4" s="10" t="n">
-        <f aca="false">'A-Interno'!F20</f>
-        <v>16430.7346879303</v>
+        <f aca="false">'A-Interno'!F21</f>
+        <v>14510.6409649795</v>
       </c>
       <c r="D4" s="10" t="n">
-        <f aca="false">'A-Interno'!G20</f>
-        <v>260373.406644836</v>
+        <f aca="false">'A-Interno'!G21</f>
+        <v>222482.887797295</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/Estações!$O$43</f>
-        <v>6509.3351661209</v>
+        <v>5562.07219493238</v>
       </c>
       <c r="F4" s="11" t="n">
         <f aca="false">D4*(1+Premissas!$B$28)</f>
-        <v>286410.74730932</v>
+        <v>244731.176577025</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C5" s="10" t="n">
-        <f aca="false">'A-Interno'!F39</f>
-        <v>16547.7806879303</v>
+        <f aca="false">'A-Interno'!F40</f>
+        <v>14731.6869649795</v>
       </c>
       <c r="D5" s="10" t="n">
-        <f aca="false">'A-Interno'!G39</f>
-        <v>262970.006644836</v>
+        <f aca="false">'A-Interno'!G40</f>
+        <v>227135.487797295</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/Estações!$O$43</f>
-        <v>6574.2501661209</v>
+        <v>5678.38719493238</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">D5*(1+Premissas!$B$28)</f>
-        <v>289267.00730932</v>
+        <v>249849.036577025</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" s="10" t="n">
-        <f aca="false">'A-Interno'!F33</f>
-        <v>21805.7508008138</v>
+        <f aca="false">'A-Interno'!F34</f>
+        <v>19211.4974214212</v>
       </c>
       <c r="D6" s="10" t="n">
-        <f aca="false">'A-Interno'!G33</f>
-        <v>355914.381111094</v>
+        <f aca="false">'A-Interno'!G34</f>
+        <v>304755.492030424</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/Estações!$O$43</f>
-        <v>8897.85952777734</v>
+        <v>7618.8873007606</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">D6*(1+Premissas!$B$28)</f>
-        <v>391505.819222203</v>
+        <v>335231.041233466</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">'A-Terceiros'!F13</f>
-        <v>38473.30927263</v>
+        <v>34967.3662477864</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">'A-Terceiros'!G13</f>
-        <v>404672.430867827</v>
+        <v>335486.888460125</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/Estações!$O$43</f>
-        <v>10116.8107716957</v>
+        <v>8387.17221150312</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">D7*(1+Premissas!$B$28)</f>
-        <v>445139.673954609</v>
+        <v>369035.577306137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">'A-Terceiros'!F25</f>
-        <v>50062.1850259429</v>
+        <v>41680.7478088907</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">'A-Terceiros'!G25</f>
-        <v>928695.303111385</v>
+        <v>763124.990903867</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">D8/Estações!$O$43</f>
-        <v>23217.3825777846</v>
+        <v>19078.1247725967</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">D8*(1+Premissas!$B$28)</f>
-        <v>1021564.83342252</v>
+        <v>839437.489994254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">'B-RFID'!F11</f>
-        <v>23565.7019255581</v>
+        <v>20971.4485461656</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">'B-RFID'!G11</f>
-        <v>388954.173667331</v>
+        <v>337795.284586661</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/Estações!$O$43</f>
-        <v>9723.85434168327</v>
+        <v>8444.88211466653</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">D9*(1+Premissas!$B$28)</f>
-        <v>427849.591034064</v>
+        <v>371574.813045327</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">'B-RFID'!F16</f>
-        <v>23144.153517633</v>
+        <v>20549.9001382404</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">'B-RFID'!G16</f>
-        <v>382682.435447478</v>
+        <v>331523.546366808</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">D10/Estações!$O$43</f>
-        <v>9567.06088618694</v>
+        <v>8288.0886591702</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">D10*(1+Premissas!$B$28)</f>
-        <v>420950.678992226</v>
+        <v>364675.901003489</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" s="10" t="n">
-        <f aca="false">'A-Interno'!F42</f>
+        <f aca="false">'A-Interno'!F43</f>
         <v>49.5</v>
       </c>
       <c r="D11" s="10" t="n">
-        <f aca="false">'A-Interno'!G42</f>
+        <f aca="false">'A-Interno'!G43</f>
         <v>1016.1</v>
       </c>
       <c r="E11" s="11" t="n">
@@ -3053,12 +3081,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="13" t="str">
         <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
@@ -3071,7 +3099,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="13" t="str">
         <f aca="false">"Horas: "&amp;TEXT(Software!C16,"#,##0")</f>
@@ -3084,37 +3112,37 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="17" t="n">
         <f aca="false">F6+D14</f>
-        <v>510233.367688461</v>
+        <v>453958.589699724</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17" t="n">
         <f aca="false">F10+D15</f>
-        <v>531375.601691612</v>
+        <v>475100.823702875</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3144,621 +3172,621 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>5.0371</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B3" s="19" t="n">
         <v>1.9</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>2846.84</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>8458.3</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>2009.59</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>163</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">$B$4*$B$7/$B$8</f>
         <v>34.9305521472393</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">$B$5*$B$7/$B$8</f>
         <v>103.78282208589</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">$B$6*$B$7/$B$8</f>
         <v>24.6575460122699</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>0.75</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B14" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B16" s="20" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>0.15</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B18" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>0.35</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>0.08</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B22" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>16</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B26" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B27" s="22" t="n">
         <v>0.05</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B28" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B29" s="20" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B31" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B33" s="19" t="n">
         <v>1.2</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B34" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>50</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B37" s="20" t="n">
         <v>22</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B38" s="20" t="n">
         <v>80</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B39" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B40" s="20" t="n">
         <v>5000</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B41" s="19" t="n">
         <v>2.2</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B42" s="20" t="n">
         <v>30</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B43" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B44" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3796,63 +3824,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E2" s="25" t="n">
         <v>131</v>
@@ -3864,13 +3892,13 @@
         <v>20</v>
       </c>
       <c r="H2" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" s="25" t="n">
         <v>82</v>
       </c>
       <c r="J2" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" s="25" t="n">
         <v>10</v>
@@ -3880,11 +3908,11 @@
       </c>
       <c r="M2" s="26" t="n">
         <f aca="false">H2+J2</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N2" s="26" t="n">
         <f aca="false">K2+M2</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O2" s="25" t="n">
         <v>1</v>
@@ -3892,16 +3920,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C3" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E3" s="25" t="n">
         <v>201</v>
@@ -3913,13 +3941,13 @@
         <v>16</v>
       </c>
       <c r="H3" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" s="25" t="n">
         <v>156</v>
       </c>
       <c r="J3" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3" s="25" t="n">
         <v>10</v>
@@ -3929,11 +3957,11 @@
       </c>
       <c r="M3" s="26" t="n">
         <f aca="false">H3+J3</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N3" s="26" t="n">
         <f aca="false">K3+M3</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O3" s="25" t="n">
         <v>1</v>
@@ -3941,16 +3969,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E4" s="25" t="n">
         <v>209</v>
@@ -3962,13 +3990,13 @@
         <v>20</v>
       </c>
       <c r="H4" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J4" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K4" s="25" t="n">
         <v>10</v>
@@ -3978,11 +4006,11 @@
       </c>
       <c r="M4" s="26" t="n">
         <f aca="false">H4+J4</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N4" s="26" t="n">
         <f aca="false">K4+M4</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O4" s="25" t="n">
         <v>1</v>
@@ -3990,16 +4018,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C5" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>209</v>
@@ -4011,13 +4039,13 @@
         <v>20</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K5" s="25" t="n">
         <v>10</v>
@@ -4027,11 +4055,11 @@
       </c>
       <c r="M5" s="26" t="n">
         <f aca="false">H5+J5</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N5" s="26" t="n">
         <f aca="false">K5+M5</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O5" s="25" t="n">
         <v>1</v>
@@ -4039,16 +4067,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>209</v>
@@ -4060,13 +4088,13 @@
         <v>20</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J6" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K6" s="25" t="n">
         <v>10</v>
@@ -4076,11 +4104,11 @@
       </c>
       <c r="M6" s="26" t="n">
         <f aca="false">H6+J6</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N6" s="26" t="n">
         <f aca="false">K6+M6</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O6" s="25" t="n">
         <v>1</v>
@@ -4088,16 +4116,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C7" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E7" s="25" t="n">
         <v>205</v>
@@ -4109,13 +4137,13 @@
         <v>16</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" s="25" t="n">
         <v>10</v>
@@ -4125,11 +4153,11 @@
       </c>
       <c r="M7" s="26" t="n">
         <f aca="false">H7+J7</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N7" s="26" t="n">
         <f aca="false">K7+M7</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O7" s="25" t="n">
         <v>1</v>
@@ -4137,16 +4165,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>241</v>
@@ -4158,13 +4186,13 @@
         <v>20</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" s="25" t="n">
         <v>192</v>
       </c>
       <c r="J8" s="25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K8" s="25" t="n">
         <v>10</v>
@@ -4174,11 +4202,11 @@
       </c>
       <c r="M8" s="26" t="n">
         <f aca="false">H8+J8</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N8" s="26" t="n">
         <f aca="false">K8+M8</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O8" s="25" t="n">
         <v>1</v>
@@ -4186,16 +4214,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E9" s="25" t="n">
         <v>237</v>
@@ -4207,13 +4235,13 @@
         <v>20</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" s="25" t="n">
         <v>188</v>
       </c>
       <c r="J9" s="25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K9" s="25" t="n">
         <v>10</v>
@@ -4223,11 +4251,11 @@
       </c>
       <c r="M9" s="26" t="n">
         <f aca="false">H9+J9</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N9" s="26" t="n">
         <f aca="false">K9+M9</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O9" s="25" t="n">
         <v>1</v>
@@ -4235,16 +4263,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C10" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E10" s="25" t="n">
         <v>205</v>
@@ -4256,13 +4284,13 @@
         <v>16</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J10" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K10" s="25" t="n">
         <v>10</v>
@@ -4272,11 +4300,11 @@
       </c>
       <c r="M10" s="26" t="n">
         <f aca="false">H10+J10</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N10" s="26" t="n">
         <f aca="false">K10+M10</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O10" s="25" t="n">
         <v>1</v>
@@ -4284,16 +4312,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E11" s="25" t="n">
         <v>209</v>
@@ -4305,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K11" s="25" t="n">
         <v>10</v>
@@ -4321,11 +4349,11 @@
       </c>
       <c r="M11" s="26" t="n">
         <f aca="false">H11+J11</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N11" s="26" t="n">
         <f aca="false">K11+M11</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O11" s="25" t="n">
         <v>1</v>
@@ -4333,16 +4361,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C12" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E12" s="25" t="n">
         <v>203</v>
@@ -4354,13 +4382,13 @@
         <v>14</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J12" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K12" s="25" t="n">
         <v>10</v>
@@ -4370,11 +4398,11 @@
       </c>
       <c r="M12" s="26" t="n">
         <f aca="false">H12+J12</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N12" s="26" t="n">
         <f aca="false">K12+M12</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O12" s="25" t="n">
         <v>1</v>
@@ -4382,16 +4410,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C13" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E13" s="25" t="n">
         <v>209</v>
@@ -4403,13 +4431,13 @@
         <v>20</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J13" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K13" s="25" t="n">
         <v>10</v>
@@ -4419,11 +4447,11 @@
       </c>
       <c r="M13" s="26" t="n">
         <f aca="false">H13+J13</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N13" s="26" t="n">
         <f aca="false">K13+M13</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O13" s="25" t="n">
         <v>1</v>
@@ -4431,16 +4459,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E14" s="25" t="n">
         <v>231</v>
@@ -4452,13 +4480,13 @@
         <v>10</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" s="25" t="n">
         <v>192</v>
       </c>
       <c r="J14" s="25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K14" s="25" t="n">
         <v>10</v>
@@ -4468,11 +4496,11 @@
       </c>
       <c r="M14" s="26" t="n">
         <f aca="false">H14+J14</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N14" s="26" t="n">
         <f aca="false">K14+M14</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O14" s="25" t="n">
         <v>1</v>
@@ -4480,16 +4508,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E15" s="25" t="n">
         <v>237</v>
@@ -4501,13 +4529,13 @@
         <v>20</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" s="25" t="n">
         <v>188</v>
       </c>
       <c r="J15" s="25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K15" s="25" t="n">
         <v>10</v>
@@ -4517,11 +4545,11 @@
       </c>
       <c r="M15" s="26" t="n">
         <f aca="false">H15+J15</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N15" s="26" t="n">
         <f aca="false">K15+M15</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O15" s="25" t="n">
         <v>1</v>
@@ -4529,16 +4557,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E16" s="25" t="n">
         <v>205</v>
@@ -4550,13 +4578,13 @@
         <v>16</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J16" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K16" s="25" t="n">
         <v>10</v>
@@ -4566,11 +4594,11 @@
       </c>
       <c r="M16" s="26" t="n">
         <f aca="false">H16+J16</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N16" s="26" t="n">
         <f aca="false">K16+M16</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O16" s="25" t="n">
         <v>1</v>
@@ -4578,16 +4606,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C17" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E17" s="25" t="n">
         <v>209</v>
@@ -4599,13 +4627,13 @@
         <v>20</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J17" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K17" s="25" t="n">
         <v>10</v>
@@ -4615,11 +4643,11 @@
       </c>
       <c r="M17" s="26" t="n">
         <f aca="false">H17+J17</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N17" s="26" t="n">
         <f aca="false">K17+M17</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O17" s="25" t="n">
         <v>1</v>
@@ -4627,16 +4655,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C18" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E18" s="25" t="n">
         <v>203</v>
@@ -4648,13 +4676,13 @@
         <v>14</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J18" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K18" s="25" t="n">
         <v>10</v>
@@ -4664,11 +4692,11 @@
       </c>
       <c r="M18" s="26" t="n">
         <f aca="false">H18+J18</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N18" s="26" t="n">
         <f aca="false">K18+M18</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O18" s="25" t="n">
         <v>1</v>
@@ -4676,16 +4704,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C19" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E19" s="25" t="n">
         <v>209</v>
@@ -4697,13 +4725,13 @@
         <v>20</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J19" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K19" s="25" t="n">
         <v>10</v>
@@ -4713,11 +4741,11 @@
       </c>
       <c r="M19" s="26" t="n">
         <f aca="false">H19+J19</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N19" s="26" t="n">
         <f aca="false">K19+M19</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O19" s="25" t="n">
         <v>1</v>
@@ -4725,16 +4753,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C20" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E20" s="25" t="n">
         <v>199</v>
@@ -4746,13 +4774,13 @@
         <v>10</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" s="25" t="n">
         <v>160</v>
       </c>
       <c r="J20" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K20" s="25" t="n">
         <v>10</v>
@@ -4762,11 +4790,11 @@
       </c>
       <c r="M20" s="26" t="n">
         <f aca="false">H20+J20</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N20" s="26" t="n">
         <f aca="false">K20+M20</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O20" s="25" t="n">
         <v>1</v>
@@ -4774,16 +4802,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E21" s="25" t="n">
         <v>43</v>
@@ -4795,7 +4823,7 @@
         <v>10</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="25" t="n">
         <v>4</v>
@@ -4811,11 +4839,11 @@
       </c>
       <c r="M21" s="26" t="n">
         <f aca="false">H21+J21</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N21" s="26" t="n">
         <f aca="false">K21+M21</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O21" s="25" t="n">
         <v>1</v>
@@ -4823,16 +4851,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>176</v>
@@ -4844,13 +4872,13 @@
         <v>13</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" s="25" t="n">
         <v>128</v>
       </c>
       <c r="J22" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K22" s="25" t="n">
         <v>10</v>
@@ -4860,11 +4888,11 @@
       </c>
       <c r="M22" s="26" t="n">
         <f aca="false">H22+J22</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N22" s="26" t="n">
         <f aca="false">K22+M22</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O22" s="25" t="n">
         <v>1</v>
@@ -4872,16 +4900,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E23" s="25" t="n">
         <v>181</v>
@@ -4893,13 +4921,13 @@
         <v>15</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J23" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K23" s="25" t="n">
         <v>10</v>
@@ -4909,11 +4937,11 @@
       </c>
       <c r="M23" s="26" t="n">
         <f aca="false">H23+J23</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N23" s="26" t="n">
         <f aca="false">K23+M23</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O23" s="25" t="n">
         <v>1</v>
@@ -4921,16 +4949,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="B24" s="23" t="s">
-        <v>212</v>
-      </c>
       <c r="C24" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E24" s="25" t="n">
         <v>181</v>
@@ -4942,13 +4970,13 @@
         <v>15</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J24" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K24" s="25" t="n">
         <v>10</v>
@@ -4958,11 +4986,11 @@
       </c>
       <c r="M24" s="26" t="n">
         <f aca="false">H24+J24</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N24" s="26" t="n">
         <f aca="false">K24+M24</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O24" s="25" t="n">
         <v>1</v>
@@ -4970,16 +4998,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C25" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E25" s="25" t="n">
         <v>181</v>
@@ -4991,13 +5019,13 @@
         <v>15</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I25" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J25" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K25" s="25" t="n">
         <v>10</v>
@@ -5007,11 +5035,11 @@
       </c>
       <c r="M25" s="26" t="n">
         <f aca="false">H25+J25</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N25" s="26" t="n">
         <f aca="false">K25+M25</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O25" s="25" t="n">
         <v>1</v>
@@ -5019,16 +5047,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C26" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E26" s="25" t="n">
         <v>179</v>
@@ -5040,13 +5068,13 @@
         <v>13</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J26" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K26" s="25" t="n">
         <v>10</v>
@@ -5056,11 +5084,11 @@
       </c>
       <c r="M26" s="26" t="n">
         <f aca="false">H26+J26</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N26" s="26" t="n">
         <f aca="false">K26+M26</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O26" s="25" t="n">
         <v>1</v>
@@ -5068,16 +5096,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C27" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E27" s="25" t="n">
         <v>181</v>
@@ -5089,13 +5117,13 @@
         <v>15</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I27" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J27" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K27" s="25" t="n">
         <v>10</v>
@@ -5105,11 +5133,11 @@
       </c>
       <c r="M27" s="26" t="n">
         <f aca="false">H27+J27</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N27" s="26" t="n">
         <f aca="false">K27+M27</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O27" s="25" t="n">
         <v>1</v>
@@ -5117,16 +5145,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E28" s="25" t="n">
         <v>280</v>
@@ -5138,13 +5166,13 @@
         <v>15</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I28" s="25" t="n">
         <v>230</v>
       </c>
       <c r="J28" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K28" s="25" t="n">
         <v>10</v>
@@ -5154,11 +5182,11 @@
       </c>
       <c r="M28" s="26" t="n">
         <f aca="false">H28+J28</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N28" s="26" t="n">
         <f aca="false">K28+M28</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O28" s="25" t="n">
         <v>1</v>
@@ -5166,16 +5194,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E29" s="25" t="n">
         <v>277</v>
@@ -5187,13 +5215,13 @@
         <v>15</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I29" s="25" t="n">
         <v>227</v>
       </c>
       <c r="J29" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K29" s="25" t="n">
         <v>10</v>
@@ -5203,11 +5231,11 @@
       </c>
       <c r="M29" s="26" t="n">
         <f aca="false">H29+J29</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N29" s="26" t="n">
         <f aca="false">K29+M29</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O29" s="25" t="n">
         <v>1</v>
@@ -5215,16 +5243,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C30" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E30" s="25" t="n">
         <v>179</v>
@@ -5236,13 +5264,13 @@
         <v>13</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I30" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J30" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K30" s="25" t="n">
         <v>10</v>
@@ -5252,11 +5280,11 @@
       </c>
       <c r="M30" s="26" t="n">
         <f aca="false">H30+J30</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N30" s="26" t="n">
         <f aca="false">K30+M30</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O30" s="25" t="n">
         <v>1</v>
@@ -5264,16 +5292,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C31" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>181</v>
@@ -5285,13 +5313,13 @@
         <v>15</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J31" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K31" s="25" t="n">
         <v>10</v>
@@ -5301,11 +5329,11 @@
       </c>
       <c r="M31" s="26" t="n">
         <f aca="false">H31+J31</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N31" s="26" t="n">
         <f aca="false">K31+M31</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O31" s="25" t="n">
         <v>1</v>
@@ -5313,16 +5341,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C32" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>177</v>
@@ -5334,13 +5362,13 @@
         <v>11</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J32" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K32" s="25" t="n">
         <v>10</v>
@@ -5350,11 +5378,11 @@
       </c>
       <c r="M32" s="26" t="n">
         <f aca="false">H32+J32</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N32" s="26" t="n">
         <f aca="false">K32+M32</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O32" s="25" t="n">
         <v>1</v>
@@ -5362,16 +5390,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C33" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>181</v>
@@ -5383,13 +5411,13 @@
         <v>15</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J33" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K33" s="25" t="n">
         <v>10</v>
@@ -5399,11 +5427,11 @@
       </c>
       <c r="M33" s="26" t="n">
         <f aca="false">H33+J33</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N33" s="26" t="n">
         <f aca="false">K33+M33</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O33" s="25" t="n">
         <v>1</v>
@@ -5411,16 +5439,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>274</v>
@@ -5432,13 +5460,13 @@
         <v>9</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" s="25" t="n">
         <v>230</v>
       </c>
       <c r="J34" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K34" s="25" t="n">
         <v>10</v>
@@ -5448,11 +5476,11 @@
       </c>
       <c r="M34" s="26" t="n">
         <f aca="false">H34+J34</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N34" s="26" t="n">
         <f aca="false">K34+M34</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O34" s="25" t="n">
         <v>1</v>
@@ -5460,16 +5488,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E35" s="25" t="n">
         <v>277</v>
@@ -5481,13 +5509,13 @@
         <v>15</v>
       </c>
       <c r="H35" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" s="25" t="n">
         <v>227</v>
       </c>
       <c r="J35" s="25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K35" s="25" t="n">
         <v>10</v>
@@ -5497,11 +5525,11 @@
       </c>
       <c r="M35" s="26" t="n">
         <f aca="false">H35+J35</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="N35" s="26" t="n">
         <f aca="false">K35+M35</f>
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O35" s="25" t="n">
         <v>1</v>
@@ -5509,16 +5537,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C36" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E36" s="25" t="n">
         <v>179</v>
@@ -5530,13 +5558,13 @@
         <v>13</v>
       </c>
       <c r="H36" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J36" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K36" s="25" t="n">
         <v>10</v>
@@ -5546,11 +5574,11 @@
       </c>
       <c r="M36" s="26" t="n">
         <f aca="false">H36+J36</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N36" s="26" t="n">
         <f aca="false">K36+M36</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O36" s="25" t="n">
         <v>1</v>
@@ -5558,16 +5586,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C37" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D37" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E37" s="25" t="n">
         <v>181</v>
@@ -5579,13 +5607,13 @@
         <v>15</v>
       </c>
       <c r="H37" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J37" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K37" s="25" t="n">
         <v>10</v>
@@ -5595,11 +5623,11 @@
       </c>
       <c r="M37" s="26" t="n">
         <f aca="false">H37+J37</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N37" s="26" t="n">
         <f aca="false">K37+M37</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O37" s="25" t="n">
         <v>1</v>
@@ -5607,16 +5635,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C38" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E38" s="25" t="n">
         <v>177</v>
@@ -5628,13 +5656,13 @@
         <v>11</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J38" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K38" s="25" t="n">
         <v>10</v>
@@ -5644,11 +5672,11 @@
       </c>
       <c r="M38" s="26" t="n">
         <f aca="false">H38+J38</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N38" s="26" t="n">
         <f aca="false">K38+M38</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O38" s="25" t="n">
         <v>1</v>
@@ -5656,16 +5684,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C39" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E39" s="25" t="n">
         <v>181</v>
@@ -5677,13 +5705,13 @@
         <v>15</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J39" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K39" s="25" t="n">
         <v>10</v>
@@ -5693,11 +5721,11 @@
       </c>
       <c r="M39" s="26" t="n">
         <f aca="false">H39+J39</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N39" s="26" t="n">
         <f aca="false">K39+M39</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O39" s="25" t="n">
         <v>1</v>
@@ -5705,16 +5733,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C40" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>188</v>
       </c>
       <c r="E40" s="25" t="n">
         <v>173</v>
@@ -5726,13 +5754,13 @@
         <v>7</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J40" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K40" s="25" t="n">
         <v>10</v>
@@ -5742,11 +5770,11 @@
       </c>
       <c r="M40" s="26" t="n">
         <f aca="false">H40+J40</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N40" s="26" t="n">
         <f aca="false">K40+M40</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O40" s="25" t="n">
         <v>1</v>
@@ -5754,16 +5782,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E41" s="25" t="n">
         <v>181</v>
@@ -5775,13 +5803,13 @@
         <v>15</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41" s="25" t="n">
         <v>131</v>
       </c>
       <c r="J41" s="25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K41" s="25" t="n">
         <v>10</v>
@@ -5791,11 +5819,11 @@
       </c>
       <c r="M41" s="26" t="n">
         <f aca="false">H41+J41</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N41" s="26" t="n">
         <f aca="false">K41+M41</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O41" s="25" t="n">
         <v>1</v>
@@ -5803,7 +5831,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D43" s="28" t="n">
         <f aca="false">COUNTA(A2:A41)</f>
@@ -5823,7 +5851,7 @@
       </c>
       <c r="H43" s="29" t="n">
         <f aca="false">SUM(H2:H41)</f>
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="I43" s="29" t="n">
         <f aca="false">SUM(I2:I41)</f>
@@ -5831,7 +5859,7 @@
       </c>
       <c r="J43" s="29" t="n">
         <f aca="false">SUM(J2:J41)</f>
-        <v>325</v>
+        <v>171</v>
       </c>
       <c r="K43" s="29" t="n">
         <f aca="false">SUM(K2:K41)</f>
@@ -5843,11 +5871,11 @@
       </c>
       <c r="M43" s="29" t="n">
         <f aca="false">SUM(M2:M41)</f>
-        <v>485</v>
+        <v>251</v>
       </c>
       <c r="N43" s="29" t="n">
         <f aca="false">SUM(N2:N41)</f>
-        <v>885</v>
+        <v>651</v>
       </c>
       <c r="O43" s="29" t="n">
         <f aca="false">SUM(O2:O41)</f>
@@ -5856,7 +5884,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D44" s="28" t="n">
         <f aca="false">COUNTIF(D2:D41,"S")</f>
@@ -5876,7 +5904,7 @@
       </c>
       <c r="H44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",H2:H41)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",I2:I41)</f>
@@ -5884,7 +5912,7 @@
       </c>
       <c r="J44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",J2:J41)</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",K2:K41)</f>
@@ -5896,11 +5924,11 @@
       </c>
       <c r="M44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",M2:M41)</f>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",N2:N41)</f>
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="O44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",O2:O41)</f>
@@ -5909,17 +5937,17 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -5944,7 +5972,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -5958,120 +5986,120 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D2" s="30" t="n">
         <v>9.98</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D3" s="30" t="n">
         <v>20.17</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>39.9</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>8.9</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">E6*Premissas!$B$2*Premissas!$B$3</f>
@@ -6081,147 +6109,147 @@
         <v>12.5</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D7" s="30" t="n">
         <v>189.98</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>185</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D9" s="33" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>18</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D11" s="33" t="n">
         <v>2.5</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>0.8</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">1229.41/305</f>
@@ -6229,357 +6257,357 @@
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D14" s="33" t="n">
         <v>5</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D15" s="33" t="n">
         <v>15</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D16" s="33" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>90</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>45</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="33" t="n">
         <v>9</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D20" s="33" t="n">
         <v>40</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>769.32</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D22" s="33" t="n">
         <v>0.9</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D23" s="30" t="n">
         <v>2.37</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D24" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D25" s="30" t="n">
         <v>29.89</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D26" s="30" t="n">
         <v>42.65</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D27" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D28" s="33" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D29" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">E30*Premissas!$B$2*Premissas!$B$3</f>
@@ -6589,21 +6617,21 @@
         <v>30</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">E31*Premissas!$B$2*Premissas!$B$3</f>
@@ -6613,21 +6641,21 @@
         <v>65</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">E32*Premissas!$B$2*Premissas!$B$3</f>
@@ -6637,21 +6665,21 @@
         <v>220</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">E33*Premissas!$B$2*Premissas!$B$3</f>
@@ -6661,21 +6689,21 @@
         <v>9</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">E34*Premissas!$B$2*Premissas!$B$3</f>
@@ -6685,21 +6713,21 @@
         <v>22</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D35" s="31" t="n">
         <f aca="false">E35*Premissas!$B$2*Premissas!$B$3</f>
@@ -6709,42 +6737,42 @@
         <v>35</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D36" s="33" t="n">
         <v>15000</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D37" s="31" t="n">
         <f aca="false">E37*Premissas!$B$2*Premissas!$B$3</f>
@@ -6754,42 +6782,42 @@
         <v>997</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D38" s="33" t="n">
         <v>350</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">913.31/100</f>
@@ -6797,178 +6825,199 @@
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D40" s="33" t="n">
         <v>12</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D41" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D42" s="30" t="n">
         <v>285.99</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D43" s="33" t="n">
         <v>700</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D44" s="30" t="n">
         <v>368.1</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D45" s="33" t="n">
         <v>550</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D46" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D47" s="33" t="n">
         <v>350</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>105</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G48" s="34" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6999,30 +7048,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C2" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B2,Preços!$A:$A,0))</f>
@@ -7042,10 +7091,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C3" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B3,Preços!$A:$A,0))</f>
@@ -7065,10 +7114,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C4" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B4,Preços!$A:$A,0))</f>
@@ -7088,10 +7137,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C5" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B5,Preços!$A:$A,0))</f>
@@ -7111,10 +7160,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C6" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B6,Preços!$A:$A,0))</f>
@@ -7134,10 +7183,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C7" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B7,Preços!$A:$A,0))</f>
@@ -7157,7 +7206,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -7170,10 +7219,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C10" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B10,Preços!$A:$A,0))</f>
@@ -7193,10 +7242,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C11" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B11,Preços!$A:$A,0))</f>
@@ -7216,10 +7265,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C12" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B12,Preços!$A:$A,0))</f>
@@ -7239,10 +7288,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C13" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B13,Preços!$A:$A,0))</f>
@@ -7262,10 +7311,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C14" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B14,Preços!$A:$A,0))</f>
@@ -7285,10 +7334,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C15" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B15,Preços!$A:$A,0))</f>
@@ -7308,7 +7357,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -7321,10 +7370,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C18" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B18,Preços!$A:$A,0))</f>
@@ -7344,10 +7393,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C19" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B19,Preços!$A:$A,0))</f>
@@ -7367,10 +7416,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C20" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B20,Preços!$A:$A,0))</f>
@@ -7390,10 +7439,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C21" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B21,Preços!$A:$A,0))</f>
@@ -7413,10 +7462,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C22" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B22,Preços!$A:$A,0))</f>
@@ -7436,10 +7485,10 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C23" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B23,Preços!$A:$A,0))</f>
@@ -7459,10 +7508,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C24" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B24,Preços!$A:$A,0))</f>
@@ -7482,10 +7531,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C25" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B25,Preços!$A:$A,0))</f>
@@ -7505,10 +7554,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C26" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B26,Preços!$A:$A,0))</f>
@@ -7528,7 +7577,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -7541,10 +7590,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C29" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B29,Preços!$A:$A,0))</f>
@@ -7564,10 +7613,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C30" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B30,Preços!$A:$A,0))</f>
@@ -7587,10 +7636,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C31" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B31,Preços!$A:$A,0))</f>
@@ -7610,10 +7659,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C32" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B32,Preços!$A:$A,0))</f>
@@ -7633,10 +7682,10 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C33" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B33,Preços!$A:$A,0))</f>
@@ -7656,10 +7705,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C34" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B34,Preços!$A:$A,0))</f>
@@ -7679,10 +7728,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C35" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B35,Preços!$A:$A,0))</f>
@@ -7702,10 +7751,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C36" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B36,Preços!$A:$A,0))</f>
@@ -7725,10 +7774,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C37" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B37,Preços!$A:$A,0))</f>
@@ -7748,10 +7797,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B38,Preços!$A:$A,0))</f>
@@ -7771,7 +7820,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7784,10 +7833,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C41" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B41,Preços!$A:$A,0))</f>
@@ -7807,10 +7856,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C42" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B42,Preços!$A:$A,0))</f>
@@ -7830,10 +7879,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C43" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B43,Preços!$A:$A,0))</f>
@@ -7853,10 +7902,10 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C44" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B44,Preços!$A:$A,0))</f>
@@ -7876,10 +7925,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C45" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B45,Preços!$A:$A,0))</f>
@@ -7899,10 +7948,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C46" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B46,Preços!$A:$A,0))</f>
@@ -7922,10 +7971,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C47" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B47,Preços!$A:$A,0))</f>
@@ -7945,10 +7994,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C48" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B48,Preços!$A:$A,0))</f>
@@ -7968,10 +8017,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C49" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B49,Preços!$A:$A,0))</f>
@@ -7991,7 +8040,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -8004,10 +8053,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C52" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B52,Preços!$A:$A,0))</f>
@@ -8027,10 +8076,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C53" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B53,Preços!$A:$A,0))</f>
@@ -8050,10 +8099,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C54" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B54,Preços!$A:$A,0))</f>
@@ -8073,10 +8122,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C55" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B55,Preços!$A:$A,0))</f>
@@ -8096,7 +8145,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -8109,10 +8158,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C58" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B58,Preços!$A:$A,0))</f>
@@ -8132,10 +8181,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C59" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B59,Preços!$A:$A,0))</f>
@@ -8155,10 +8204,10 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C60" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B60,Preços!$A:$A,0))</f>
@@ -8178,10 +8227,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C61" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B61,Preços!$A:$A,0))</f>
@@ -8201,10 +8250,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C62" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B62,Preços!$A:$A,0))</f>
@@ -8224,10 +8273,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C63" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B63,Preços!$A:$A,0))</f>
@@ -8247,10 +8296,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C64" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B64,Preços!$A:$A,0))</f>
@@ -8270,10 +8319,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C65" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B65,Preços!$A:$A,0))</f>
@@ -8293,10 +8342,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C66" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B66,Preços!$A:$A,0))</f>
@@ -8316,10 +8365,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C67" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B67,Preços!$A:$A,0))</f>
@@ -8339,10 +8388,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C68" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B68,Preços!$A:$A,0))</f>
@@ -8362,7 +8411,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -8375,10 +8424,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C71" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B71,Preços!$A:$A,0))</f>
@@ -8398,10 +8447,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C72" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B72,Preços!$A:$A,0))</f>
@@ -8421,7 +8470,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -8434,17 +8483,17 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -8463,7 +8512,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -8477,38 +8526,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -8533,10 +8582,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$K$44*(1+Premissas!$B$26),0)</f>
@@ -8561,18 +8610,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
-        <v>534</v>
+        <v>277</v>
       </c>
       <c r="E5" s="37" t="n">
         <f aca="false">Composição!$F$27</f>
@@ -8580,19 +8629,19 @@
       </c>
       <c r="F5" s="31" t="n">
         <f aca="false">C5*E5</f>
-        <v>3643.65</v>
+        <v>1889.3</v>
       </c>
       <c r="G5" s="31" t="n">
         <f aca="false">D5*E5</f>
-        <v>72063.3</v>
+        <v>37381.15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -8617,18 +8666,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="D7" s="39" t="n">
         <f aca="false">Estações!$N$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
-        <v>3135</v>
+        <v>2433</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Preços!$D$13</f>
@@ -8636,27 +8685,27 @@
       </c>
       <c r="F7" s="31" t="n">
         <f aca="false">C7*E7</f>
-        <v>628.812983606558</v>
+        <v>483.702295081967</v>
       </c>
       <c r="G7" s="31" t="n">
         <f aca="false">D7*E7</f>
-        <v>12636.7224590164</v>
+        <v>9807.06403278689</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">Estações!$N$44*2+Estações!$O$44*4</f>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D8" s="39" t="n">
         <f aca="false">Estações!$N$43*2+Estações!$O$43*4</f>
-        <v>1930</v>
+        <v>1462</v>
       </c>
       <c r="E8" s="37" t="n">
         <f aca="false">Preços!$D$12</f>
@@ -8664,19 +8713,19 @@
       </c>
       <c r="F8" s="31" t="n">
         <f aca="false">C8*E8</f>
-        <v>76.8</v>
+        <v>57.6</v>
       </c>
       <c r="G8" s="31" t="n">
         <f aca="false">D8*E8</f>
-        <v>1544</v>
+        <v>1169.6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">Estações!$K$44*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$O$44*2*Premissas!$B$34+Estações!$O$44*Premissas!$B$35</f>
@@ -8701,10 +8750,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -8729,206 +8778,206 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C11" s="39" t="n">
+        <f aca="false">Estações!$O$44</f>
+        <v>2</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <f aca="false">Estações!$O$43</f>
+        <v>40</v>
+      </c>
+      <c r="E11" s="37" t="n">
+        <f aca="false">Preços!$D$48</f>
+        <v>45</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <f aca="false">C11*E11</f>
+        <v>90</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <f aca="false">D11*E11</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C12" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$36</f>
         <v>100</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D12" s="39" t="n">
         <f aca="false">Estações!$O$43*Premissas!$B$36</f>
         <v>2000</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E12" s="37" t="n">
         <f aca="false">Preços!$D$13</f>
         <v>4.03085245901639</v>
       </c>
-      <c r="F11" s="31" t="n">
-        <f aca="false">C11*E11</f>
+      <c r="F12" s="31" t="n">
+        <f aca="false">C12*E12</f>
         <v>403.085245901639</v>
       </c>
-      <c r="G11" s="31" t="n">
-        <f aca="false">D11*E11</f>
+      <c r="G12" s="31" t="n">
+        <f aca="false">D12*E12</f>
         <v>8061.70491803279</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="C12" s="39" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44/Premissas!$B$37,0)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D13" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$43/Premissas!$B$37,0)</f>
         <v>2</v>
       </c>
-      <c r="E12" s="37" t="n">
+      <c r="E13" s="37" t="n">
         <f aca="false">Preços!$D$21</f>
         <v>769.32</v>
       </c>
-      <c r="F12" s="31" t="n">
-        <f aca="false">C12*E12</f>
+      <c r="F13" s="31" t="n">
+        <f aca="false">C13*E13</f>
         <v>769.32</v>
       </c>
-      <c r="G12" s="31" t="n">
-        <f aca="false">D12*E12</f>
+      <c r="G13" s="31" t="n">
+        <f aca="false">D13*E13</f>
         <v>1538.64</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C13" s="39" t="n">
-        <f aca="false">C12</f>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="39" t="n">
+        <f aca="false">C13</f>
         <v>1</v>
       </c>
-      <c r="D13" s="39" t="n">
-        <f aca="false">D12</f>
+      <c r="D14" s="39" t="n">
+        <f aca="false">D13</f>
         <v>2</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E14" s="37" t="n">
         <f aca="false">Preços!$D$44</f>
         <v>368.1</v>
       </c>
-      <c r="F13" s="31" t="n">
-        <f aca="false">C13*E13</f>
+      <c r="F14" s="31" t="n">
+        <f aca="false">C14*E14</f>
         <v>368.1</v>
       </c>
-      <c r="G13" s="31" t="n">
-        <f aca="false">D13*E13</f>
+      <c r="G14" s="31" t="n">
+        <f aca="false">D14*E14</f>
         <v>736.2</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C14" s="39" t="n">
-        <f aca="false">C12</f>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="C15" s="39" t="n">
+        <f aca="false">C13</f>
         <v>1</v>
       </c>
-      <c r="D14" s="39" t="n">
-        <f aca="false">D12</f>
+      <c r="D15" s="39" t="n">
+        <f aca="false">D13</f>
         <v>2</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E15" s="37" t="n">
         <f aca="false">Preços!$D$45</f>
         <v>550</v>
       </c>
-      <c r="F14" s="31" t="n">
-        <f aca="false">C14*E14</f>
+      <c r="F15" s="31" t="n">
+        <f aca="false">C15*E15</f>
         <v>550</v>
       </c>
-      <c r="G14" s="31" t="n">
-        <f aca="false">D14*E14</f>
+      <c r="G15" s="31" t="n">
+        <f aca="false">D15*E15</f>
         <v>1100</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C15" s="39" t="n">
-        <f aca="false">C12*Premissas!$B$38</f>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" s="39" t="n">
+        <f aca="false">C13*Premissas!$B$38</f>
         <v>80</v>
       </c>
-      <c r="D15" s="39" t="n">
-        <f aca="false">D12*Premissas!$B$38</f>
+      <c r="D16" s="39" t="n">
+        <f aca="false">D13*Premissas!$B$38</f>
         <v>160</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E16" s="37" t="n">
         <f aca="false">Preços!$D$13</f>
         <v>4.03085245901639</v>
       </c>
-      <c r="F15" s="31" t="n">
-        <f aca="false">C15*E15</f>
+      <c r="F16" s="31" t="n">
+        <f aca="false">C16*E16</f>
         <v>322.468196721312</v>
       </c>
-      <c r="G15" s="31" t="n">
-        <f aca="false">D15*E15</f>
+      <c r="G16" s="31" t="n">
+        <f aca="false">D16*E16</f>
         <v>644.936393442623</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="C16" s="39" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$39,0)</f>
         <v>1</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$43*Premissas!$B$39,0)</f>
         <v>20</v>
       </c>
-      <c r="E16" s="37" t="n">
+      <c r="E17" s="37" t="n">
         <f aca="false">Preços!$D$47</f>
         <v>350</v>
       </c>
-      <c r="F16" s="31" t="n">
-        <f aca="false">C16*E16</f>
-        <v>350</v>
-      </c>
-      <c r="G16" s="31" t="n">
-        <f aca="false">D16*E16</f>
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="C17" s="39" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
-      </c>
-      <c r="D17" s="39" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
-      </c>
-      <c r="E17" s="37" t="n">
-        <f aca="false">Preços!$D$42</f>
-        <v>285.99</v>
-      </c>
       <c r="F17" s="31" t="n">
         <f aca="false">C17*E17</f>
-        <v>285.99</v>
+        <v>350</v>
       </c>
       <c r="G17" s="31" t="n">
         <f aca="false">D17*E17</f>
-        <v>285.99</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">1</f>
@@ -8939,104 +8988,104 @@
         <v>1</v>
       </c>
       <c r="E18" s="37" t="n">
+        <f aca="false">Preços!$D$42</f>
+        <v>285.99</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <f aca="false">C18*E18</f>
+        <v>285.99</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <f aca="false">D18*E18</f>
+        <v>285.99</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="C19" s="39" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="39" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="37" t="n">
         <f aca="false">Preços!$D$43</f>
         <v>700</v>
       </c>
-      <c r="F18" s="31" t="n">
-        <f aca="false">C18*E18</f>
+      <c r="F19" s="31" t="n">
+        <f aca="false">C19*E19</f>
         <v>700</v>
       </c>
-      <c r="G18" s="31" t="n">
-        <f aca="false">D18*E18</f>
+      <c r="G19" s="31" t="n">
+        <f aca="false">D19*E19</f>
         <v>700</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="40" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="40" t="n">
         <f aca="false">Premissas!$B$27</f>
         <v>0.05</v>
       </c>
-      <c r="F19" s="31" t="n">
-        <f aca="false">E19*SUM(F3:F18)</f>
-        <v>782.415937520492</v>
-      </c>
-      <c r="G19" s="31" t="n">
-        <f aca="false">E19*SUM(G3:G18)</f>
-        <v>12398.7336497541</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="38" t="n">
-        <f aca="false">SUM(F3:F19)</f>
-        <v>16430.7346879303</v>
-      </c>
-      <c r="G20" s="38" t="n">
-        <f aca="false">SUM(G3:G19)</f>
-        <v>260373.406644836</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>433</v>
+      <c r="F20" s="31" t="n">
+        <f aca="false">E20*SUM(F3:F19)</f>
+        <v>690.982903094262</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <f aca="false">E20*SUM(G3:G19)</f>
+        <v>10594.4232284426</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="38" t="n">
+        <f aca="false">SUM(F3:F20)</f>
+        <v>14510.6409649795</v>
+      </c>
+      <c r="G21" s="38" t="n">
+        <f aca="false">SUM(G3:G20)</f>
+        <v>222482.887797295</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="C23" s="21" t="n">
+      <c r="A23" s="12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C24" s="21" t="n">
         <f aca="false">C3*Premissas!$B$12</f>
         <v>17.75</v>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D24" s="21" t="n">
         <f aca="false">D3*Premissas!$B$12</f>
         <v>352</v>
-      </c>
-      <c r="E23" s="37" t="n">
-        <f aca="false">Premissas!$B$9</f>
-        <v>34.9305521472393</v>
-      </c>
-      <c r="F23" s="31" t="n">
-        <f aca="false">C23*E23</f>
-        <v>620.017300613497</v>
-      </c>
-      <c r="G23" s="31" t="n">
-        <f aca="false">D23*E23</f>
-        <v>12295.5543558282</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="C24" s="21" t="n">
-        <f aca="false">C4*Premissas!$B$13</f>
-        <v>16.5</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <f aca="false">D4*Premissas!$B$13</f>
-        <v>330</v>
       </c>
       <c r="E24" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9044,27 +9093,27 @@
       </c>
       <c r="F24" s="31" t="n">
         <f aca="false">C24*E24</f>
-        <v>576.354110429448</v>
+        <v>620.017300613497</v>
       </c>
       <c r="G24" s="31" t="n">
         <f aca="false">D24*E24</f>
-        <v>11527.082208589</v>
+        <v>12295.5543558282</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C25" s="21" t="n">
-        <f aca="false">C5*Premissas!$B$14</f>
-        <v>27</v>
+        <f aca="false">C4*Premissas!$B$13</f>
+        <v>16.5</v>
       </c>
       <c r="D25" s="21" t="n">
-        <f aca="false">D5*Premissas!$B$14</f>
-        <v>534</v>
+        <f aca="false">D4*Premissas!$B$13</f>
+        <v>330</v>
       </c>
       <c r="E25" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9072,27 +9121,27 @@
       </c>
       <c r="F25" s="31" t="n">
         <f aca="false">C25*E25</f>
-        <v>943.12490797546</v>
+        <v>576.354110429448</v>
       </c>
       <c r="G25" s="31" t="n">
         <f aca="false">D25*E25</f>
-        <v>18652.9148466258</v>
+        <v>11527.082208589</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C26" s="21" t="n">
-        <f aca="false">C6*Premissas!$B$15</f>
-        <v>6</v>
+        <f aca="false">C5*Premissas!$B$14</f>
+        <v>14</v>
       </c>
       <c r="D26" s="21" t="n">
-        <f aca="false">D6*Premissas!$B$15</f>
-        <v>88</v>
+        <f aca="false">D5*Premissas!$B$14</f>
+        <v>277</v>
       </c>
       <c r="E26" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9100,27 +9149,27 @@
       </c>
       <c r="F26" s="31" t="n">
         <f aca="false">C26*E26</f>
-        <v>209.583312883436</v>
+        <v>489.02773006135</v>
       </c>
       <c r="G26" s="31" t="n">
         <f aca="false">D26*E26</f>
-        <v>3073.88858895706</v>
+        <v>9675.76294478528</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C27" s="21" t="n">
-        <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$K$44*Premissas!$B$18+Estações!$M$44*Premissas!$B$19+C9*Premissas!$B$20)*Premissas!$B$22</f>
-        <v>52.98</v>
+        <f aca="false">C6*Premissas!$B$15</f>
+        <v>6</v>
       </c>
       <c r="D27" s="21" t="n">
-        <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$K$43*Premissas!$B$18+Estações!$M$43*Premissas!$B$19+D9*Premissas!$B$20)*Premissas!$B$22</f>
-        <v>1062.225</v>
+        <f aca="false">D6*Premissas!$B$15</f>
+        <v>88</v>
       </c>
       <c r="E27" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9128,27 +9177,27 @@
       </c>
       <c r="F27" s="31" t="n">
         <f aca="false">C27*E27</f>
-        <v>1850.62065276074</v>
+        <v>209.583312883436</v>
       </c>
       <c r="G27" s="31" t="n">
         <f aca="false">D27*E27</f>
-        <v>37104.1057546012</v>
+        <v>3073.88858895706</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C28" s="21" t="n">
-        <f aca="false">Estações!$O$44*Premissas!$B$21*Premissas!$B$22</f>
-        <v>12</v>
+        <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$K$44*Premissas!$B$18+Estações!$M$44*Premissas!$B$19+C9*Premissas!$B$20)*Premissas!$B$22</f>
+        <v>46.68</v>
       </c>
       <c r="D28" s="21" t="n">
-        <f aca="false">Estações!$O$43*Premissas!$B$21*Premissas!$B$22</f>
-        <v>240</v>
+        <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$K$43*Premissas!$B$18+Estações!$M$43*Premissas!$B$19+D9*Premissas!$B$20)*Premissas!$B$22</f>
+        <v>939.375</v>
       </c>
       <c r="E28" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9156,245 +9205,273 @@
       </c>
       <c r="F28" s="31" t="n">
         <f aca="false">C28*E28</f>
-        <v>419.166625766871</v>
+        <v>1630.55817423313</v>
       </c>
       <c r="G28" s="31" t="n">
         <f aca="false">D28*E28</f>
-        <v>8383.33251533742</v>
+        <v>32812.8874233129</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C29" s="21" t="n">
+        <f aca="false">Estações!$O$44*Premissas!$B$21*Premissas!$B$22</f>
+        <v>12</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <f aca="false">Estações!$O$43*Premissas!$B$21*Premissas!$B$22</f>
+        <v>240</v>
+      </c>
+      <c r="E29" s="37" t="n">
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
+      </c>
+      <c r="F29" s="31" t="n">
+        <f aca="false">C29*E29</f>
+        <v>419.166625766871</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <f aca="false">D29*E29</f>
+        <v>8383.33251533742</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$23*Premissas!$B$24</f>
         <v>8</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D30" s="21" t="n">
         <f aca="false">Estações!$O$43*Premissas!$B$23*Premissas!$B$24</f>
         <v>160</v>
       </c>
-      <c r="E29" s="37" t="n">
+      <c r="E30" s="37" t="n">
         <f aca="false">Premissas!$B$11</f>
         <v>24.6575460122699</v>
       </c>
-      <c r="F29" s="31" t="n">
-        <f aca="false">C29*E29</f>
+      <c r="F30" s="31" t="n">
+        <f aca="false">C30*E30</f>
         <v>197.26036809816</v>
       </c>
-      <c r="G29" s="31" t="n">
-        <f aca="false">D29*E29</f>
+      <c r="G30" s="31" t="n">
+        <f aca="false">D30*E30</f>
         <v>3945.20736196319</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="C30" s="21" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="C31" s="21" t="n">
         <f aca="false">Premissas!$B$25</f>
         <v>16</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D31" s="21" t="n">
         <f aca="false">Premissas!$B$25</f>
         <v>16</v>
       </c>
-      <c r="E30" s="37" t="n">
+      <c r="E31" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
         <v>34.9305521472393</v>
       </c>
-      <c r="F30" s="31" t="n">
-        <f aca="false">C30*E30</f>
+      <c r="F31" s="31" t="n">
+        <f aca="false">C31*E31</f>
         <v>558.888834355828</v>
       </c>
-      <c r="G30" s="31" t="n">
-        <f aca="false">D30*E30</f>
+      <c r="G31" s="31" t="n">
+        <f aca="false">D31*E31</f>
         <v>558.888834355828</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="41" t="n">
-        <f aca="false">SUM(C23:C30)</f>
-        <v>156.23</v>
-      </c>
-      <c r="D31" s="41" t="n">
-        <f aca="false">SUM(D23:D30)</f>
-        <v>2782.225</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="38" t="n">
-        <f aca="false">SUM(F23:F30)</f>
-        <v>5375.01611288344</v>
-      </c>
-      <c r="G31" s="38" t="n">
-        <f aca="false">SUM(G23:G30)</f>
-        <v>95540.9744662577</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="38" t="n">
-        <f aca="false">F20+F31</f>
-        <v>21805.7508008138</v>
-      </c>
-      <c r="G33" s="38" t="n">
-        <f aca="false">G20+G31</f>
-        <v>355914.381111094</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
-        <v>451</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="41" t="n">
+        <f aca="false">SUM(C24:C31)</f>
+        <v>136.93</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <f aca="false">SUM(D24:D31)</f>
+        <v>2402.375</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="38" t="n">
+        <f aca="false">SUM(F24:F31)</f>
+        <v>4700.85645644172</v>
+      </c>
+      <c r="G32" s="38" t="n">
+        <f aca="false">SUM(G24:G31)</f>
+        <v>82272.6042331288</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="38" t="n">
+        <f aca="false">F21+F32</f>
+        <v>19211.4974214212</v>
+      </c>
+      <c r="G34" s="38" t="n">
+        <f aca="false">G21+G32</f>
+        <v>304755.492030424</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="C36" s="39" t="n">
+      <c r="A36" s="12" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="C37" s="39" t="n">
         <f aca="false">-(C4+C5+C6)</f>
-        <v>-52</v>
-      </c>
-      <c r="D36" s="39" t="n">
+        <v>-39</v>
+      </c>
+      <c r="D37" s="39" t="n">
         <f aca="false">-(D4+D5+D6)</f>
-        <v>-1018</v>
-      </c>
-      <c r="E36" s="37" t="n">
+        <v>-761</v>
+      </c>
+      <c r="E37" s="37" t="n">
         <f aca="false">Preços!$D$9</f>
         <v>8</v>
       </c>
-      <c r="F36" s="31" t="n">
-        <f aca="false">C36*E36</f>
-        <v>-416</v>
-      </c>
-      <c r="G36" s="31" t="n">
-        <f aca="false">D36*E36</f>
-        <v>-8144</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="C37" s="39" t="n">
+      <c r="F37" s="31" t="n">
+        <f aca="false">C37*E37</f>
+        <v>-312</v>
+      </c>
+      <c r="G37" s="31" t="n">
+        <f aca="false">D37*E37</f>
+        <v>-6088</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C38" s="39" t="n">
         <f aca="false">C6</f>
         <v>3</v>
       </c>
-      <c r="D37" s="39" t="n">
+      <c r="D38" s="39" t="n">
         <f aca="false">D6</f>
         <v>44</v>
       </c>
-      <c r="E37" s="37" t="n">
+      <c r="E38" s="37" t="n">
         <f aca="false">(Preços!$D$8-Preços!$D$7)</f>
         <v>-4.97999999999999</v>
       </c>
-      <c r="F37" s="31" t="n">
-        <f aca="false">C37*E37</f>
+      <c r="F38" s="31" t="n">
+        <f aca="false">C38*E38</f>
         <v>-14.94</v>
       </c>
-      <c r="G37" s="31" t="n">
-        <f aca="false">D37*E37</f>
+      <c r="G38" s="31" t="n">
+        <f aca="false">D38*E38</f>
         <v>-219.12</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="C38" s="39" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C39" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$42</f>
         <v>60</v>
       </c>
-      <c r="D38" s="39" t="n">
+      <c r="D39" s="39" t="n">
         <f aca="false">Estações!$O$43*Premissas!$B$42</f>
         <v>1200</v>
       </c>
-      <c r="E38" s="37" t="n">
+      <c r="E39" s="37" t="n">
         <f aca="false">Preços!$D$39</f>
         <v>9.1331</v>
       </c>
-      <c r="F38" s="31" t="n">
-        <f aca="false">C38*E38</f>
+      <c r="F39" s="31" t="n">
+        <f aca="false">C39*E39</f>
         <v>547.986</v>
       </c>
-      <c r="G38" s="31" t="n">
-        <f aca="false">D38*E38</f>
+      <c r="G39" s="31" t="n">
+        <f aca="false">D39*E39</f>
         <v>10959.72</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
-        <v>457</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="38" t="n">
-        <f aca="false">F20+SUM(F36:F38)</f>
-        <v>16547.7806879303</v>
-      </c>
-      <c r="G39" s="38" t="n">
-        <f aca="false">G20+SUM(G36:G38)</f>
-        <v>262970.006644836</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
-        <v>458</v>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="38" t="n">
+        <f aca="false">F21+SUM(F37:F39)</f>
+        <v>14731.6869649795</v>
+      </c>
+      <c r="G40" s="38" t="n">
+        <f aca="false">G21+SUM(G37:G39)</f>
+        <v>227135.487797295</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="C42" s="39" t="n">
+      <c r="A42" s="12" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C43" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$L$44*(1+Premissas!$B$26),0)</f>
         <v>55</v>
       </c>
-      <c r="D42" s="39" t="n">
+      <c r="D43" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$L$43*(1+Premissas!$B$26),0)</f>
         <v>1129</v>
       </c>
-      <c r="E42" s="37" t="n">
+      <c r="E43" s="37" t="n">
         <f aca="false">Preços!$D$22</f>
         <v>0.9</v>
       </c>
-      <c r="F42" s="31" t="n">
-        <f aca="false">C42*E42</f>
+      <c r="F43" s="31" t="n">
+        <f aca="false">C43*E43</f>
         <v>49.5</v>
       </c>
-      <c r="G42" s="31" t="n">
-        <f aca="false">D42*E42</f>
+      <c r="G43" s="31" t="n">
+        <f aca="false">D43*E43</f>
         <v>1016.1</v>
       </c>
     </row>
@@ -9428,38 +9505,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9484,18 +9561,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
-        <v>534</v>
+        <v>277</v>
       </c>
       <c r="E4" s="37" t="n">
         <f aca="false">Preços!$D$34+Preços!$D$15+Preços!$D$10</f>
@@ -9503,19 +9580,19 @@
       </c>
       <c r="F4" s="31" t="n">
         <f aca="false">C4*E4</f>
-        <v>6575.87106</v>
+        <v>3409.71092</v>
       </c>
       <c r="G4" s="31" t="n">
         <f aca="false">D4*E4</f>
-        <v>130056.11652</v>
+        <v>67463.56606</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -9540,18 +9617,18 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D6" s="39" t="n">
         <f aca="false">Estações!$F$43*Premissas!$B$43+Estações!$M$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
-        <v>3215</v>
+        <v>2513</v>
       </c>
       <c r="E6" s="37" t="n">
         <f aca="false">Preços!$D$13</f>
@@ -9559,27 +9636,27 @@
       </c>
       <c r="F6" s="31" t="n">
         <f aca="false">C6*E6</f>
-        <v>644.936393442623</v>
+        <v>499.825704918033</v>
       </c>
       <c r="G6" s="31" t="n">
         <f aca="false">D6*E6</f>
-        <v>12959.1906557377</v>
+        <v>10129.5322295082</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D7" s="39" t="n">
         <f aca="false">(Estações!$F$43+Estações!$M$43)*2+Estações!$O$43*4</f>
-        <v>3690</v>
+        <v>3222</v>
       </c>
       <c r="E7" s="37" t="n">
         <f aca="false">Preços!$D$12</f>
@@ -9587,38 +9664,38 @@
       </c>
       <c r="F7" s="31" t="n">
         <f aca="false">C7*E7</f>
-        <v>147.2</v>
+        <v>128</v>
       </c>
       <c r="G7" s="31" t="n">
         <f aca="false">D7*E7</f>
-        <v>2952</v>
+        <v>2577.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!F9:F18)</f>
-        <v>4314.96344262295</v>
+        <f aca="false">SUM('A-Interno'!F9:F19)</f>
+        <v>4404.96344262295</v>
       </c>
       <c r="G8" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!G9:G18)</f>
-        <v>31387.4713114754</v>
+        <f aca="false">SUM('A-Interno'!G9:G19)</f>
+        <v>33187.4713114754</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">1</f>
@@ -9643,18 +9720,18 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">(C3+C4+C5)*Premissas!$B$44</f>
-        <v>10.1</v>
+        <v>8.8</v>
       </c>
       <c r="D10" s="21" t="n">
         <f aca="false">(D3+D4+D5)*Premissas!$B$44</f>
-        <v>198.6</v>
+        <v>172.9</v>
       </c>
       <c r="E10" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9662,27 +9739,27 @@
       </c>
       <c r="F10" s="31" t="n">
         <f aca="false">C10*E10</f>
-        <v>352.798576687117</v>
+        <v>307.388858895706</v>
       </c>
       <c r="G10" s="31" t="n">
         <f aca="false">D10*E10</f>
-        <v>6937.20765644172</v>
+        <v>6039.49246625767</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>57.48</v>
+        <v>51.18</v>
       </c>
       <c r="D11" s="21" t="n">
         <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>1152.225</v>
+        <v>1029.375</v>
       </c>
       <c r="E11" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9690,35 +9767,35 @@
       </c>
       <c r="F11" s="31" t="n">
         <f aca="false">C11*E11</f>
-        <v>2007.80813742331</v>
+        <v>1787.74565889571</v>
       </c>
       <c r="G11" s="31" t="n">
         <f aca="false">D11*E11</f>
-        <v>40247.8554478528</v>
+        <v>35956.6371165644</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!F29:F30)</f>
+        <f aca="false">SUM('A-Interno'!F30:F31)</f>
         <v>756.149202453988</v>
       </c>
       <c r="G12" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!G29:G30)</f>
+        <f aca="false">SUM('A-Interno'!G30:G31)</f>
         <v>4504.09619631902</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -9726,24 +9803,24 @@
       <c r="E13" s="16"/>
       <c r="F13" s="38" t="n">
         <f aca="false">SUM(F3:F12)</f>
-        <v>38473.30927263</v>
+        <v>34967.3662477864</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">SUM(G3:G12)</f>
-        <v>404672.430867827</v>
+        <v>335486.888460125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9768,18 +9845,18 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
-        <v>534</v>
+        <v>277</v>
       </c>
       <c r="E17" s="37" t="n">
         <f aca="false">Preços!$D$31</f>
@@ -9787,19 +9864,19 @@
       </c>
       <c r="F17" s="31" t="n">
         <f aca="false">C17*E17</f>
-        <v>16796.20995</v>
+        <v>8709.1459</v>
       </c>
       <c r="G17" s="31" t="n">
         <f aca="false">D17*E17</f>
-        <v>332191.7079</v>
+        <v>172316.67245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -9824,10 +9901,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C19" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -9852,18 +9929,18 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C20" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D20" s="39" t="n">
         <f aca="false">Estações!$F$43*Premissas!$B$43+Estações!$M$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
-        <v>3215</v>
+        <v>2513</v>
       </c>
       <c r="E20" s="37" t="n">
         <f aca="false">Preços!$D$13</f>
@@ -9871,27 +9948,27 @@
       </c>
       <c r="F20" s="31" t="n">
         <f aca="false">C20*E20</f>
-        <v>644.936393442623</v>
+        <v>499.825704918033</v>
       </c>
       <c r="G20" s="31" t="n">
         <f aca="false">D20*E20</f>
-        <v>12959.1906557377</v>
+        <v>10129.5322295082</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C21" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D21" s="39" t="n">
         <f aca="false">(Estações!$F$43+Estações!$M$43)*2+Estações!$O$43*4</f>
-        <v>3690</v>
+        <v>3222</v>
       </c>
       <c r="E21" s="37" t="n">
         <f aca="false">Preços!$D$12</f>
@@ -9899,46 +9976,46 @@
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">C21*E21</f>
-        <v>147.2</v>
+        <v>128</v>
       </c>
       <c r="G21" s="31" t="n">
         <f aca="false">D21*E21</f>
-        <v>2952</v>
+        <v>2577.6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!F9:F18)</f>
-        <v>4314.96344262295</v>
+        <f aca="false">SUM('A-Interno'!F9:F19)</f>
+        <v>4404.96344262295</v>
       </c>
       <c r="G22" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!G9:G18)</f>
-        <v>31387.4713114754</v>
+        <f aca="false">SUM('A-Interno'!G9:G19)</f>
+        <v>33187.4713114754</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>57.48</v>
+        <v>51.18</v>
       </c>
       <c r="D23" s="21" t="n">
         <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>1152.225</v>
+        <v>1029.375</v>
       </c>
       <c r="E23" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
@@ -9946,35 +10023,35 @@
       </c>
       <c r="F23" s="31" t="n">
         <f aca="false">C23*E23</f>
-        <v>2007.80813742331</v>
+        <v>1787.74565889571</v>
       </c>
       <c r="G23" s="31" t="n">
         <f aca="false">D23*E23</f>
-        <v>40247.8554478528</v>
+        <v>35956.6371165644</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
       <c r="F24" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!F29:F30)</f>
+        <f aca="false">SUM('A-Interno'!F30:F31)</f>
         <v>756.149202453988</v>
       </c>
       <c r="G24" s="37" t="n">
-        <f aca="false">SUM('A-Interno'!G29:G30)</f>
+        <f aca="false">SUM('A-Interno'!G30:G31)</f>
         <v>4504.09619631902</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -9982,16 +10059,16 @@
       <c r="E25" s="16"/>
       <c r="F25" s="38" t="n">
         <f aca="false">SUM(F16:F24)</f>
-        <v>50062.1850259429</v>
+        <v>41680.7478088907</v>
       </c>
       <c r="G25" s="38" t="n">
         <f aca="false">SUM(G16:G24)</f>
-        <v>928695.303111385</v>
+        <v>763124.990903867</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -10023,57 +10100,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="37" t="n">
-        <f aca="false">'A-Interno'!F33</f>
-        <v>21805.7508008138</v>
+        <f aca="false">'A-Interno'!F34</f>
+        <v>19211.4974214212</v>
       </c>
       <c r="G3" s="37" t="n">
-        <f aca="false">'A-Interno'!G33</f>
-        <v>355914.381111094</v>
+        <f aca="false">'A-Interno'!G34</f>
+        <v>304755.492030424</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Premissas!$B$40*Estações!$O$44/Estações!$O$43,0)</f>
@@ -10098,10 +10175,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">C4*30/3600</f>
@@ -10126,15 +10203,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$41,0)</f>
@@ -10159,10 +10236,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10187,10 +10264,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">C8*1.5</f>
@@ -10215,7 +10292,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -10223,24 +10300,24 @@
       <c r="E11" s="16"/>
       <c r="F11" s="38" t="n">
         <f aca="false">SUM(F3:F5)+SUM(F8:F10)</f>
-        <v>23565.7019255581</v>
+        <v>20971.4485461656</v>
       </c>
       <c r="G11" s="38" t="n">
         <f aca="false">SUM(G3:G5)+SUM(G8:G10)</f>
-        <v>388954.173667331</v>
+        <v>337795.284586661</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10265,10 +10342,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">C14*2</f>
@@ -10293,7 +10370,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -10301,19 +10378,19 @@
       <c r="E16" s="16"/>
       <c r="F16" s="38" t="n">
         <f aca="false">SUM(F3:F5)+SUM(F14:F15)</f>
-        <v>23144.153517633</v>
+        <v>20549.9001382404</v>
       </c>
       <c r="G16" s="38" t="n">
         <f aca="false">SUM(G3:G5)+SUM(G14:G15)</f>
-        <v>382682.435447478</v>
+        <v>331523.546366808</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">C8</f>
@@ -10338,7 +10415,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -18,6 +18,7 @@
     <sheet name="A-Terceiros" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="B-RFID" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Software" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="POC" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="614">
   <si>
     <t xml:space="preserve">Orçamento do projeto Pick-to-Light (flow rack)</t>
   </si>
@@ -49,7 +50,7 @@
     <t xml:space="preserve">• Aba 'Estações': números de endereços por estação, extraídos de wms_endereco (esteiras 1 e 2) em 23/10/2026. Corrija qualquer número direto ali: todo o orçamento recalcula.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Coluna 'Piloto' (S/N) na aba 'Estações' define quais estações entram no cenário piloto (padrão: 05 e 27).</t>
+    <t xml:space="preserve">• Coluna 'Piloto' (S/N) na aba 'Estações' define quais estações entram no cenário piloto (POC: 04 e 27).</t>
   </si>
   <si>
     <t xml:space="preserve">• Aba 'Preços': catálogo de peças com fonte e data. Itens marcados 'Estimativa' devem ser cotados antes da compra.</t>
@@ -154,7 +155,7 @@
     <t xml:space="preserve">Resumo do orçamento, Pick-to-Light</t>
   </si>
   <si>
-    <t xml:space="preserve">Piloto: estações marcadas 'S' na aba Estações (padrão 05 e 27). A operação completa já inclui o piloto. Hardware, instalação e treinamento; software nas linhas abaixo.</t>
+    <t xml:space="preserve">Piloto: estações marcadas 'S' na aba Estações (POC: 04 e 27). A operação completa já inclui o piloto. Hardware, instalação e treinamento; software nas linhas abaixo.</t>
   </si>
   <si>
     <t xml:space="preserve">Cenário</t>
@@ -217,12 +218,6 @@
     <t xml:space="preserve">Displays (A interno) + tags + leitor fixo e painel (opção indicada na B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Opcional, guia de coluna no baixo giro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 LED por prédio do baixo giro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Desenvolvimento de software (interno)</t>
   </si>
   <si>
@@ -242,6 +237,12 @@
   </si>
   <si>
     <t xml:space="preserve">B2 com contingência + software da Arquitetura B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POC (bancada + estações 04 e 27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware com contingência (aba POC); software da POC é interno</t>
   </si>
   <si>
     <t xml:space="preserve">Volume da operação (informado): ~3.000 volumes/dia e 250.000 a 270.000 produtos separados por dia.</t>
@@ -617,12 +618,12 @@
     <t xml:space="preserve">Comum</t>
   </si>
   <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
     <t xml:space="preserve">05</t>
   </si>
   <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
     <t xml:space="preserve">06</t>
   </si>
   <si>
@@ -830,7 +831,7 @@
     <t xml:space="preserve">Fonte Mean Well LRS-150-12 (12 V / 12,5 A / 150 W)</t>
   </si>
   <si>
-    <t xml:space="preserve">MCEIG (fontesmeanwell.com.br), 23/10/2026. Carga estimada &lt; 40 W por estação: folga para LED guia e expansão</t>
+    <t xml:space="preserve">MCEIG (fontesmeanwell.com.br), 23/10/2026. Carga estimada &lt; 40 W por estação: folga para expansão</t>
   </si>
   <si>
     <t xml:space="preserve">P07</t>
@@ -950,12 +951,18 @@
     <t xml:space="preserve">P21</t>
   </si>
   <si>
-    <t xml:space="preserve">Fita LED endereçável WS2812, guia de coluna (por LED) [opcional]</t>
+    <t xml:space="preserve">(não usado) LED guia de coluna, retirado em 26/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">LED</t>
   </si>
   <si>
+    <t xml:space="preserve">Não faz parte do projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirado</t>
+  </si>
+  <si>
     <t xml:space="preserve">P22</t>
   </si>
   <si>
@@ -1157,6 +1164,21 @@
     <t xml:space="preserve">Estimativa, cotar com a manutenção predial</t>
   </si>
   <si>
+    <t xml:space="preserve">P48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel de MDF 1,2 × 0,6 m com longarina para a bancada + parafusos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch 5 portas (bancada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimativa, cotar (ou porta livre de switch existente)</t>
+  </si>
+  <si>
     <t xml:space="preserve">P47</t>
   </si>
   <si>
@@ -1430,15 +1452,6 @@
     <t xml:space="preserve">SUBTOTAL MATERIAIS, variante 5 V</t>
   </si>
   <si>
-    <t xml:space="preserve">Opcional, guia de coluna no baixo giro (1 LED por prédio do baixo giro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEDs guia de coluna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prédios do baixo giro × (1 + reserva); ligados ao E+Q da zona</t>
-  </si>
-  <si>
     <t xml:space="preserve">T1, Placas próprias fabricadas e montadas por EMS (cada módulo com seu microcontrolador)</t>
   </si>
   <si>
@@ -1682,7 +1695,7 @@
     <t xml:space="preserve">Testes integrados, piloto e homologação</t>
   </si>
   <si>
-    <t xml:space="preserve">Inclui ajustes no piloto (estações 05 e 27)</t>
+    <t xml:space="preserve">Inclui ajustes na POC (estações 04 e 27)</t>
   </si>
   <si>
     <t xml:space="preserve">Documentação e treinamento</t>
@@ -1701,6 +1714,171 @@
   </si>
   <si>
     <t xml:space="preserve">Custo-hora de desenvolvimento calculado na aba Premissas (salário de mercado × encargos ÷ horas). É custo interno da equipe, não desembolso extra, a menos que o desenvolvimento seja contratado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POC: bancada + estações 04 e 27 (Arquitetura A, coletor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 1 valida o hardware e o software na bancada; fase 2 instala nas estações 04 (Medicamento) e 27 (Perfumaria). As estações da POC são as marcadas 'S' na aba Estações.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qtd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 1, bancada (1 coluna de alto giro, 1 zona de cada tipo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrador 12 V completo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gabinete, fonte, placa, alimentação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 prédio de alto giro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Módulos Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 andares (0 a 3) do prédio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 zona dos andares 4-5 + 1 zona do baixo giro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barra âmbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo Cat5e (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barramento e ligações da bancada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugs RJ45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel de MDF com longarina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simula a prateleira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch 5 portas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rede da bancada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compra única, servem para a fase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compra única, serve para a fase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% sobre os itens acima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montagem dos módulos (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conc. + nó + 4 Q + 2 E+Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testes de bancada (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acender, confirmar, falha, troca e cadastro de LED, 48 h de operação contínua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL FASE 1, bancada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fase 2, instalação nas estações 04 e 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiais, montagem, instalação e treinamento das 2 estações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aba A-Interno, coluna piloto (estações com 'S')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(−) Ferramentas já compradas na fase 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kit de rede + bancada de eletrônica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(−) Módulos da bancada reaproveitados na estação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o concentrador, o nó, os 4 Q e os 2 E+Q da bancada vão para a estação 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL FASE 2, estações 04 e 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARDWARE DA POC (fase 1 + fase 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% sobre o hardware da POC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARDWARE DA POC COM CONTINGÊNCIA (desembolso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software para a POC (equipe interna, versão mínima)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firmware do concentrador, dos nós e dos E+Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barramento, endereçamento, diagnóstico, cadastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serviço PTL, versão mínima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abrir e fechar caixa, acender, confirmar, sinal de baixo giro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integração Sybase (leitura dos itens da caixa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">views de leitura e gravação de eventos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App do coletor (A1), versão mínima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leitura com gatilho e progresso da caixa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface de controle, versão mínima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falhas de LED e cadastro por endereço</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testes da bancada e operação assistida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajustes durante a POC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFTWARE DA POC (horas e custo interno)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prazo estimado: bancada 3 a 4 semanas; instalação nas 2 estações 1 semana; operação assistida 4 semanas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O software da POC é a primeira parte do software do projeto (aba Software), não um custo a mais.</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +2051,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2043,6 +2221,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2545,27 +2727,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C2" s="20" t="n">
         <v>240</v>
@@ -2575,15 +2757,15 @@
         <v>24907.8773006135</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C3" s="20" t="n">
         <v>120</v>
@@ -2593,15 +2775,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>526</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>522</v>
       </c>
       <c r="C4" s="20" t="n">
         <v>60</v>
@@ -2611,15 +2793,15 @@
         <v>6226.96932515337</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>160</v>
@@ -2629,15 +2811,15 @@
         <v>16605.2515337423</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>80</v>
@@ -2647,15 +2829,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>120</v>
@@ -2665,15 +2847,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>100</v>
@@ -2683,15 +2865,15 @@
         <v>10378.282208589</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>80</v>
@@ -2701,15 +2883,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>120</v>
@@ -2719,15 +2901,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>40</v>
@@ -2737,15 +2919,15 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>24</v>
@@ -2755,15 +2937,15 @@
         <v>2490.78773006135</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>120</v>
@@ -2773,15 +2955,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>40</v>
@@ -2791,12 +2973,12 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="42" t="n">
@@ -2808,12 +2990,12 @@
         <v>118727.548466258</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="42" t="n">
@@ -2828,7 +3010,583 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>554</v>
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="37" t="n">
+        <f aca="false">Composição!$F$39</f>
+        <v>549.810425</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <f aca="false">C5*D5</f>
+        <v>549.810425</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="C6" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <f aca="false">Composição!$F$16</f>
+        <v>96.8</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <f aca="false">C6*D6</f>
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <f aca="false">Composição!$F$8</f>
+        <v>45.1417049180328</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <f aca="false">C7*D7</f>
+        <v>180.566819672131</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <f aca="false">Composição!$F$27</f>
+        <v>134.95</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <f aca="false">C8*D8</f>
+        <v>269.9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="37" t="n">
+        <f aca="false">Preços!$D$50</f>
+        <v>45</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <f aca="false">C9*D9</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <f aca="false">Preços!$D$13</f>
+        <v>4.03085245901639</v>
+      </c>
+      <c r="E10" s="31" t="n">
+        <f aca="false">C10*D10</f>
+        <v>80.6170491803279</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <f aca="false">Preços!$D$12</f>
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <f aca="false">C11*D11</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="37" t="n">
+        <f aca="false">Preços!$D$48</f>
+        <v>150</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <f aca="false">C12*D12</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>577</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="37" t="n">
+        <f aca="false">Preços!$D$49</f>
+        <v>90</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <f aca="false">C13*D13</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <f aca="false">Preços!$D$42</f>
+        <v>285.99</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <f aca="false">C14*D14</f>
+        <v>285.99</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="C15" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="37" t="n">
+        <f aca="false">Preços!$D$43</f>
+        <v>700</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <f aca="false">C15*D15</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="40" t="n">
+        <f aca="false">Premissas!$B$27</f>
+        <v>0.05</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <f aca="false">D16*SUM(E5:E15)</f>
+        <v>123.234214692623</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <f aca="false">Premissas!$B$15+Premissas!$B$13+4*Premissas!$B$12+2*Premissas!$B$14</f>
+        <v>5.75</v>
+      </c>
+      <c r="D17" s="37" t="n">
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <f aca="false">C17*D17</f>
+        <v>200.850674846626</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <f aca="false">C18*D18</f>
+        <v>558.888834355828</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="38" t="n">
+        <f aca="false">SUM(E5:E18)</f>
+        <v>3347.65801774754</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="37" t="n">
+        <f aca="false">'A-Interno'!F34</f>
+        <v>19211.4974214212</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="31" t="n">
+        <f aca="false">-('A-Interno'!F18+'A-Interno'!F19)*(1+Premissas!$B$27)</f>
+        <v>-1035.2895</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="31" t="n">
+        <f aca="false">-(Composição!$F$39+Composição!$F$16+4*Composição!$F$8+2*Composição!$F$27)</f>
+        <v>-1097.07724467213</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="38" t="n">
+        <f aca="false">SUM(E22:E24)</f>
+        <v>17079.1306767491</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="38" t="n">
+        <f aca="false">E19+E25</f>
+        <v>20426.7886944966</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="40" t="n">
+        <f aca="false">Premissas!$B$28</f>
+        <v>0.1</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <f aca="false">D28*E27</f>
+        <v>2042.67886944966</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="38" t="n">
+        <f aca="false">E27+E28</f>
+        <v>22469.4675639463</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>160</v>
+      </c>
+      <c r="D32" s="37" t="n">
+        <f aca="false">Premissas!$B$10</f>
+        <v>103.78282208589</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <f aca="false">C32*D32</f>
+        <v>16605.2515337423</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>160</v>
+      </c>
+      <c r="D33" s="37" t="n">
+        <f aca="false">Premissas!$B$10</f>
+        <v>103.78282208589</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <f aca="false">C33*D33</f>
+        <v>16605.2515337423</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="D34" s="37" t="n">
+        <f aca="false">Premissas!$B$10</f>
+        <v>103.78282208589</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <f aca="false">C34*D34</f>
+        <v>6226.96932515337</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="37" t="n">
+        <f aca="false">Premissas!$B$10</f>
+        <v>103.78282208589</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <f aca="false">C35*D35</f>
+        <v>10378.282208589</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="D36" s="37" t="n">
+        <f aca="false">Premissas!$B$10</f>
+        <v>103.78282208589</v>
+      </c>
+      <c r="E36" s="31" t="n">
+        <f aca="false">C36*D36</f>
+        <v>4151.31288343558</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>610</v>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="D37" s="37" t="n">
+        <f aca="false">Premissas!$B$10</f>
+        <v>103.78282208589</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <f aca="false">C37*D37</f>
+        <v>8302.62576687117</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="42" t="n">
+        <f aca="false">SUM(C32:C37)</f>
+        <v>600</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="38" t="n">
+        <f aca="false">SUM(E32:E37)</f>
+        <v>62269.6932515337</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -2847,7 +3605,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -3055,59 +3813,50 @@
         <v>364675.901003489</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="9" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <f aca="false">'A-Interno'!F43</f>
-        <v>49.5</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <f aca="false">'A-Interno'!G43</f>
-        <v>1016.1</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <f aca="false">D11/Estações!$O$43</f>
-        <v>25.4025</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <f aca="false">D11*(1+Premissas!$B$28)</f>
-        <v>1117.71</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>64</v>
+      <c r="B13" s="13" t="str">
+        <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
+        <v>Horas: 1,144</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <f aca="false">Software!D15</f>
+        <v>118727.548466258</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="13" t="str">
-        <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
-        <v>Horas: 1,144</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <f aca="false">Software!D15</f>
-        <v>118727.548466258</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="13" t="str">
         <f aca="false">"Horas: "&amp;TEXT(Software!C16,"#,##0")</f>
         <v>Horas: 1,064</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D14" s="10" t="n">
         <f aca="false">Software!D16</f>
         <v>110424.922699387</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17" t="n">
+        <f aca="false">F6+D13</f>
+        <v>453958.589699724</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3121,27 +3870,27 @@
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="17" t="n">
-        <f aca="false">F6+D14</f>
-        <v>453958.589699724</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+        <f aca="false">F10+D14</f>
+        <v>475100.823702875</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B19" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17" t="n">
-        <f aca="false">F10+D15</f>
-        <v>475100.823702875</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="C19" s="17" t="n">
+        <f aca="false">POC!E29</f>
+        <v>22469.4675639463</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3929,7 +4678,7 @@
         <v>192</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E3" s="25" t="n">
         <v>201</v>
@@ -3969,7 +4718,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>188</v>
@@ -3978,7 +4727,7 @@
         <v>192</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E4" s="25" t="n">
         <v>209</v>
@@ -4909,7 +5658,7 @@
         <v>192</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E23" s="25" t="n">
         <v>181</v>
@@ -5892,7 +6641,7 @@
       </c>
       <c r="E44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",E2:E41)</f>
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",F2:F41)</f>
@@ -5900,7 +6649,7 @@
       </c>
       <c r="G44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",G2:G41)</f>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",H2:H41)</f>
@@ -5908,7 +6657,7 @@
       </c>
       <c r="I44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",I2:I41)</f>
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",J2:J41)</f>
@@ -5920,7 +6669,7 @@
       </c>
       <c r="L44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",L2:L41)</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M44" s="29" t="n">
         <f aca="false">SUMIF($D$2:$D$41,"S",M2:M41)</f>
@@ -5972,7 +6721,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -6441,23 +7190,23 @@
       <c r="C22" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="D22" s="33" t="n">
-        <v>0.9</v>
+      <c r="D22" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>107</v>
+        <v>306</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>165</v>
@@ -6467,7 +7216,7 @@
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>248</v>
@@ -6475,10 +7224,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>165</v>
@@ -6496,10 +7245,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>165</v>
@@ -6509,7 +7258,7 @@
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>248</v>
@@ -6517,10 +7266,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>165</v>
@@ -6530,7 +7279,7 @@
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>248</v>
@@ -6538,10 +7287,10 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>294</v>
@@ -6559,10 +7308,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>165</v>
@@ -6580,10 +7329,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>165</v>
@@ -6601,10 +7350,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>165</v>
@@ -6617,7 +7366,7 @@
         <v>30</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>261</v>
@@ -6625,10 +7374,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>165</v>
@@ -6641,7 +7390,7 @@
         <v>65</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G31" s="34" t="s">
         <v>107</v>
@@ -6649,10 +7398,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>165</v>
@@ -6665,7 +7414,7 @@
         <v>220</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G32" s="34" t="s">
         <v>107</v>
@@ -6673,10 +7422,10 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>165</v>
@@ -6689,7 +7438,7 @@
         <v>9</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G33" s="34" t="s">
         <v>107</v>
@@ -6697,10 +7446,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>165</v>
@@ -6713,7 +7462,7 @@
         <v>22</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G34" s="34" t="s">
         <v>107</v>
@@ -6721,10 +7470,10 @@
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>165</v>
@@ -6737,7 +7486,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G35" s="34" t="s">
         <v>107</v>
@@ -6745,20 +7494,20 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D36" s="33" t="n">
         <v>15000</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G36" s="34" t="s">
         <v>107</v>
@@ -6766,10 +7515,10 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>165</v>
@@ -6782,7 +7531,7 @@
         <v>997</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>261</v>
@@ -6790,10 +7539,10 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>165</v>
@@ -6803,7 +7552,7 @@
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G38" s="34" t="s">
         <v>107</v>
@@ -6811,10 +7560,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>137</v>
@@ -6825,7 +7574,7 @@
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>248</v>
@@ -6833,10 +7582,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>165</v>
@@ -6854,10 +7603,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>165</v>
@@ -6875,10 +7624,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>294</v>
@@ -6888,7 +7637,7 @@
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>248</v>
@@ -6896,10 +7645,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>294</v>
@@ -6917,10 +7666,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>165</v>
@@ -6930,7 +7679,7 @@
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>248</v>
@@ -6938,10 +7687,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>294</v>
@@ -6951,7 +7700,7 @@
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G45" s="34" t="s">
         <v>107</v>
@@ -6959,10 +7708,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>165</v>
@@ -6980,10 +7729,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>165</v>
@@ -6993,7 +7742,7 @@
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G47" s="34" t="s">
         <v>107</v>
@@ -7001,22 +7750,64 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>45</v>
+        <v>150</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="9" t="s">
         <v>276</v>
       </c>
       <c r="G48" s="34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D49" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="G49" s="34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D50" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G50" s="34" t="s">
         <v>107</v>
       </c>
     </row>
@@ -7048,7 +7839,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>239</v>
@@ -7057,18 +7848,18 @@
         <v>240</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>245</v>
@@ -7091,7 +7882,7 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>271</v>
@@ -7114,7 +7905,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>283</v>
@@ -7137,7 +7928,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>274</v>
@@ -7160,7 +7951,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>280</v>
@@ -7183,7 +7974,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>277</v>
@@ -7206,7 +7997,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -7219,7 +8010,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>252</v>
@@ -7242,7 +8033,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>255</v>
@@ -7265,7 +8056,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>268</v>
@@ -7288,7 +8079,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>287</v>
@@ -7311,7 +8102,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>274</v>
@@ -7334,7 +8125,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>285</v>
@@ -7357,7 +8148,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -7370,7 +8161,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>249</v>
@@ -7393,7 +8184,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>245</v>
@@ -7416,7 +8207,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>252</v>
@@ -7439,7 +8230,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>255</v>
@@ -7462,7 +8253,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>268</v>
@@ -7485,7 +8276,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>271</v>
@@ -7508,7 +8299,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>274</v>
@@ -7531,7 +8322,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>285</v>
@@ -7554,7 +8345,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>287</v>
@@ -7577,7 +8368,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -7590,7 +8381,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>258</v>
@@ -7613,7 +8404,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>255</v>
@@ -7636,7 +8427,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>262</v>
@@ -7659,7 +8450,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>268</v>
@@ -7682,7 +8473,7 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>289</v>
@@ -7705,7 +8496,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>292</v>
@@ -7728,7 +8519,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>274</v>
@@ -7751,10 +8542,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C36" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B36,Preços!$A:$A,0))</f>
@@ -7774,10 +8565,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C37" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B37,Preços!$A:$A,0))</f>
@@ -7797,10 +8588,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C38" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B38,Preços!$A:$A,0))</f>
@@ -7820,7 +8611,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -7833,7 +8624,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>258</v>
@@ -7856,7 +8647,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>255</v>
@@ -7879,7 +8670,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>265</v>
@@ -7902,7 +8693,7 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>289</v>
@@ -7925,7 +8716,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>292</v>
@@ -7948,7 +8739,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>274</v>
@@ -7971,10 +8762,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C47" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B47,Preços!$A:$A,0))</f>
@@ -7994,10 +8785,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C48" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B48,Preços!$A:$A,0))</f>
@@ -8017,10 +8808,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C49" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B49,Preços!$A:$A,0))</f>
@@ -8040,7 +8831,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -8053,10 +8844,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C52" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B52,Preços!$A:$A,0))</f>
@@ -8076,10 +8867,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C53" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B53,Preços!$A:$A,0))</f>
@@ -8099,10 +8890,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C54" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B54,Preços!$A:$A,0))</f>
@@ -8122,10 +8913,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C55" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B55,Preços!$A:$A,0))</f>
@@ -8145,7 +8936,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -8158,10 +8949,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C58" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B58,Preços!$A:$A,0))</f>
@@ -8181,10 +8972,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C59" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B59,Preços!$A:$A,0))</f>
@@ -8204,7 +8995,7 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>271</v>
@@ -8227,7 +9018,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>252</v>
@@ -8250,7 +9041,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>255</v>
@@ -8273,7 +9064,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>268</v>
@@ -8296,7 +9087,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>287</v>
@@ -8319,7 +9110,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>274</v>
@@ -8342,7 +9133,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>285</v>
@@ -8365,7 +9156,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B67" s="13" t="s">
         <v>280</v>
@@ -8388,7 +9179,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>277</v>
@@ -8411,7 +9202,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -8424,10 +9215,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C71" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B71,Preços!$A:$A,0))</f>
@@ -8447,10 +9238,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C72" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B72,Preços!$A:$A,0))</f>
@@ -8470,7 +9261,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -8483,17 +9274,17 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -8512,7 +9303,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -8529,35 +9320,35 @@
         <v>240</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -8582,10 +9373,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$K$44*(1+Premissas!$B$26),0)</f>
@@ -8610,10 +9401,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -8638,10 +9429,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -8666,10 +9457,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -8694,10 +9485,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">Estações!$N$44*2+Estações!$O$44*4</f>
@@ -8722,10 +9513,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">Estações!$K$44*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$O$44*2*Premissas!$B$34+Estações!$O$44*Premissas!$B$35</f>
@@ -8750,10 +9541,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -8778,10 +9569,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -8792,7 +9583,7 @@
         <v>40</v>
       </c>
       <c r="E11" s="37" t="n">
-        <f aca="false">Preços!$D$48</f>
+        <f aca="false">Preços!$D$50</f>
         <v>45</v>
       </c>
       <c r="F11" s="31" t="n">
@@ -8806,10 +9597,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$36</f>
@@ -8834,10 +9625,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44/Premissas!$B$37,0)</f>
@@ -8862,10 +9653,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">C13</f>
@@ -8890,10 +9681,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">C13</f>
@@ -8918,10 +9709,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">C13*Premissas!$B$38</f>
@@ -8946,10 +9737,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$39,0)</f>
@@ -8974,10 +9765,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">1</f>
@@ -9002,10 +9793,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C19" s="39" t="n">
         <f aca="false">1</f>
@@ -9030,10 +9821,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -9052,7 +9843,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -9069,15 +9860,15 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C3*Premissas!$B$12</f>
@@ -9102,10 +9893,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C25" s="21" t="n">
         <f aca="false">C4*Premissas!$B$13</f>
@@ -9130,10 +9921,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C26" s="21" t="n">
         <f aca="false">C5*Premissas!$B$14</f>
@@ -9158,10 +9949,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C27" s="21" t="n">
         <f aca="false">C6*Premissas!$B$15</f>
@@ -9186,10 +9977,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$K$44*Premissas!$B$18+Estações!$M$44*Premissas!$B$19+C9*Premissas!$B$20)*Premissas!$B$22</f>
@@ -9214,10 +10005,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$21*Premissas!$B$22</f>
@@ -9242,10 +10033,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C30" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$23*Premissas!$B$24</f>
@@ -9270,10 +10061,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C31" s="21" t="n">
         <f aca="false">Premissas!$B$25</f>
@@ -9298,7 +10089,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="41" t="n">
@@ -9321,7 +10112,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -9338,15 +10129,15 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C37" s="39" t="n">
         <f aca="false">-(C4+C5+C6)</f>
@@ -9371,10 +10162,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C38" s="39" t="n">
         <f aca="false">C6</f>
@@ -9399,10 +10190,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C39" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$42</f>
@@ -9427,7 +10218,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -9440,39 +10231,6 @@
       <c r="G40" s="38" t="n">
         <f aca="false">G21+SUM(G37:G39)</f>
         <v>227135.487797295</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="C43" s="39" t="n">
-        <f aca="false">ROUNDUP(Estações!$L$44*(1+Premissas!$B$26),0)</f>
-        <v>55</v>
-      </c>
-      <c r="D43" s="39" t="n">
-        <f aca="false">ROUNDUP(Estações!$L$43*(1+Premissas!$B$26),0)</f>
-        <v>1129</v>
-      </c>
-      <c r="E43" s="37" t="n">
-        <f aca="false">Preços!$D$22</f>
-        <v>0.9</v>
-      </c>
-      <c r="F43" s="31" t="n">
-        <f aca="false">C43*E43</f>
-        <v>49.5</v>
-      </c>
-      <c r="G43" s="31" t="n">
-        <f aca="false">D43*E43</f>
-        <v>1016.1</v>
       </c>
     </row>
   </sheetData>
@@ -9508,35 +10266,35 @@
         <v>240</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9561,10 +10319,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -9589,10 +10347,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -9617,10 +10375,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -9645,10 +10403,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
@@ -9673,10 +10431,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -9692,10 +10450,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">1</f>
@@ -9720,10 +10478,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">(C3+C4+C5)*Premissas!$B$44</f>
@@ -9748,10 +10506,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
@@ -9776,10 +10534,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -9795,7 +10553,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -9812,15 +10570,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9845,10 +10603,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -9873,7 +10631,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>155</v>
@@ -9901,7 +10659,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>155</v>
@@ -9929,10 +10687,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C20" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -9957,10 +10715,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C21" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
@@ -9985,10 +10743,10 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -10004,10 +10762,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
@@ -10032,10 +10790,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -10051,7 +10809,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -10068,7 +10826,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -10103,35 +10861,35 @@
         <v>240</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -10147,10 +10905,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Premissas!$B$40*Estações!$O$44/Estações!$O$43,0)</f>
@@ -10175,10 +10933,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">C4*30/3600</f>
@@ -10203,15 +10961,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$41,0)</f>
@@ -10236,10 +10994,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10264,10 +11022,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">C8*1.5</f>
@@ -10292,7 +11050,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -10309,15 +11067,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10342,10 +11100,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">C14*2</f>
@@ -10370,7 +11128,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -10387,10 +11145,10 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">C8</f>
@@ -10415,7 +11173,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Composição" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="A-Interno" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="A-Terceiros" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="B-RFID" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="RFID-futuro" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Software" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="POC" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
@@ -30,12 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="596">
   <si>
     <t xml:space="preserve">Orçamento do projeto Pick-to-Light (flow rack)</t>
   </si>
   <si>
-    <t xml:space="preserve">Arquitetura A (coletor + concentrador + displays) e Arquitetura B (identificação por RFID). Revisão 26/10/2026.</t>
+    <t xml:space="preserve">Arquitetura A: coletor MovFast + concentrador + displays. RFID com pulseira fica como melhoria futura. Revisão 26/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">COMO USAR</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">A-Terceiros: Arquitetura A com produção de terceiros: (T1) placa própria montada por EMS e (T2) PTL comercial importado.</t>
   </si>
   <si>
-    <t xml:space="preserve">B-RFID: Arquitetura B: mesma infraestrutura de displays + identificação RFID (B1 pulseira, B2 leitor fixo).</t>
+    <t xml:space="preserve">RFID-futuro: melhoria futura, fora da POC e da implantação inicial: tag na caixa + pulseira NFC (acréscimo sobre a Arquitetura A).</t>
   </si>
   <si>
     <t xml:space="preserve">Software: esforço estimado de desenvolvimento (horas) para as duas arquiteturas.</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">• Treinamento de operadores e manutenção incluído em todos os cenários.</t>
   </si>
   <si>
-    <t xml:space="preserve">• B1: 2 pulseiras por estação (a bateria de 500 mAh não cobre um turno inteiro com leitura contínua) + carregador.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• B2: o leitor fixo vira um nó do barramento RS-485 (microcontrolador próprio), sem ligação I2C longa até o concentrador.</t>
+    <t xml:space="preserve">• RFID (melhoria futura): 2 pulseiras por estação (a bateria de 500 mAh não cobre um turno inteiro com leitura contínua) + carregador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Leitor fixo na estação (antiga opção B2) retirado do projeto; o foco é o coletor, e o RFID com pulseira fica como melhoria futura.</t>
   </si>
   <si>
     <t xml:space="preserve">• T1: horas de montagem final/gravação dos módulos vindos da EMS; T1/T2: cabo em cadeia dos módulos Q com 1 m por módulo.</t>
@@ -206,16 +206,10 @@
     <t xml:space="preserve">Hardware PTL pronto + instalação</t>
   </si>
   <si>
-    <t xml:space="preserve">B1, RFID com pulseira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Displays (A interno) + tags + pulseiras NFC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2, RFID com leitor fixo na estação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Displays (A interno) + tags + leitor fixo e painel (opção indicada na B)</t>
+    <t xml:space="preserve">Melhoria futura: RFID com pulseira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acréscimo sobre a A: tags nas caixas + pulseiras (não incluído no investimento)</t>
   </si>
   <si>
     <t xml:space="preserve">Desenvolvimento de software (interno)</t>
@@ -224,7 +218,7 @@
     <t xml:space="preserve">Arquitetura A (app próprio)</t>
   </si>
   <si>
-    <t xml:space="preserve">Arquitetura B</t>
+    <t xml:space="preserve">Melhoria futura: RFID (acréscimo)</t>
   </si>
   <si>
     <t xml:space="preserve">Investimento total, Arquitetura A (proposta)</t>
@@ -233,12 +227,6 @@
     <t xml:space="preserve">A interno com contingência + software da Arquitetura A</t>
   </si>
   <si>
-    <t xml:space="preserve">Investimento total, Arquitetura B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2 com contingência + software da Arquitetura B</t>
-  </si>
-  <si>
     <t xml:space="preserve">POC (bancada + estações 04 e 27)</t>
   </si>
   <si>
@@ -515,7 +503,7 @@
     <t xml:space="preserve">CONFIRMAR com a manutenção predial</t>
   </si>
   <si>
-    <t xml:space="preserve">Frota de caixas retornáveis (Arq. B)</t>
+    <t xml:space="preserve">Frota de caixas retornáveis (RFID, melhoria futura)</t>
   </si>
   <si>
     <t xml:space="preserve">caixas</t>
@@ -524,7 +512,7 @@
     <t xml:space="preserve">Estimativa: ~1,7 × 3.000 volumes/dia. CONFIRMAR com a operação.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulseiras por estação (Arq. B1)</t>
+    <t xml:space="preserve">Pulseiras por estação (RFID, melhoria futura)</t>
   </si>
   <si>
     <t xml:space="preserve">un</t>
@@ -1008,12 +996,6 @@
     <t xml:space="preserve">Carcaça 3D + pulseira velcro</t>
   </si>
   <si>
-    <t xml:space="preserve">P28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display LCD 20×4 I2C (painel da estação, Arq. B2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">P29</t>
   </si>
   <si>
@@ -1086,15 +1068,6 @@
     <t xml:space="preserve">atlasRFIDstore, US$ 997, 22/10/2026 (UHF; não lê tags NFC)</t>
   </si>
   <si>
-    <t xml:space="preserve">P37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leitor HF/NFC fixo industrial (USB/RS-232), alternativa comercial ao PN532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimativa, cotar (ex.: ACS ACR122U ou similar)</t>
-  </si>
-  <si>
     <t xml:space="preserve">P38</t>
   </si>
   <si>
@@ -1152,7 +1125,7 @@
     <t xml:space="preserve">P45</t>
   </si>
   <si>
-    <t xml:space="preserve">Carregador USB 2 portas para pulseiras (Arq. B1)</t>
+    <t xml:space="preserve">Carregador USB 2 portas para pulseiras (RFID futuro)</t>
   </si>
   <si>
     <t xml:space="preserve">P46</t>
@@ -1227,22 +1200,16 @@
     <t xml:space="preserve">Custo unitário, Concentrador 5 V</t>
   </si>
   <si>
-    <t xml:space="preserve">Pulseira RFID (B1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo unitário, Pulseira RFID (B1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leitor fixo + painel (B2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo unitário, Leitor fixo + painel (B2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tag por caixa (B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custo unitário, Tag por caixa (B)</t>
+    <t xml:space="preserve">Pulseira RFID (futuro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo unitário, Pulseira RFID (futuro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tag por caixa (RFID futuro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo unitário, Tag por caixa (RFID futuro)</t>
   </si>
   <si>
     <t xml:space="preserve">Variante 5 V: os módulos e nós não usam regulador step-down (P08); o custo é descontado na aba A-Interno.</t>
@@ -1251,9 +1218,6 @@
     <t xml:space="preserve">Concentrador: inclui alimentação até a tomada (3 m de cabo PP, plugue) e protetor de surto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Leitor fixo (B2): tem microcontrolador e RS-485 próprios e entra no barramento como mais um nó (cabo de 5 m).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Base de cálculo</t>
   </si>
   <si>
@@ -1530,13 +1494,7 @@
     <t xml:space="preserve">Valores em US$ convertidos por câmbio × fator de importação (aba Premissas). Itens de PTL comercial sem preço público devem ser cotados com fornecedores (ex.: ATOP, Aioi, fornecedores nacionais). Frete nacional não aplicado aqui: os itens principais são importados (frete no fator de importação).</t>
   </si>
   <si>
-    <t xml:space="preserve">Arquitetura B = infraestrutura de displays da Arquitetura A + identificação da caixa por RFID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infraestrutura de displays (Arquitetura A interna, materiais + mão de obra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aba A-Interno</t>
+    <t xml:space="preserve">Melhoria futura (não entra na POC nem na implantação inicial): tag NFC na caixa + pulseira no operador</t>
   </si>
   <si>
     <t xml:space="preserve">Tags NFC nas caixas retornáveis (frota)</t>
@@ -1551,9 +1509,6 @@
     <t xml:space="preserve">30 s por caixa</t>
   </si>
   <si>
-    <t xml:space="preserve">B1, Pulseira NFC (montagem própria)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pulseiras NFC (ESP32-C3 + PN532 + bateria)</t>
   </si>
   <si>
@@ -1572,22 +1527,13 @@
     <t xml:space="preserve">1,5 h por pulseira</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL B1, displays + tags + pulseiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B2, Leitor fixo na estação + painel (sem item no corpo do operador)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leitor PN532 + LCD 20×4 + botão Fechar (nó do barramento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montagem e instalação do leitor (h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 h por estação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL B2, displays + tags + leitor fixo</t>
+    <t xml:space="preserve">ACRÉSCIMO DO RFID sobre a Arquitetura A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referência: Arquitetura A + RFID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aba A-Interno + acréscimo acima</t>
   </si>
   <si>
     <t xml:space="preserve">Referência de mercado, leitor de pulso comercial</t>
@@ -1596,7 +1542,7 @@
     <t xml:space="preserve">FEIG HyWEAR (UHF) por pulseira, não lê NFC; exigiria tags UHF</t>
   </si>
   <si>
-    <t xml:space="preserve">Coletores MovFast já existentes não entram no custo (Arquitetura A). Na Arquitetura B eles deixam de ser necessários na separação, mas continuam disponíveis para as demais operações.</t>
+    <t xml:space="preserve">O hardware e o software da Arquitetura A já ficam preparados para receber a leitura RFID depois. O leitor fixo na estação (antiga opção B2) foi retirado do projeto em 26/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Componente</t>
@@ -1665,13 +1611,13 @@
     <t xml:space="preserve">Protocolo de barramento, endereçamento, auto-teste</t>
   </si>
   <si>
-    <t xml:space="preserve">Leitura RFID no concentrador + painel da estação (B2) / pulseira (B1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somente Arquitetura B</t>
+    <t xml:space="preserve">Leitura RFID pela pulseira (melhoria futura)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fora do escopo inicial</t>
   </si>
   <si>
     <t xml:space="preserve">Painel de monitoramento (gestão e TI)</t>
@@ -1710,7 +1656,7 @@
     <t xml:space="preserve">Com a tela no WMS (A2) no lugar do app: troque o item A1 (160 h) pelo A2 (80 h).</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL, Arquitetura B</t>
+    <t xml:space="preserve">Melhoria futura: acréscimo do RFID</t>
   </si>
   <si>
     <t xml:space="preserve">Custo-hora de desenvolvimento calculado na aba Premissas (salário de mercado × encargos ÷ horas). É custo interno da equipe, não desembolso extra, a menos que o desenvolvimento seja contratado.</t>
@@ -2492,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2727,27 +2673,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C2" s="20" t="n">
         <v>240</v>
@@ -2757,15 +2703,15 @@
         <v>24907.8773006135</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C3" s="20" t="n">
         <v>120</v>
@@ -2775,15 +2721,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C4" s="20" t="n">
         <v>60</v>
@@ -2793,15 +2739,15 @@
         <v>6226.96932515337</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>160</v>
@@ -2811,15 +2757,15 @@
         <v>16605.2515337423</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>80</v>
@@ -2829,15 +2775,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>120</v>
@@ -2847,15 +2793,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>100</v>
@@ -2865,15 +2811,15 @@
         <v>10378.282208589</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>80</v>
@@ -2883,15 +2829,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>120</v>
@@ -2901,15 +2847,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>40</v>
@@ -2919,15 +2865,15 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>24</v>
@@ -2937,15 +2883,15 @@
         <v>2490.78773006135</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>120</v>
@@ -2955,15 +2901,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>40</v>
@@ -2973,12 +2919,12 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="42" t="n">
@@ -2990,27 +2936,27 @@
         <v>118727.548466258</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="42" t="n">
-        <f aca="false">SUMIF(B2:B14,"A e B",C2:C14)+SUMIF(B2:B14,"B",C2:C14)</f>
-        <v>1064</v>
+        <f aca="false">SUMIF(B2:B14,"RFID",C2:C14)</f>
+        <v>80</v>
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">C16*Premissas!$B$10</f>
-        <v>110424.922699387</v>
+        <v>8302.62576687117</v>
       </c>
       <c r="E16" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -3040,42 +2986,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>1</v>
@@ -3091,10 +3037,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>1</v>
@@ -3110,10 +3056,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>4</v>
@@ -3129,10 +3075,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>2</v>
@@ -3148,16 +3094,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="37" t="n">
-        <f aca="false">Preços!$D$50</f>
+        <f aca="false">Preços!$D$48</f>
         <v>45</v>
       </c>
       <c r="E9" s="31" t="n">
@@ -3167,10 +3113,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>20</v>
@@ -3186,7 +3132,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="43" t="n">
@@ -3203,16 +3149,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="C12" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="37" t="n">
-        <f aca="false">Preços!$D$48</f>
+        <f aca="false">Preços!$D$46</f>
         <v>150</v>
       </c>
       <c r="E12" s="31" t="n">
@@ -3222,16 +3168,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="C13" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="37" t="n">
-        <f aca="false">Preços!$D$49</f>
+        <f aca="false">Preços!$D$47</f>
         <v>90</v>
       </c>
       <c r="E13" s="31" t="n">
@@ -3241,16 +3187,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="C14" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="37" t="n">
-        <f aca="false">Preços!$D$42</f>
+        <f aca="false">Preços!$D$40</f>
         <v>285.99</v>
       </c>
       <c r="E14" s="31" t="n">
@@ -3260,16 +3206,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="C15" s="43" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="37" t="n">
-        <f aca="false">Preços!$D$43</f>
+        <f aca="false">Preços!$D$41</f>
         <v>700</v>
       </c>
       <c r="E15" s="31" t="n">
@@ -3279,10 +3225,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="40" t="n">
@@ -3296,10 +3242,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="C17" s="21" t="n">
         <f aca="false">Premissas!$B$15+Premissas!$B$13+4*Premissas!$B$12+2*Premissas!$B$14</f>
@@ -3316,10 +3262,10 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="C18" s="18" t="n">
         <v>16</v>
@@ -3335,7 +3281,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -3347,15 +3293,15 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -3366,10 +3312,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -3380,10 +3326,10 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -3394,7 +3340,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -3406,7 +3352,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -3418,10 +3364,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="40" t="n">
@@ -3435,7 +3381,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -3447,15 +3393,15 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="C32" s="20" t="n">
         <v>160</v>
@@ -3471,10 +3417,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="C33" s="20" t="n">
         <v>160</v>
@@ -3490,10 +3436,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="C34" s="20" t="n">
         <v>60</v>
@@ -3509,10 +3455,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="C35" s="20" t="n">
         <v>100</v>
@@ -3528,10 +3474,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="C36" s="20" t="n">
         <v>40</v>
@@ -3547,10 +3493,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="C37" s="20" t="n">
         <v>80</v>
@@ -3566,7 +3512,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="42" t="n">
@@ -3581,12 +3527,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -3605,7 +3551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -3765,7 +3711,7 @@
         <v>839437.489994254</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
         <v>58</v>
       </c>
@@ -3773,125 +3719,86 @@
         <v>59</v>
       </c>
       <c r="C9" s="10" t="n">
-        <f aca="false">'B-RFID'!F11</f>
-        <v>20971.4485461656</v>
+        <f aca="false">'RFID-futuro'!F8</f>
+        <v>1759.95112474438</v>
       </c>
       <c r="D9" s="10" t="n">
-        <f aca="false">'B-RFID'!G11</f>
-        <v>337795.284586661</v>
+        <f aca="false">'RFID-futuro'!G8</f>
+        <v>33039.7925562372</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/Estações!$O$43</f>
-        <v>8444.88211466653</v>
+        <v>825.99481390593</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">D9*(1+Premissas!$B$28)</f>
-        <v>371574.813045327</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+        <v>36343.7718118609</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="9" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <f aca="false">'B-RFID'!F16</f>
-        <v>20549.9001382404</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <f aca="false">'B-RFID'!G16</f>
-        <v>331523.546366808</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <f aca="false">D10/Estações!$O$43</f>
-        <v>8288.0886591702</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <f aca="false">D10*(1+Premissas!$B$28)</f>
-        <v>364675.901003489</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>62</v>
+      <c r="B12" s="13" t="str">
+        <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
+        <v>Horas: 1,144</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <f aca="false">Software!D15</f>
+        <v>118727.548466258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="13" t="str">
+        <f aca="false">"Horas: "&amp;TEXT(Software!C16,"#,##0")</f>
+        <v>Horas: 80</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <f aca="false">Software!D16</f>
+        <v>8302.62576687117</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="13" t="str">
-        <f aca="false">"Horas: "&amp;TEXT(Software!C15,"#,##0")</f>
-        <v>Horas: 1,144</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <f aca="false">Software!D15</f>
-        <v>118727.548466258</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="B15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="13" t="str">
-        <f aca="false">"Horas: "&amp;TEXT(Software!C16,"#,##0")</f>
-        <v>Horas: 1,064</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <f aca="false">Software!D16</f>
-        <v>110424.922699387</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17" t="n">
-        <f aca="false">F6+D13</f>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17" t="n">
+        <f aca="false">F6+D12</f>
         <v>453958.589699724</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="16"/>
+        <v>66</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <f aca="false">POC!E29</f>
+        <v>22469.4675639463</v>
+      </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
-      <c r="F17" s="17" t="n">
-        <f aca="false">F10+D14</f>
-        <v>475100.823702875</v>
-      </c>
+      <c r="F17" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="17" t="n">
-        <f aca="false">POC!E29</f>
-        <v>22469.4675639463</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>71</v>
+      <c r="A19" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3921,621 +3828,621 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>5.0371</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B3" s="19" t="n">
         <v>1.9</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>2846.84</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>8458.3</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>2009.59</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>163</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">$B$4*$B$7/$B$8</f>
         <v>34.9305521472393</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="false">$B$5*$B$7/$B$8</f>
         <v>103.78282208589</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">$B$6*$B$7/$B$8</f>
         <v>24.6575460122699</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>0.75</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B14" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B16" s="20" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>0.15</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B18" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>0.35</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>0.08</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B22" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>16</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B26" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B27" s="22" t="n">
         <v>0.05</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B28" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B29" s="20" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B30" s="20" t="n">
         <v>6</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B31" s="19" t="n">
         <v>0.25</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B32" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B33" s="19" t="n">
         <v>1.2</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B34" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B35" s="20" t="n">
         <v>6</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B36" s="20" t="n">
         <v>50</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B37" s="20" t="n">
         <v>22</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B38" s="20" t="n">
         <v>80</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B39" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B40" s="20" t="n">
         <v>5000</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B41" s="19" t="n">
         <v>2.2</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B42" s="20" t="n">
         <v>30</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B43" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B44" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4573,63 +4480,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E2" s="25" t="n">
         <v>131</v>
@@ -4669,16 +4576,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B3" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D3" s="24" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E3" s="25" t="n">
         <v>201</v>
@@ -4718,16 +4625,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D4" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E4" s="25" t="n">
         <v>209</v>
@@ -4767,16 +4674,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B5" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D5" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>209</v>
@@ -4816,16 +4723,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B6" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D6" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>209</v>
@@ -4865,16 +4772,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B7" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D7" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E7" s="25" t="n">
         <v>205</v>
@@ -4914,16 +4821,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>241</v>
@@ -4963,16 +4870,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E9" s="25" t="n">
         <v>237</v>
@@ -5012,16 +4919,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B10" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D10" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E10" s="25" t="n">
         <v>205</v>
@@ -5061,16 +4968,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B11" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D11" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E11" s="25" t="n">
         <v>209</v>
@@ -5110,16 +5017,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B12" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D12" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E12" s="25" t="n">
         <v>203</v>
@@ -5159,16 +5066,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B13" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D13" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E13" s="25" t="n">
         <v>209</v>
@@ -5208,16 +5115,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E14" s="25" t="n">
         <v>231</v>
@@ -5257,16 +5164,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E15" s="25" t="n">
         <v>237</v>
@@ -5306,16 +5213,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B16" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D16" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E16" s="25" t="n">
         <v>205</v>
@@ -5355,16 +5262,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B17" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D17" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E17" s="25" t="n">
         <v>209</v>
@@ -5404,16 +5311,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B18" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D18" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E18" s="25" t="n">
         <v>203</v>
@@ -5453,16 +5360,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B19" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D19" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E19" s="25" t="n">
         <v>209</v>
@@ -5502,16 +5409,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B20" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>192</v>
-      </c>
       <c r="D20" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E20" s="25" t="n">
         <v>199</v>
@@ -5551,16 +5458,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E21" s="25" t="n">
         <v>43</v>
@@ -5600,16 +5507,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>176</v>
@@ -5649,16 +5556,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E23" s="25" t="n">
         <v>181</v>
@@ -5698,16 +5605,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E24" s="25" t="n">
         <v>181</v>
@@ -5747,16 +5654,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E25" s="25" t="n">
         <v>181</v>
@@ -5796,16 +5703,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E26" s="25" t="n">
         <v>179</v>
@@ -5845,16 +5752,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E27" s="25" t="n">
         <v>181</v>
@@ -5894,16 +5801,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E28" s="25" t="n">
         <v>280</v>
@@ -5943,16 +5850,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E29" s="25" t="n">
         <v>277</v>
@@ -5992,16 +5899,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E30" s="25" t="n">
         <v>179</v>
@@ -6041,16 +5948,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>181</v>
@@ -6090,16 +5997,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E32" s="25" t="n">
         <v>177</v>
@@ -6139,16 +6046,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E33" s="25" t="n">
         <v>181</v>
@@ -6188,16 +6095,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E34" s="25" t="n">
         <v>274</v>
@@ -6237,16 +6144,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E35" s="25" t="n">
         <v>277</v>
@@ -6286,16 +6193,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E36" s="25" t="n">
         <v>179</v>
@@ -6335,16 +6242,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E37" s="25" t="n">
         <v>181</v>
@@ -6384,16 +6291,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E38" s="25" t="n">
         <v>177</v>
@@ -6433,16 +6340,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E39" s="25" t="n">
         <v>181</v>
@@ -6482,16 +6389,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E40" s="25" t="n">
         <v>173</v>
@@ -6531,16 +6438,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E41" s="25" t="n">
         <v>181</v>
@@ -6580,7 +6487,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="27" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D43" s="28" t="n">
         <f aca="false">COUNTA(A2:A41)</f>
@@ -6633,7 +6540,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D44" s="28" t="n">
         <f aca="false">COUNTIF(D2:D41,"S")</f>
@@ -6686,17 +6593,17 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -6721,7 +6628,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -6735,120 +6642,120 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D2" s="30" t="n">
         <v>9.98</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="9" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D3" s="30" t="n">
         <v>20.17</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>39.9</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>8.9</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="9" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D6" s="31" t="n">
         <f aca="false">E6*Premissas!$B$2*Premissas!$B$3</f>
@@ -6858,147 +6765,147 @@
         <v>12.5</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D7" s="30" t="n">
         <v>189.98</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>185</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D9" s="33" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>18</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D11" s="33" t="n">
         <v>2.5</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>0.8</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D13" s="31" t="n">
         <f aca="false">1229.41/305</f>
@@ -7006,809 +6913,767 @@
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D14" s="33" t="n">
         <v>5</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D15" s="33" t="n">
         <v>15</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D16" s="33" t="n">
         <v>10</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>90</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>45</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D19" s="33" t="n">
         <v>9</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D20" s="33" t="n">
         <v>40</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>769.32</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D22" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D23" s="30" t="n">
         <v>2.37</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D24" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D25" s="30" t="n">
         <v>29.89</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D26" s="30" t="n">
         <v>42.65</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D27" s="33" t="n">
         <v>35</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D28" s="33" t="n">
         <v>20</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="33" t="n">
-        <v>35</v>
-      </c>
-      <c r="E29" s="13"/>
+        <v>161</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <f aca="false">E29*Premissas!$B$2*Premissas!$B$3</f>
+        <v>287.1147</v>
+      </c>
+      <c r="E29" s="32" t="n">
+        <v>30</v>
+      </c>
       <c r="F29" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>107</v>
+        <v>321</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D30" s="31" t="n">
         <f aca="false">E30*Premissas!$B$2*Premissas!$B$3</f>
-        <v>287.1147</v>
-      </c>
-      <c r="E30" s="32" t="n">
-        <v>30</v>
+        <v>622.08185</v>
+      </c>
+      <c r="E30" s="35" t="n">
+        <v>65</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>261</v>
+        <v>324</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D31" s="31" t="n">
         <f aca="false">E31*Premissas!$B$2*Premissas!$B$3</f>
-        <v>622.08185</v>
+        <v>2105.5078</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D32" s="31" t="n">
         <f aca="false">E32*Premissas!$B$2*Premissas!$B$3</f>
-        <v>2105.5078</v>
+        <v>86.13441</v>
       </c>
       <c r="E32" s="35" t="n">
-        <v>220</v>
+        <v>9</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D33" s="31" t="n">
         <f aca="false">E33*Premissas!$B$2*Premissas!$B$3</f>
-        <v>86.13441</v>
+        <v>210.55078</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D34" s="31" t="n">
         <f aca="false">E34*Premissas!$B$2*Premissas!$B$3</f>
-        <v>210.55078</v>
+        <v>334.96715</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D35" s="31" t="n">
-        <f aca="false">E35*Premissas!$B$2*Premissas!$B$3</f>
-        <v>334.96715</v>
-      </c>
-      <c r="E35" s="35" t="n">
-        <v>35</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E35" s="13"/>
       <c r="F35" s="9" t="s">
         <v>339</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" s="31" t="n">
+        <f aca="false">E36*Premissas!$B$2*Premissas!$B$3</f>
+        <v>9541.77853</v>
+      </c>
+      <c r="E36" s="32" t="n">
+        <v>997</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="G36" s="13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="B37" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="D36" s="33" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="9" t="s">
+      <c r="C37" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="31" t="n">
+        <f aca="false">913.31/100</f>
+        <v>9.1331</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="G36" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+      <c r="G37" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B38" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" s="31" t="n">
-        <f aca="false">E37*Premissas!$B$2*Premissas!$B$3</f>
-        <v>9541.77853</v>
-      </c>
-      <c r="E37" s="32" t="n">
-        <v>997</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>350</v>
-      </c>
       <c r="C38" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D38" s="33" t="n">
-        <v>350</v>
+        <v>12</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="9" t="s">
-        <v>351</v>
+        <v>272</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="31" t="n">
-        <f aca="false">913.31/100</f>
-        <v>9.1331</v>
+        <v>161</v>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>35</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>272</v>
+      </c>
+      <c r="G39" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>12</v>
+        <v>290</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>285.99</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="G40" s="34" t="s">
-        <v>107</v>
+        <v>352</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="D41" s="33" t="n">
-        <v>35</v>
+        <v>700</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>294</v>
+        <v>161</v>
       </c>
       <c r="D42" s="30" t="n">
-        <v>285.99</v>
+        <v>368.1</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="9" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D43" s="33" t="n">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="9" t="s">
-        <v>276</v>
+        <v>360</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D44" s="30" t="n">
-        <v>368.1</v>
+        <v>161</v>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>35</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>248</v>
+        <v>272</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>294</v>
+        <v>161</v>
       </c>
       <c r="D45" s="33" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="9" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="D46" s="33" t="n">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="9" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>294</v>
+        <v>161</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D49" s="33" t="n">
-        <v>90</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="G49" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="G50" s="34" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -7827,7 +7692,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -7839,30 +7704,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C2" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B2,Preços!$A:$A,0))</f>
@@ -7882,10 +7747,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C3" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B3,Preços!$A:$A,0))</f>
@@ -7905,10 +7770,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C4" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B4,Preços!$A:$A,0))</f>
@@ -7928,10 +7793,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C5" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B5,Preços!$A:$A,0))</f>
@@ -7951,10 +7816,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C6" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B6,Preços!$A:$A,0))</f>
@@ -7974,10 +7839,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C7" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B7,Preços!$A:$A,0))</f>
@@ -7997,7 +7862,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -8010,10 +7875,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C10" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B10,Preços!$A:$A,0))</f>
@@ -8033,10 +7898,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C11" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B11,Preços!$A:$A,0))</f>
@@ -8056,10 +7921,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C12" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B12,Preços!$A:$A,0))</f>
@@ -8079,10 +7944,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C13" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B13,Preços!$A:$A,0))</f>
@@ -8102,10 +7967,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C14" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B14,Preços!$A:$A,0))</f>
@@ -8125,10 +7990,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C15" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B15,Preços!$A:$A,0))</f>
@@ -8148,7 +8013,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -8161,10 +8026,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C18" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B18,Preços!$A:$A,0))</f>
@@ -8184,10 +8049,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C19" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B19,Preços!$A:$A,0))</f>
@@ -8207,10 +8072,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C20" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B20,Preços!$A:$A,0))</f>
@@ -8230,10 +8095,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C21" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B21,Preços!$A:$A,0))</f>
@@ -8253,10 +8118,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C22" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B22,Preços!$A:$A,0))</f>
@@ -8276,10 +8141,10 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C23" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B23,Preços!$A:$A,0))</f>
@@ -8299,10 +8164,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C24" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B24,Preços!$A:$A,0))</f>
@@ -8322,10 +8187,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C25" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B25,Preços!$A:$A,0))</f>
@@ -8345,10 +8210,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C26" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B26,Preços!$A:$A,0))</f>
@@ -8368,7 +8233,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -8381,10 +8246,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C29" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B29,Preços!$A:$A,0))</f>
@@ -8404,10 +8269,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C30" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B30,Preços!$A:$A,0))</f>
@@ -8427,10 +8292,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C31" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B31,Preços!$A:$A,0))</f>
@@ -8450,10 +8315,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C32" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B32,Preços!$A:$A,0))</f>
@@ -8473,10 +8338,10 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C33" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B33,Preços!$A:$A,0))</f>
@@ -8496,10 +8361,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C34" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B34,Preços!$A:$A,0))</f>
@@ -8519,10 +8384,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C35" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B35,Preços!$A:$A,0))</f>
@@ -8542,10 +8407,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C36" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B36,Preços!$A:$A,0))</f>
@@ -8565,10 +8430,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C37" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B37,Preços!$A:$A,0))</f>
@@ -8588,10 +8453,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C38" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B38,Preços!$A:$A,0))</f>
@@ -8611,7 +8476,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -8624,10 +8489,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C41" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B41,Preços!$A:$A,0))</f>
@@ -8647,10 +8512,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C42" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B42,Preços!$A:$A,0))</f>
@@ -8670,10 +8535,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C43" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B43,Preços!$A:$A,0))</f>
@@ -8693,10 +8558,10 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C44" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B44,Preços!$A:$A,0))</f>
@@ -8716,10 +8581,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C45" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B45,Preços!$A:$A,0))</f>
@@ -8739,10 +8604,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C46" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B46,Preços!$A:$A,0))</f>
@@ -8762,10 +8627,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C47" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B47,Preços!$A:$A,0))</f>
@@ -8785,10 +8650,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C48" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B48,Preços!$A:$A,0))</f>
@@ -8808,10 +8673,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C49" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B49,Preços!$A:$A,0))</f>
@@ -8831,7 +8696,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -8844,10 +8709,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C52" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B52,Preços!$A:$A,0))</f>
@@ -8867,10 +8732,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C53" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B53,Preços!$A:$A,0))</f>
@@ -8890,10 +8755,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C54" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B54,Preços!$A:$A,0))</f>
@@ -8913,10 +8778,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C55" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B55,Preços!$A:$A,0))</f>
@@ -8936,7 +8801,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -8949,342 +8814,71 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C58" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B58,Preços!$A:$A,0))</f>
-        <v>Módulo leitor NFC PN532 (43×40 mm, com cartão e chaveiro)</v>
+        <v>Tag NFC NTAG213 adesiva 13,56 MHz</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E58" s="37" t="n">
         <f aca="false">INDEX(Preços!$D:$D,MATCH(B58,Preços!$A:$A,0))</f>
-        <v>42.65</v>
+        <v>2.37</v>
       </c>
       <c r="F58" s="31" t="n">
         <f aca="false">D58*E58</f>
-        <v>42.65</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C59" s="36" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B59,Preços!$A:$A,0))</f>
-        <v>Display LCD 20×4 I2C (painel da estação, Arq. B2)</v>
+        <v>Suporte/proteção da tag na caixa retornável</v>
       </c>
       <c r="D59" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E59" s="37" t="n">
         <f aca="false">INDEX(Preços!$D:$D,MATCH(B59,Preços!$A:$A,0))</f>
-        <v>35</v>
+        <v>0.5</v>
       </c>
       <c r="F59" s="31" t="n">
         <f aca="false">D59*E59</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="C60" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B60,Preços!$A:$A,0))</f>
-        <v>Botão de confirmação metálico 16 mm com anel de LED 12 V (momentâneo)</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B60,Preços!$A:$A,0))</f>
-        <v>18</v>
-      </c>
-      <c r="F60" s="31" t="n">
-        <f aca="false">D60*E60</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C61" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B61,Preços!$A:$A,0))</f>
-        <v>Microcontrolador Raspberry Pi Pico (RP2040)</v>
-      </c>
-      <c r="D61" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B61,Preços!$A:$A,0))</f>
-        <v>39.9</v>
-      </c>
-      <c r="F61" s="31" t="n">
-        <f aca="false">D61*E61</f>
-        <v>39.9</v>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="38" t="n">
+        <f aca="false">SUM(F58:F59)</f>
+        <v>2.87</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C62" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B62,Preços!$A:$A,0))</f>
-        <v>Módulo transceptor RS-485 (MAX485)</v>
-      </c>
-      <c r="D62" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B62,Preços!$A:$A,0))</f>
-        <v>8.9</v>
-      </c>
-      <c r="F62" s="31" t="n">
-        <f aca="false">D62*E62</f>
-        <v>8.9</v>
+      <c r="A62" s="6" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C63" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B63,Preços!$A:$A,0))</f>
-        <v>Regulador step-down 12 V → 5 V (mini, 3 A)</v>
-      </c>
-      <c r="D63" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B63,Preços!$A:$A,0))</f>
-        <v>8</v>
-      </c>
-      <c r="F63" s="31" t="n">
-        <f aca="false">D63*E63</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="C64" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B64,Preços!$A:$A,0))</f>
-        <v>Placa base universal + bornes (nó / módulo E+Q)</v>
-      </c>
-      <c r="D64" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B64,Preços!$A:$A,0))</f>
-        <v>10</v>
-      </c>
-      <c r="F64" s="31" t="n">
-        <f aca="false">D64*E64</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="C65" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B65,Preços!$A:$A,0))</f>
-        <v>Conector RJ45 fêmea para placa (jack)</v>
-      </c>
-      <c r="D65" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B65,Preços!$A:$A,0))</f>
-        <v>2.5</v>
-      </c>
-      <c r="F65" s="31" t="n">
-        <f aca="false">D65*E65</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="C66" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B66,Preços!$A:$A,0))</f>
-        <v>Carcaça do Módulo E+Q / Nó de coluna</v>
-      </c>
-      <c r="D66" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B66,Preços!$A:$A,0))</f>
-        <v>15</v>
-      </c>
-      <c r="F66" s="31" t="n">
-        <f aca="false">D66*E66</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C67" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B67,Preços!$A:$A,0))</f>
-        <v>Cabo Cat5e (por metro)</v>
-      </c>
-      <c r="D67" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B67,Preços!$A:$A,0))</f>
-        <v>4.03085245901639</v>
-      </c>
-      <c r="F67" s="31" t="n">
-        <f aca="false">D67*E67</f>
-        <v>20.154262295082</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="C68" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B68,Preços!$A:$A,0))</f>
-        <v>Plug RJ45 Cat5e (macho)</v>
-      </c>
-      <c r="D68" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B68,Preços!$A:$A,0))</f>
-        <v>0.8</v>
-      </c>
-      <c r="F68" s="31" t="n">
-        <f aca="false">D68*E68</f>
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="14" t="s">
-        <v>399</v>
-      </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="38" t="n">
-        <f aca="false">SUM(F58:F68)</f>
-        <v>204.204262295082</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="C71" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B71,Preços!$A:$A,0))</f>
-        <v>Tag NFC NTAG213 adesiva 13,56 MHz</v>
-      </c>
-      <c r="D71" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B71,Preços!$A:$A,0))</f>
-        <v>2.37</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <f aca="false">D71*E71</f>
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="C72" s="36" t="str">
-        <f aca="false">INDEX(Preços!$B:$B,MATCH(B72,Preços!$A:$A,0))</f>
-        <v>Suporte/proteção da tag na caixa retornável</v>
-      </c>
-      <c r="D72" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="37" t="n">
-        <f aca="false">INDEX(Preços!$D:$D,MATCH(B72,Preços!$A:$A,0))</f>
-        <v>0.5</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <f aca="false">D72*E72</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="38" t="n">
-        <f aca="false">SUM(F71:F72)</f>
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
-        <v>404</v>
+      <c r="A63" s="6" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -9317,38 +8911,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -9373,10 +8967,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$K$44*(1+Premissas!$B$26),0)</f>
@@ -9401,10 +8995,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -9429,10 +9023,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -9457,10 +9051,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -9485,10 +9079,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">Estações!$N$44*2+Estações!$O$44*4</f>
@@ -9513,10 +9107,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">Estações!$K$44*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$O$44*2*Premissas!$B$34+Estações!$O$44*Premissas!$B$35</f>
@@ -9541,10 +9135,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -9569,10 +9163,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -9583,7 +9177,7 @@
         <v>40</v>
       </c>
       <c r="E11" s="37" t="n">
-        <f aca="false">Preços!$D$50</f>
+        <f aca="false">Preços!$D$48</f>
         <v>45</v>
       </c>
       <c r="F11" s="31" t="n">
@@ -9597,10 +9191,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$36</f>
@@ -9625,10 +9219,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44/Premissas!$B$37,0)</f>
@@ -9653,10 +9247,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">C13</f>
@@ -9667,7 +9261,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="37" t="n">
-        <f aca="false">Preços!$D$44</f>
+        <f aca="false">Preços!$D$42</f>
         <v>368.1</v>
       </c>
       <c r="F14" s="31" t="n">
@@ -9681,10 +9275,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">C13</f>
@@ -9695,7 +9289,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="37" t="n">
-        <f aca="false">Preços!$D$45</f>
+        <f aca="false">Preços!$D$43</f>
         <v>550</v>
       </c>
       <c r="F15" s="31" t="n">
@@ -9709,10 +9303,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">C13*Premissas!$B$38</f>
@@ -9737,10 +9331,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$39,0)</f>
@@ -9751,7 +9345,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="37" t="n">
-        <f aca="false">Preços!$D$47</f>
+        <f aca="false">Preços!$D$45</f>
         <v>350</v>
       </c>
       <c r="F17" s="31" t="n">
@@ -9765,10 +9359,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">1</f>
@@ -9779,7 +9373,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">Preços!$D$42</f>
+        <f aca="false">Preços!$D$40</f>
         <v>285.99</v>
       </c>
       <c r="F18" s="31" t="n">
@@ -9793,10 +9387,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C19" s="39" t="n">
         <f aca="false">1</f>
@@ -9807,7 +9401,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">Preços!$D$43</f>
+        <f aca="false">Preços!$D$41</f>
         <v>700</v>
       </c>
       <c r="F19" s="31" t="n">
@@ -9821,10 +9415,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -9843,7 +9437,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -9860,15 +9454,15 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C3*Premissas!$B$12</f>
@@ -9893,10 +9487,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="C25" s="21" t="n">
         <f aca="false">C4*Premissas!$B$13</f>
@@ -9921,10 +9515,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C26" s="21" t="n">
         <f aca="false">C5*Premissas!$B$14</f>
@@ -9949,10 +9543,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C27" s="21" t="n">
         <f aca="false">C6*Premissas!$B$15</f>
@@ -9977,10 +9571,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$K$44*Premissas!$B$18+Estações!$M$44*Premissas!$B$19+C9*Premissas!$B$20)*Premissas!$B$22</f>
@@ -10005,10 +9599,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$21*Premissas!$B$22</f>
@@ -10033,10 +9627,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C30" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$23*Premissas!$B$24</f>
@@ -10061,10 +9655,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C31" s="21" t="n">
         <f aca="false">Premissas!$B$25</f>
@@ -10089,7 +9683,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="41" t="n">
@@ -10112,7 +9706,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -10129,15 +9723,15 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C37" s="39" t="n">
         <f aca="false">-(C4+C5+C6)</f>
@@ -10162,10 +9756,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="C38" s="39" t="n">
         <f aca="false">C6</f>
@@ -10190,10 +9784,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C39" s="39" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$42</f>
@@ -10204,7 +9798,7 @@
         <v>1200</v>
       </c>
       <c r="E39" s="37" t="n">
-        <f aca="false">Preços!$D$39</f>
+        <f aca="false">Preços!$D$37</f>
         <v>9.1331</v>
       </c>
       <c r="F39" s="31" t="n">
@@ -10218,7 +9812,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -10263,38 +9857,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C3" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -10305,7 +9899,7 @@
         <v>1408</v>
       </c>
       <c r="E3" s="37" t="n">
-        <f aca="false">Preços!$D$33+Preços!$D$14</f>
+        <f aca="false">Preços!$D$32+Preços!$D$14</f>
         <v>91.13441</v>
       </c>
       <c r="F3" s="31" t="n">
@@ -10319,10 +9913,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C4" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -10333,7 +9927,7 @@
         <v>277</v>
       </c>
       <c r="E4" s="37" t="n">
-        <f aca="false">Preços!$D$34+Preços!$D$15+Preços!$D$10</f>
+        <f aca="false">Preços!$D$33+Preços!$D$15+Preços!$D$10</f>
         <v>243.55078</v>
       </c>
       <c r="F4" s="31" t="n">
@@ -10347,10 +9941,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -10361,7 +9955,7 @@
         <v>44</v>
       </c>
       <c r="E5" s="37" t="n">
-        <f aca="false">Preços!$D$35+Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$39*3+Preços!$D$40*1+Preços!$D$41*1</f>
+        <f aca="false">Preços!$D$34+Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$37*3+Preços!$D$38*1+Preços!$D$39*1</f>
         <v>734.34645</v>
       </c>
       <c r="F5" s="31" t="n">
@@ -10375,10 +9969,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -10403,10 +9997,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
@@ -10431,10 +10025,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -10450,10 +10044,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">1</f>
@@ -10464,7 +10058,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="37" t="n">
-        <f aca="false">Preços!$D$36</f>
+        <f aca="false">Preços!$D$35</f>
         <v>15000</v>
       </c>
       <c r="F9" s="31" t="n">
@@ -10478,10 +10072,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">(C3+C4+C5)*Premissas!$B$44</f>
@@ -10506,10 +10100,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
@@ -10534,10 +10128,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -10553,7 +10147,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -10570,15 +10164,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -10589,7 +10183,7 @@
         <v>1408</v>
       </c>
       <c r="E16" s="37" t="n">
-        <f aca="false">Preços!$D$30</f>
+        <f aca="false">Preços!$D$29</f>
         <v>287.1147</v>
       </c>
       <c r="F16" s="31" t="n">
@@ -10603,10 +10197,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -10617,7 +10211,7 @@
         <v>277</v>
       </c>
       <c r="E17" s="37" t="n">
-        <f aca="false">Preços!$D$31</f>
+        <f aca="false">Preços!$D$30</f>
         <v>622.08185</v>
       </c>
       <c r="F17" s="31" t="n">
@@ -10631,10 +10225,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C18" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10645,7 +10239,7 @@
         <v>40</v>
       </c>
       <c r="E18" s="37" t="n">
-        <f aca="false">Preços!$D$32</f>
+        <f aca="false">Preços!$D$31</f>
         <v>2105.5078</v>
       </c>
       <c r="F18" s="31" t="n">
@@ -10659,10 +10253,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C19" s="39" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -10673,7 +10267,7 @@
         <v>40</v>
       </c>
       <c r="E19" s="37" t="n">
-        <f aca="false">Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$39*3+Preços!$D$40*1+Preços!$D$41*1</f>
+        <f aca="false">Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$37*3+Preços!$D$38*1+Preços!$D$39*1</f>
         <v>399.3793</v>
       </c>
       <c r="F19" s="31" t="n">
@@ -10687,10 +10281,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C20" s="39" t="n">
         <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -10715,10 +10309,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="C21" s="39" t="n">
         <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
@@ -10743,10 +10337,10 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
@@ -10762,10 +10356,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
@@ -10790,10 +10384,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -10809,7 +10403,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
@@ -10826,7 +10420,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -10845,7 +10439,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="48"/>
@@ -10858,322 +10452,239 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="37" t="n">
-        <f aca="false">'A-Interno'!F34</f>
-        <v>19211.4974214212</v>
-      </c>
-      <c r="G3" s="37" t="n">
-        <f aca="false">'A-Interno'!G34</f>
-        <v>304755.492030424</v>
+        <v>487</v>
+      </c>
+      <c r="C3" s="39" t="n">
+        <f aca="false">ROUNDUP(Premissas!$B$40*Estações!$O$44/Estações!$O$43,0)</f>
+        <v>250</v>
+      </c>
+      <c r="D3" s="39" t="n">
+        <f aca="false">Premissas!$B$40</f>
+        <v>5000</v>
+      </c>
+      <c r="E3" s="37" t="n">
+        <f aca="false">Composição!$F$60</f>
+        <v>2.87</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <f aca="false">C3*E3</f>
+        <v>717.5</v>
+      </c>
+      <c r="G3" s="31" t="n">
+        <f aca="false">D3*E3</f>
+        <v>14350</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="C4" s="39" t="n">
-        <f aca="false">ROUNDUP(Premissas!$B$40*Estações!$O$44/Estações!$O$43,0)</f>
-        <v>250</v>
-      </c>
-      <c r="D4" s="39" t="n">
-        <f aca="false">Premissas!$B$40</f>
-        <v>5000</v>
+        <v>489</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <f aca="false">C3*30/3600</f>
+        <v>2.08333333333333</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <f aca="false">D3*30/3600</f>
+        <v>41.6666666666667</v>
       </c>
       <c r="E4" s="37" t="n">
-        <f aca="false">Composição!$F$73</f>
-        <v>2.87</v>
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
       </c>
       <c r="F4" s="31" t="n">
         <f aca="false">C4*E4</f>
-        <v>717.5</v>
+        <v>72.7719836400818</v>
       </c>
       <c r="G4" s="31" t="n">
         <f aca="false">D4*E4</f>
-        <v>14350</v>
+        <v>1455.43967280164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <f aca="false">C4*30/3600</f>
-        <v>2.08333333333333</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <f aca="false">D4*30/3600</f>
-        <v>41.6666666666667</v>
+        <v>491</v>
+      </c>
+      <c r="C5" s="39" t="n">
+        <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$41,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D5" s="39" t="n">
+        <f aca="false">ROUNDUP(Estações!$O$43*Premissas!$B$41,0)</f>
+        <v>88</v>
       </c>
       <c r="E5" s="37" t="n">
+        <f aca="false">Composição!$F$56</f>
+        <v>127.54</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <f aca="false">C5*E5</f>
+        <v>637.7</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <f aca="false">D5*E5</f>
+        <v>11223.52</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C6" s="39" t="n">
+        <f aca="false">Estações!$O$44</f>
+        <v>2</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <f aca="false">Estações!$O$43</f>
+        <v>40</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <f aca="false">Preços!$D$44</f>
+        <v>35</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <f aca="false">C6*E6</f>
+        <v>70</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <f aca="false">D6*E6</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <f aca="false">C5*1.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <f aca="false">D5*1.5</f>
+        <v>132</v>
+      </c>
+      <c r="E7" s="37" t="n">
         <f aca="false">Premissas!$B$9</f>
         <v>34.9305521472393</v>
       </c>
-      <c r="F5" s="31" t="n">
-        <f aca="false">C5*E5</f>
-        <v>72.7719836400818</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <f aca="false">D5*E5</f>
-        <v>1455.43967280164</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>504</v>
+      <c r="F7" s="31" t="n">
+        <f aca="false">C7*E7</f>
+        <v>261.979141104295</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <f aca="false">D7*E7</f>
+        <v>4610.83288343558</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="C8" s="39" t="n">
-        <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$41,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <f aca="false">ROUNDUP(Estações!$O$43*Premissas!$B$41,0)</f>
-        <v>88</v>
-      </c>
-      <c r="E8" s="37" t="n">
-        <f aca="false">Composição!$F$56</f>
-        <v>127.54</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <f aca="false">C8*E8</f>
-        <v>637.7</v>
-      </c>
-      <c r="G8" s="31" t="n">
-        <f aca="false">D8*E8</f>
-        <v>11223.52</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C9" s="39" t="n">
-        <f aca="false">Estações!$O$44</f>
-        <v>2</v>
-      </c>
-      <c r="D9" s="39" t="n">
-        <f aca="false">Estações!$O$43</f>
-        <v>40</v>
-      </c>
-      <c r="E9" s="37" t="n">
-        <f aca="false">Preços!$D$46</f>
-        <v>35</v>
-      </c>
-      <c r="F9" s="31" t="n">
-        <f aca="false">C9*E9</f>
-        <v>70</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <f aca="false">D9*E9</f>
-        <v>1400</v>
+      <c r="A8" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="38" t="n">
+        <f aca="false">SUM(F3:F7)</f>
+        <v>1759.95112474438</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <f aca="false">SUM(G3:G7)</f>
+        <v>33039.7925562372</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <f aca="false">C8*1.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <f aca="false">D8*1.5</f>
-        <v>132</v>
-      </c>
-      <c r="E10" s="37" t="n">
-        <f aca="false">Premissas!$B$9</f>
-        <v>34.9305521472393</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <f aca="false">C10*E10</f>
-        <v>261.979141104295</v>
-      </c>
-      <c r="G10" s="31" t="n">
-        <f aca="false">D10*E10</f>
-        <v>4610.83288343558</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>511</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="38" t="n">
-        <f aca="false">SUM(F3:F5)+SUM(F8:F10)</f>
+        <v>498</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="37" t="n">
+        <f aca="false">'A-Interno'!F34+F8</f>
         <v>20971.4485461656</v>
       </c>
-      <c r="G11" s="38" t="n">
-        <f aca="false">SUM(G3:G5)+SUM(G8:G10)</f>
+      <c r="G10" s="37" t="n">
+        <f aca="false">'A-Interno'!G34+G8</f>
         <v>337795.284586661</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C14" s="39" t="n">
-        <f aca="false">Estações!$O$44</f>
-        <v>2</v>
-      </c>
-      <c r="D14" s="39" t="n">
-        <f aca="false">Estações!$O$43</f>
-        <v>40</v>
-      </c>
-      <c r="E14" s="37" t="n">
-        <f aca="false">Composição!$F$69</f>
-        <v>204.204262295082</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <f aca="false">C14*E14</f>
-        <v>408.408524590164</v>
-      </c>
-      <c r="G14" s="31" t="n">
-        <f aca="false">D14*E14</f>
-        <v>8168.17049180328</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="C15" s="21" t="n">
-        <f aca="false">C14*2</f>
-        <v>4</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <f aca="false">D14*2</f>
-        <v>80</v>
-      </c>
-      <c r="E15" s="37" t="n">
-        <f aca="false">Premissas!$B$9</f>
-        <v>34.9305521472393</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <f aca="false">C15*E15</f>
-        <v>139.722208588957</v>
-      </c>
-      <c r="G15" s="31" t="n">
-        <f aca="false">D15*E15</f>
-        <v>2794.44417177914</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="38" t="n">
-        <f aca="false">SUM(F3:F5)+SUM(F14:F15)</f>
-        <v>20549.9001382404</v>
-      </c>
-      <c r="G16" s="38" t="n">
-        <f aca="false">SUM(G3:G5)+SUM(G14:G15)</f>
-        <v>331523.546366808</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="C18" s="39" t="n">
-        <f aca="false">C8</f>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="C12" s="39" t="n">
+        <f aca="false">C5</f>
         <v>5</v>
       </c>
-      <c r="D18" s="39" t="n">
-        <f aca="false">D8</f>
+      <c r="D12" s="39" t="n">
+        <f aca="false">D5</f>
         <v>88</v>
       </c>
-      <c r="E18" s="37" t="n">
-        <f aca="false">Preços!$D$37</f>
+      <c r="E12" s="37" t="n">
+        <f aca="false">Preços!$D$36</f>
         <v>9541.77853</v>
       </c>
-      <c r="F18" s="31" t="n">
-        <f aca="false">C18*E18</f>
+      <c r="F12" s="31" t="n">
+        <f aca="false">C12*E12</f>
         <v>47708.89265</v>
       </c>
-      <c r="G18" s="31" t="n">
-        <f aca="false">D18*E18</f>
+      <c r="G12" s="31" t="n">
+        <f aca="false">D12*E12</f>
         <v>839676.51064</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>519</v>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/entregaveis/Orcamento_PTL.xlsx
+++ b/projeto/entregaveis/Orcamento_PTL.xlsx
@@ -14,12 +14,13 @@
     <sheet name="Estações" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Preços" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Composição" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="A-Interno" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="A-Terceiros" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="RFID-futuro" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Software" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="POC" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Fontes RFID" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Composição" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="A-Interno" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="A-Terceiros" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="RFID-futuro" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Software" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="POC" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="862">
   <si>
     <t xml:space="preserve">Orçamento do projeto Pick-to-Light (flow rack)</t>
   </si>
@@ -75,7 +76,7 @@
     <t xml:space="preserve">Preços: catálogo de peças; o preço de cada código vem da aba Fontes (loja, link e preço consultados em 27/10/2026).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fontes: cada componente com loja, produto, link clicável, preço publicado e observações de estoque.</t>
+    <t xml:space="preserve">Fontes: cada componente do projeto com loja, produto, link clicável, preço publicado e observações de estoque. Fontes RFID: o mesmo para a melhoria futura, separado.</t>
   </si>
   <si>
     <t xml:space="preserve">Composição: lista de materiais (BOM) de cada tipo de módulo e custo unitário.</t>
@@ -880,19 +881,19 @@
     <t xml:space="preserve">P13</t>
   </si>
   <si>
-    <t xml:space="preserve">Carcaça do Módulo Q (caixa Patola PB-075, 36 × 60 × 75 mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usinainfo, Caixa Patola PB-075 para Montagem 36 x 60 x 75 mm, 27/10/2026: https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-075-para-montagem-36-x-60-x-75-mm-4390.html</t>
+    <t xml:space="preserve">Carcaça do Módulo Q (impressão 3D, medida padrão compacta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor estipulado, Carcaça impressa em 3D, medida padrão compacta (definida pelo projeto), 27/10/2026: sem link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor estipulado</t>
   </si>
   <si>
     <t xml:space="preserve">P14</t>
   </si>
   <si>
-    <t xml:space="preserve">Carcaça do Módulo E+Q / Nó de coluna (caixa Patola PB-112, 53 × 85 × 124 mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usinainfo, Caixa Patola / Case para Montagem 53 x 85 x 124 mm - PB-112, 27/10/2026: https://www.usinainfo.com.br/caixas-patola/caixa-patola-case-para-montagem-53-x-85-x-124-mm-pb-112-3879.html</t>
+    <t xml:space="preserve">Carcaça do Módulo E+Q / Nó de coluna (impressão 3D, medida padrão compacta)</t>
   </si>
   <si>
     <t xml:space="preserve">P15</t>
@@ -1009,7 +1010,7 @@
     <t xml:space="preserve">Kit energia pulseira (LiPo + carregador TP4056 + motor de vibração + botão)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kit com 4 componentes, ver aba Fontes: Bateria LiPo 3,7 V ~500 mAh; Carregador TP4056 USB-C; Motor de vibração 1027; Chave táctil 6 × 6 mm</t>
+    <t xml:space="preserve">Kit com 4 componentes, ver aba Fontes RFID: Bateria LiPo 3,7 V ~500 mAh; Carregador TP4056 USB-C; Motor de vibração 1027; Chave táctil 6 × 6 mm</t>
   </si>
   <si>
     <t xml:space="preserve">Cotado com link, 1 item estimado</t>
@@ -1021,7 +1022,7 @@
     <t xml:space="preserve">Carcaça da pulseira (caixa Patola PB-060) + fita de velcro</t>
   </si>
   <si>
-    <t xml:space="preserve">Kit com 2 componentes, ver aba Fontes: Caixa Patola PB-060; Fita de velcro 10 mm (rolo 10 m)</t>
+    <t xml:space="preserve">Kit com 2 componentes, ver aba Fontes RFID: Caixa Patola PB-060; Fita de velcro 10 mm (rolo 10 m)</t>
   </si>
   <si>
     <t xml:space="preserve">P29</t>
@@ -1423,28 +1424,25 @@
     <t xml:space="preserve">normal R$ 1.111,00; restam 10 caixas</t>
   </si>
   <si>
-    <t xml:space="preserve">Caixa Patola PB-075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caixa Patola PB-075 para Montagem 36 x 60 x 75 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-075-para-montagem-36-x-60-x-75-mm-4390.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cartão R$ 12,99; últimas unidades (Patola também vende direto). Impressão 3D em PETG pode sair mais barata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caixa Patola PB-112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caixa Patola / Case para Montagem 53 x 85 x 124 mm - PB-112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.usinainfo.com.br/caixas-patola/caixa-patola-case-para-montagem-53-x-85-x-124-mm-pb-112-3879.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cartão R$ 29,65; últimas unidades</t>
+    <t xml:space="preserve">Carcaça 3D do módulo Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carcaça impressa em 3D, medida padrão compacta (definida pelo projeto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sem link (valor estipulado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor estipulado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor estipulado pelo projeto: carcaça compacta impressa em 3D, sem ocupar espaço na frente da prateleira. Referência do material: filamento PETG 1 kg R$ 169,82 (Pix) na KaBuM, https://www.kabum.com.br/produto/1063679/filamento-1-75mm-petg-basico-1kg-marrom-escuro-para-impressora-3d-com-carretel-reutilizavel-bambu-lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carcaça 3D do módulo E+Q / nó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor estipulado pelo projeto: carcaça compacta impressa em 3D para o E+Q e o nó de coluna. Mesma referência de filamento do P13</t>
   </si>
   <si>
     <t xml:space="preserve">Placa fenolite perfurada 7 × 5 cm</t>
@@ -1600,6 +1598,228 @@
     <t xml:space="preserve">10x R$ 76,93</t>
   </si>
   <si>
+    <t xml:space="preserve">Cabo PP 3 × 1,0 mm² (50 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo Pp 3x1,00 Mm Elétrico Flexível Preto - 50 Metros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/722927/cabo-pp-3x1-00-mm-eletrico-flexivel-preto-50-metros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x R$ 48,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugue 2P+T com prensa-cabo (10 un)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pino Plug Macho Ilumi Prensa Cabo 2p+t 10a Embalagem Com 10 Unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.leroymerlin.com.br/pino-plug-macho-ilumi-prensa-cabo-2p-t-10a-embalagem-com-10-unidades_1568301310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vendido por Mtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS 275 V 20 kA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protetor De Surto Dps Classe Ii/iii 20ka 275vca Fase (Embrastec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.leroymerlin.com.br/protetor-de-surto-dps-classe-ii-iii-20ka-275vca-fase_1570251308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vendido por Eletrotécnica Vera Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit rede Nexans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kit Cabo De Rede Nexans 40 Metros, Alicate, Testador, 10xrj45, Cat5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/386101/kit-cabo-de-rede-nexans-40-metros-alicate-testador-10xrj45-cat5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x R$ 28,59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estação de solda 60 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estacao De Solda Analogica 60w 220v Hk936a Preta Hikari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.leroymerlin.com.br/estacao-de-solda-analogica-60w-220v-hk936a-preta-hikari_1566757438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de R$ 536,90; vendido por 47elétrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multímetro digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multímetro Digital Hikari HM-1001 CAT I 1000V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.usinainfo.com.br/multimetros/multimetro-digital-hikari-hm-1001-cat-i-1000v-5502.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cartão R$ 60,83; últimas unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estanho 1,0 mm 500 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solda Estanho Cobix 1.0mm 60x40 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.leroymerlin.com.br/solda-estanho-cobix-1-0mm-60x40-500g_1566817011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de R$ 195,00; vendido por Pd Atacadista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nobreak XNB 720 VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nobreak Intelbras XNB, 720VA, Bivolt - 4822010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/229971/nobreak-intelbras-xnb-720va-bivolt-4822010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">normal R$ 697,00; vendido por Kadri Tecnologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini rack 5U MRM 537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mini Rack 05U x 19P x 370mm, Montado MRM 537, Preto - Intelbras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/291255/mini-rack-05u-x-19p-x-370mm-montado-mrm-537-preto-intelbras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10x R$ 36,10; vendido por MIRANDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizador de cabos 1U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizador De Cabos Intelbras Och1u 40, Para Rack 1u 40mm, Preto - 4770004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/235380/organizador-de-cabos-intelbras-para-rack-1u-40-mm-och1u-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vendido por Digi Mania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patch cord Cat5e 1,5 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo De Rede Md9 Patch Cord 1.5m Azul Cat5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/233241/cabo-de-rede-md9-patch-cord-1-5m-azul-cat5e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">normal R$ 8,01; uplink e reserva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponto de tomada 220 V (serviço)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cotar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material + eletricista, com a manutenção predial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sem link (a cotar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEM LINK por decisão: serviço a cotar com a manutenção predial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinaleiro LED 22 mm amarelo 12 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luz Automação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L20-AR9-Y | Sinaleiro Led 22mm - 12vcc/vca - Amarelo | Metaltex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.luzautomacao.com.br/produto/sinaleiro-led-22mm-12v-amarelo-metaltex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 em estoque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haste (cantoneira de alumínio 1 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfil Aluminio Preto L-013 Cantoneira 1 Pol 25mm Acabamento Canto Parede Barra 1 Mt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.leroymerlin.com.br/perfil-aluminio-preto-l-013-cantoneira-1-pol-25mm-acabamento-canto-parede-barra-1-mt_1572585517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a prazo R$ 33,24; 0,5 m por estação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transistor BC337 (kit 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transistor BC337 NPN para Projetos - Kit com 5 unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.usinainfo.com.br/transistor-bc/transistor-bc337-para-projetos-kit-com-5-unidades-2998.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cartão R$ 3,45; aciona o sinaleiro pela saída do nó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano de MDF cru 120 × 60 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Móveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano de Mdf Cru 120x60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.keymoveis.com.br/plano-de-mdf-cru-120x60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de R$ 54,27; disponível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longarina (cantoneira de alumínio 1 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simula a frente da prateleira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch 5 portas TL-SG1005D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switch 5 Portas Gigabit - Tp-link Tl-sg1005d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kabum.com.br/produto/205611/switch-5-portas-10-100-1000-gigabit-mesa-tl-sg1005d-tp-link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4x R$ 27,53; vendido por STORN35</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tag NFC NTAG213 (100 un)</t>
   </si>
   <si>
@@ -1732,138 +1952,6 @@
     <t xml:space="preserve">0,3 m por pulseira; vendido por 47elétrica</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabo PP 3 × 1,0 mm² (50 m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo Pp 3x1,00 Mm Elétrico Flexível Preto - 50 Metros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/722927/cabo-pp-3x1-00-mm-eletrico-flexivel-preto-50-metros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10x R$ 48,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plugue 2P+T com prensa-cabo (10 un)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pino Plug Macho Ilumi Prensa Cabo 2p+t 10a Embalagem Com 10 Unidades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.leroymerlin.com.br/pino-plug-macho-ilumi-prensa-cabo-2p-t-10a-embalagem-com-10-unidades_1568301310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vendido por Mtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPS 275 V 20 kA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protetor De Surto Dps Classe Ii/iii 20ka 275vca Fase (Embrastec)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.leroymerlin.com.br/protetor-de-surto-dps-classe-ii-iii-20ka-275vca-fase_1570251308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vendido por Eletrotécnica Vera Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kit rede Nexans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kit Cabo De Rede Nexans 40 Metros, Alicate, Testador, 10xrj45, Cat5e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/386101/kit-cabo-de-rede-nexans-40-metros-alicate-testador-10xrj45-cat5e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10x R$ 28,59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estação de solda 60 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estacao De Solda Analogica 60w 220v Hk936a Preta Hikari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.leroymerlin.com.br/estacao-de-solda-analogica-60w-220v-hk936a-preta-hikari_1566757438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">de R$ 536,90; vendido por 47elétrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multímetro digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multímetro Digital Hikari HM-1001 CAT I 1000V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.usinainfo.com.br/multimetros/multimetro-digital-hikari-hm-1001-cat-i-1000v-5502.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cartão R$ 60,83; últimas unidades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estanho 1,0 mm 500 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solda Estanho Cobix 1.0mm 60x40 500g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.leroymerlin.com.br/solda-estanho-cobix-1-0mm-60x40-500g_1566817011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">de R$ 195,00; vendido por Pd Atacadista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nobreak XNB 720 VA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nobreak Intelbras XNB, 720VA, Bivolt - 4822010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/229971/nobreak-intelbras-xnb-720va-bivolt-4822010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normal R$ 697,00; vendido por Kadri Tecnologia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mini rack 5U MRM 537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mini Rack 05U x 19P x 370mm, Montado MRM 537, Preto - Intelbras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/291255/mini-rack-05u-x-19p-x-370mm-montado-mrm-537-preto-intelbras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10x R$ 36,10; vendido por MIRANDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organizador de cabos 1U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organizador De Cabos Intelbras Och1u 40, Para Rack 1u 40mm, Preto - 4770004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/235380/organizador-de-cabos-intelbras-para-rack-1u-40-mm-och1u-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vendido por Digi Mania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patch cord Cat5e 1,5 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo De Rede Md9 Patch Cord 1.5m Azul Cat5e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/233241/cabo-de-rede-md9-patch-cord-1-5m-azul-cat5e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normal R$ 8,01; uplink e reserva</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carregador USB 2 portas</t>
   </si>
   <si>
@@ -1874,96 +1962,6 @@
   </si>
   <si>
     <t xml:space="preserve">vendido por Assistec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ponto de tomada 220 V (serviço)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A cotar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material + eletricista, com a manutenção predial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sem link (cotar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEM LINK por decisão: serviço a cotar com a manutenção predial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sinaleiro LED 22 mm amarelo 12 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luz Automação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L20-AR9-Y | Sinaleiro Led 22mm - 12vcc/vca - Amarelo | Metaltex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.luzautomacao.com.br/produto/sinaleiro-led-22mm-12v-amarelo-metaltex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40 em estoque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haste (cantoneira de alumínio 1 m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfil Aluminio Preto L-013 Cantoneira 1 Pol 25mm Acabamento Canto Parede Barra 1 Mt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.leroymerlin.com.br/perfil-aluminio-preto-l-013-cantoneira-1-pol-25mm-acabamento-canto-parede-barra-1-mt_1572585517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a prazo R$ 33,24; 0,5 m por estação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transistor BC337 (kit 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transistor BC337 NPN para Projetos - Kit com 5 unidades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.usinainfo.com.br/transistor-bc/transistor-bc337-para-projetos-kit-com-5-unidades-2998.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cartão R$ 3,45; aciona o sinaleiro pela saída do nó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano de MDF cru 120 × 60 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Móveis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano de Mdf Cru 120x60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.keymoveis.com.br/plano-de-mdf-cru-120x60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">de R$ 54,27; disponível</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longarina (cantoneira de alumínio 1 m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">simula a frente da prateleira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch 5 portas TL-SG1005D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switch 5 Portas Gigabit - Tp-link Tl-sg1005d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.kabum.com.br/produto/205611/switch-5-portas-10-100-1000-gigabit-mesa-tl-sg1005d-tp-link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4x R$ 27,53; vendido por STORN35</t>
   </si>
   <si>
     <t xml:space="preserve">Conjunto</t>
@@ -2936,6 +2934,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2944,15 +2950,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3331,7 +3329,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
         <v>14</v>
       </c>
@@ -3484,6 +3482,602 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="C3" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
+        <v>71</v>
+      </c>
+      <c r="D3" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$F$43*(1+Premissas!$B$26),0)</f>
+        <v>1408</v>
+      </c>
+      <c r="E3" s="40" t="n">
+        <f aca="false">Preços!$D$32+Preços!$D$14</f>
+        <v>91.13441</v>
+      </c>
+      <c r="F3" s="30" t="n">
+        <f aca="false">C3*E3</f>
+        <v>6470.54311</v>
+      </c>
+      <c r="G3" s="30" t="n">
+        <f aca="false">D3*E3</f>
+        <v>128317.24928</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>729</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C4" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
+        <v>14</v>
+      </c>
+      <c r="D4" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
+        <v>277</v>
+      </c>
+      <c r="E4" s="40" t="n">
+        <f aca="false">Preços!$D$33+Preços!$D$15+Preços!$D$10</f>
+        <v>246.30078</v>
+      </c>
+      <c r="F4" s="30" t="n">
+        <f aca="false">C4*E4</f>
+        <v>3448.21092</v>
+      </c>
+      <c r="G4" s="30" t="n">
+        <f aca="false">D4*E4</f>
+        <v>68225.31606</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="C5" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$O$43*(1+Premissas!$B$26),0)</f>
+        <v>44</v>
+      </c>
+      <c r="E5" s="40" t="n">
+        <f aca="false">Preços!$D$34+Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$37*3+Preços!$D$38*1+Preços!$D$39*1</f>
+        <v>851.37555</v>
+      </c>
+      <c r="F5" s="30" t="n">
+        <f aca="false">C5*E5</f>
+        <v>2554.12665</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <f aca="false">D5*E5</f>
+        <v>37460.5242</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="C6" s="42" t="n">
+        <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
+        <v>124</v>
+      </c>
+      <c r="D6" s="42" t="n">
+        <f aca="false">Estações!$F$43*Premissas!$B$43+Estações!$M$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
+        <v>2513</v>
+      </c>
+      <c r="E6" s="40" t="n">
+        <f aca="false">Preços!$D$13</f>
+        <v>2.62262295081967</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <f aca="false">C6*E6</f>
+        <v>325.205245901639</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <f aca="false">D6*E6</f>
+        <v>6590.65147540984</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="C7" s="42" t="n">
+        <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
+        <v>160</v>
+      </c>
+      <c r="D7" s="42" t="n">
+        <f aca="false">(Estações!$F$43+Estações!$M$43)*2+Estações!$O$43*4</f>
+        <v>3222</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <f aca="false">Preços!$D$12</f>
+        <v>0.7099</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <f aca="false">C7*E7</f>
+        <v>113.584</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <f aca="false">D7*E7</f>
+        <v>2287.2978</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!F9:F19)</f>
+        <v>3725.95413114754</v>
+      </c>
+      <c r="G8" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!G9:G19)</f>
+        <v>23667.5855737705</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="C9" s="42" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="42" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <f aca="false">Preços!$D$35</f>
+        <v>15000</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <f aca="false">C9*E9</f>
+        <v>15000</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <f aca="false">D9*E9</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <f aca="false">(C3+C4+C5)*Premissas!$B$44</f>
+        <v>8.8</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <f aca="false">(D3+D4+D5)*Premissas!$B$44</f>
+        <v>172.9</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <f aca="false">C10*E10</f>
+        <v>307.388858895706</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <f aca="false">D10*E10</f>
+        <v>6039.49246625767</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
+        <v>51.18</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
+        <v>1029.375</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <f aca="false">C11*E11</f>
+        <v>1787.74565889571</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <f aca="false">D11*E11</f>
+        <v>35956.6371165644</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!F30:F31)</f>
+        <v>756.149202453988</v>
+      </c>
+      <c r="G12" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!G30:G31)</f>
+        <v>4504.09619631902</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>744</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="41" t="n">
+        <f aca="false">SUM(F3:F12)</f>
+        <v>34488.9077772946</v>
+      </c>
+      <c r="G13" s="41" t="n">
+        <f aca="false">SUM(G3:G12)</f>
+        <v>328048.850168321</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>747</v>
+      </c>
+      <c r="C16" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
+        <v>71</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$F$43*(1+Premissas!$B$26),0)</f>
+        <v>1408</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <f aca="false">Preços!$D$29</f>
+        <v>287.1147</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <f aca="false">C16*E16</f>
+        <v>20385.1437</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <f aca="false">D16*E16</f>
+        <v>404257.4976</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C17" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
+        <v>14</v>
+      </c>
+      <c r="D17" s="42" t="n">
+        <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
+        <v>277</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <f aca="false">Preços!$D$30</f>
+        <v>622.08185</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <f aca="false">C17*E17</f>
+        <v>8709.1459</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <f aca="false">D17*E17</f>
+        <v>172316.67245</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" s="42" t="n">
+        <f aca="false">Estações!$O$44</f>
+        <v>2</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <f aca="false">Estações!$O$43</f>
+        <v>40</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <f aca="false">Preços!$D$31</f>
+        <v>2105.5078</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <f aca="false">C18*E18</f>
+        <v>4211.0156</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <f aca="false">D18*E18</f>
+        <v>84220.312</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="42" t="n">
+        <f aca="false">Estações!$O$44</f>
+        <v>2</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <f aca="false">Estações!$O$43</f>
+        <v>40</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <f aca="false">Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$37*3+Preços!$D$38*1+Preços!$D$39*1</f>
+        <v>516.4084</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <f aca="false">C19*E19</f>
+        <v>1032.8168</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <f aca="false">D19*E19</f>
+        <v>20656.336</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="C20" s="42" t="n">
+        <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
+        <v>124</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <f aca="false">Estações!$F$43*Premissas!$B$43+Estações!$M$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
+        <v>2513</v>
+      </c>
+      <c r="E20" s="40" t="n">
+        <f aca="false">Preços!$D$13</f>
+        <v>2.62262295081967</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <f aca="false">C20*E20</f>
+        <v>325.205245901639</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <f aca="false">D20*E20</f>
+        <v>6590.65147540984</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="C21" s="42" t="n">
+        <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
+        <v>160</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <f aca="false">(Estações!$F$43+Estações!$M$43)*2+Estações!$O$43*4</f>
+        <v>3222</v>
+      </c>
+      <c r="E21" s="40" t="n">
+        <f aca="false">Preços!$D$12</f>
+        <v>0.7099</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <f aca="false">C21*E21</f>
+        <v>113.584</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <f aca="false">D21*E21</f>
+        <v>2287.2978</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!F9:F19)</f>
+        <v>3725.95413114754</v>
+      </c>
+      <c r="G22" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!G9:G19)</f>
+        <v>23667.5855737705</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
+        <v>51.18</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
+        <v>1029.375</v>
+      </c>
+      <c r="E23" s="40" t="n">
+        <f aca="false">Premissas!$B$9</f>
+        <v>34.9305521472393</v>
+      </c>
+      <c r="F23" s="30" t="n">
+        <f aca="false">C23*E23</f>
+        <v>1787.74565889571</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <f aca="false">D23*E23</f>
+        <v>35956.6371165644</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!F30:F31)</f>
+        <v>756.149202453988</v>
+      </c>
+      <c r="G24" s="40" t="n">
+        <f aca="false">SUM('A-Interno'!G30:G31)</f>
+        <v>4504.09619631902</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>751</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="41" t="n">
+        <f aca="false">SUM(F16:F24)</f>
+        <v>41046.7602383989</v>
+      </c>
+      <c r="G25" s="41" t="n">
+        <f aca="false">SUM(G16:G24)</f>
+        <v>754457.086212064</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3504,35 +4098,35 @@
         <v>237</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>665</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>755</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>756</v>
       </c>
       <c r="C3" s="42" t="n">
         <f aca="false">ROUNDUP(Premissas!$B$40*Estações!$O$44/Estações!$O$43,0)</f>
@@ -3557,10 +4151,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>757</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>758</v>
       </c>
       <c r="C4" s="21" t="n">
         <f aca="false">C3*30/3600</f>
@@ -3585,10 +4179,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>759</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>760</v>
       </c>
       <c r="C5" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$41,0)</f>
@@ -3613,10 +4207,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>761</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>762</v>
       </c>
       <c r="C6" s="42" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -3641,10 +4235,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>763</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>764</v>
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">C5*1.5</f>
@@ -3669,7 +4263,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -3686,29 +4280,29 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>766</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>767</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="40" t="n">
         <f aca="false">'A-Interno'!F34+F8</f>
-        <v>21729.7550264115</v>
+        <v>20684.7320264115</v>
       </c>
       <c r="G10" s="40" t="n">
         <f aca="false">'A-Interno'!G34+G8</f>
-        <v>355086.04076912</v>
+        <v>334319.55026912</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>768</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>769</v>
       </c>
       <c r="C12" s="42" t="n">
         <f aca="false">C5</f>
@@ -3733,7 +4327,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -3747,7 +4341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3767,13 +4361,13 @@
         <v>390</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>771</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>772</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>773</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>400</v>
@@ -3781,10 +4375,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>774</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>775</v>
       </c>
       <c r="C2" s="20" t="n">
         <v>240</v>
@@ -3794,15 +4388,15 @@
         <v>24907.8773006135</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C3" s="20" t="n">
         <v>120</v>
@@ -3812,15 +4406,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C4" s="20" t="n">
         <v>60</v>
@@ -3830,15 +4424,15 @@
         <v>6226.96932515337</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>781</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>782</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>160</v>
@@ -3848,15 +4442,15 @@
         <v>16605.2515337423</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>784</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>785</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>80</v>
@@ -3866,15 +4460,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>120</v>
@@ -3884,15 +4478,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C8" s="20" t="n">
         <v>100</v>
@@ -3902,15 +4496,15 @@
         <v>10378.282208589</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>791</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>792</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>80</v>
@@ -3920,15 +4514,15 @@
         <v>8302.62576687117</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C10" s="20" t="n">
         <v>120</v>
@@ -3938,15 +4532,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C11" s="20" t="n">
         <v>40</v>
@@ -3956,15 +4550,15 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>24</v>
@@ -3974,15 +4568,15 @@
         <v>2490.78773006135</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C13" s="20" t="n">
         <v>120</v>
@@ -3992,15 +4586,15 @@
         <v>12453.9386503067</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>40</v>
@@ -4010,12 +4604,12 @@
         <v>4151.31288343558</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="45" t="n">
@@ -4027,12 +4621,12 @@
         <v>118727.548466258</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="45" t="n">
@@ -4047,7 +4641,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
   </sheetData>
@@ -4061,7 +4655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4077,12 +4671,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4090,29 +4684,29 @@
         <v>237</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>810</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>813</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>814</v>
       </c>
       <c r="C5" s="46" t="n">
         <v>1</v>
@@ -4128,40 +4722,40 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="40" t="n">
         <f aca="false">Composição!$F$16</f>
-        <v>117.59</v>
+        <v>104.42</v>
       </c>
       <c r="E6" s="30" t="n">
         <f aca="false">C6*D6</f>
-        <v>117.59</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>816</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>817</v>
       </c>
       <c r="C7" s="46" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="40" t="n">
         <f aca="false">Composição!$F$8</f>
-        <v>55.2250459016394</v>
+        <v>47.8850459016393</v>
       </c>
       <c r="E7" s="30" t="n">
         <f aca="false">C7*D7</f>
-        <v>220.900183606557</v>
+        <v>191.540183606557</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,26 +4763,26 @@
         <v>181</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C8" s="46" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="40" t="n">
         <f aca="false">Composição!$F$27</f>
-        <v>151.48</v>
+        <v>138.31</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="false">C8*D8</f>
-        <v>302.96</v>
+        <v>276.62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C9" s="46" t="n">
         <v>1</v>
@@ -4204,10 +4798,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>820</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>821</v>
       </c>
       <c r="C10" s="46" t="n">
         <v>20</v>
@@ -4223,7 +4817,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="46" t="n">
@@ -4240,10 +4834,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>823</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>824</v>
       </c>
       <c r="C12" s="46" t="n">
         <v>1</v>
@@ -4259,10 +4853,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>825</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>826</v>
       </c>
       <c r="C13" s="46" t="n">
         <v>1</v>
@@ -4278,10 +4872,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C14" s="46" t="n">
         <v>1</v>
@@ -4297,10 +4891,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C15" s="46" t="n">
         <v>1</v>
@@ -4316,10 +4910,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="43" t="n">
@@ -4328,15 +4922,15 @@
       </c>
       <c r="E16" s="30" t="n">
         <f aca="false">D16*SUM(E5:E15)</f>
-        <v>127.971058381148</v>
+        <v>124.527558381148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>830</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>831</v>
       </c>
       <c r="C17" s="21" t="n">
         <f aca="false">Premissas!$B$15+Premissas!$B$13+4*Premissas!$B$12+2*Premissas!$B$14</f>
@@ -4353,10 +4947,10 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>832</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>833</v>
       </c>
       <c r="C18" s="18" t="n">
         <v>16</v>
@@ -4372,41 +4966,41 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="41" t="n">
         <f aca="false">SUM(E5:E18)</f>
-        <v>3447.13173520655</v>
+        <v>3374.81823520655</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
+        <v>835</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>836</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>837</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="40" t="n">
         <f aca="false">'A-Interno'!F34</f>
-        <v>20179.6189016671</v>
+        <v>19134.5959016671</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
+        <v>837</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>838</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>839</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -4417,48 +5011,48 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
+        <v>839</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>840</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>841</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="30" t="n">
         <f aca="false">-(Composição!$F$39+Composição!$F$16+4*Composição!$F$8+2*Composição!$F$27)</f>
-        <v>-1315.18970860656</v>
+        <v>-1246.31970860656</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="41" t="n">
         <f aca="false">SUM(E22:E24)</f>
-        <v>17823.1651930606</v>
+        <v>16847.0121930606</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="41" t="n">
         <f aca="false">E19+E25</f>
-        <v>21270.2969282671</v>
+        <v>20221.8304282671</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
+        <v>843</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>844</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>845</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="43" t="n">
@@ -4467,32 +5061,32 @@
       </c>
       <c r="E28" s="30" t="n">
         <f aca="false">D28*E27</f>
-        <v>2127.02969282671</v>
+        <v>2022.18304282671</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
       <c r="E29" s="41" t="n">
         <f aca="false">E27+E28</f>
-        <v>23397.3266210938</v>
+        <v>22244.0134710938</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>848</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>849</v>
       </c>
       <c r="C32" s="20" t="n">
         <v>160</v>
@@ -4508,10 +5102,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>850</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>851</v>
       </c>
       <c r="C33" s="20" t="n">
         <v>160</v>
@@ -4527,10 +5121,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>852</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>853</v>
       </c>
       <c r="C34" s="20" t="n">
         <v>60</v>
@@ -4546,10 +5140,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>854</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>855</v>
       </c>
       <c r="C35" s="20" t="n">
         <v>100</v>
@@ -4565,10 +5159,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>856</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>857</v>
       </c>
       <c r="C36" s="20" t="n">
         <v>40</v>
@@ -4584,10 +5178,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>858</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>859</v>
       </c>
       <c r="C37" s="20" t="n">
         <v>80</v>
@@ -4603,7 +5197,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="45" t="n">
@@ -4618,12 +5212,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -4691,19 +5285,19 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">'A-Interno'!F21</f>
-        <v>15478.7624452254</v>
+        <v>14433.7394452254</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">'A-Interno'!G21</f>
-        <v>243796.627979754</v>
+        <v>223030.137479754</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/Estações!$O$43</f>
-        <v>6094.91569949385</v>
+        <v>5575.75343699385</v>
       </c>
       <c r="F4" s="11" t="n">
         <f aca="false">D4*(1+Premissas!$B$28)</f>
-        <v>268176.29077773</v>
+        <v>245333.15122773</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4715,19 +5309,19 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">'A-Interno'!F40</f>
-        <v>16813.0304452254</v>
+        <v>15768.0074452254</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">'A-Interno'!G40</f>
-        <v>264261.887979754</v>
+        <v>243495.397479754</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/Estações!$O$43</f>
-        <v>6606.54719949385</v>
+        <v>6087.38493699385</v>
       </c>
       <c r="F5" s="11" t="n">
         <f aca="false">D5*(1+Premissas!$B$28)</f>
-        <v>290688.07677773</v>
+        <v>267844.93722773</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4739,19 +5333,19 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">'A-Interno'!F34</f>
-        <v>20179.6189016671</v>
+        <v>19134.5959016671</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">'A-Interno'!G34</f>
-        <v>326069.232212883</v>
+        <v>305302.741712883</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/Estações!$O$43</f>
-        <v>8151.73080532207</v>
+        <v>7632.56854282207</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">D6*(1+Premissas!$B$28)</f>
-        <v>358676.155434171</v>
+        <v>335833.015884171</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4763,19 +5357,19 @@
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">'A-Terceiros'!F13</f>
-        <v>35194.4277772946</v>
+        <v>34488.9077772946</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">'A-Terceiros'!G13</f>
-        <v>342031.660168321</v>
+        <v>328048.850168321</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/Estações!$O$43</f>
-        <v>8550.79150420804</v>
+        <v>8201.22125420804</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">D7*(1+Premissas!$B$28)</f>
-        <v>376234.826185154</v>
+        <v>360853.735185154</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4869,7 +5463,7 @@
       <c r="E15" s="16"/>
       <c r="F15" s="17" t="n">
         <f aca="false">F6+D12</f>
-        <v>477403.703900429</v>
+        <v>454560.564350429</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4881,7 +5475,7 @@
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">POC!E29</f>
-        <v>23397.3266210938</v>
+        <v>22244.0134710938</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
@@ -7765,7 +8359,7 @@
         <v>162</v>
       </c>
       <c r="D2" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A2,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A2,Fontes!$J$2:$J$45)</f>
         <v>10.97</v>
       </c>
       <c r="E2" s="13"/>
@@ -7787,7 +8381,7 @@
         <v>162</v>
       </c>
       <c r="D3" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A3,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A3,Fontes!$J$2:$J$45)</f>
         <v>20.17</v>
       </c>
       <c r="E3" s="13"/>
@@ -7809,7 +8403,7 @@
         <v>162</v>
       </c>
       <c r="D4" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A4,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A4,Fontes!$J$2:$J$45)</f>
         <v>37.9</v>
       </c>
       <c r="E4" s="13"/>
@@ -7831,7 +8425,7 @@
         <v>162</v>
       </c>
       <c r="D5" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A5,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A5,Fontes!$J$2:$J$45)</f>
         <v>8.9</v>
       </c>
       <c r="E5" s="13"/>
@@ -7853,7 +8447,7 @@
         <v>162</v>
       </c>
       <c r="D6" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A6,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A6,Fontes!$J$2:$J$45)</f>
         <v>119.631125</v>
       </c>
       <c r="E6" s="31" t="n">
@@ -7877,7 +8471,7 @@
         <v>162</v>
       </c>
       <c r="D7" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A7,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A7,Fontes!$J$2:$J$45)</f>
         <v>189.98</v>
       </c>
       <c r="E7" s="13"/>
@@ -7899,7 +8493,7 @@
         <v>162</v>
       </c>
       <c r="D8" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A8,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A8,Fontes!$J$2:$J$45)</f>
         <v>591.68</v>
       </c>
       <c r="E8" s="13"/>
@@ -7921,7 +8515,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A9,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A9,Fontes!$J$2:$J$45)</f>
         <v>10.9</v>
       </c>
       <c r="E9" s="13"/>
@@ -7943,7 +8537,7 @@
         <v>162</v>
       </c>
       <c r="D10" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A10,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A10,Fontes!$J$2:$J$45)</f>
         <v>20.75</v>
       </c>
       <c r="E10" s="13"/>
@@ -7965,7 +8559,7 @@
         <v>162</v>
       </c>
       <c r="D11" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A11,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A11,Fontes!$J$2:$J$45)</f>
         <v>4.5</v>
       </c>
       <c r="E11" s="13"/>
@@ -7987,7 +8581,7 @@
         <v>162</v>
       </c>
       <c r="D12" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A12,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A12,Fontes!$J$2:$J$45)</f>
         <v>0.7099</v>
       </c>
       <c r="E12" s="13"/>
@@ -8009,7 +8603,7 @@
         <v>134</v>
       </c>
       <c r="D13" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A13,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A13,Fontes!$J$2:$J$45)</f>
         <v>2.62262295081967</v>
       </c>
       <c r="E13" s="13"/>
@@ -8020,7 +8614,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>279</v>
       </c>
@@ -8030,38 +8624,38 @@
       <c r="C14" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A14,Fontes!$J$2:$J$56)</f>
-        <v>12.34</v>
+      <c r="D14" s="32" t="n">
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A14,Fontes!$J$2:$J$45)</f>
+        <v>5</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D15" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A15,Fontes!$J$2:$J$56)</f>
-        <v>28.17</v>
+      <c r="D15" s="32" t="n">
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A15,Fontes!$J$2:$J$45)</f>
+        <v>15</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>245</v>
+        <v>281</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8075,7 +8669,7 @@
         <v>162</v>
       </c>
       <c r="D16" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A16,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A16,Fontes!$J$2:$J$45)</f>
         <v>4.72</v>
       </c>
       <c r="E16" s="13"/>
@@ -8097,7 +8691,7 @@
         <v>162</v>
       </c>
       <c r="D17" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A17,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A17,Fontes!$J$2:$J$45)</f>
         <v>187.52</v>
       </c>
       <c r="E17" s="13"/>
@@ -8119,7 +8713,7 @@
         <v>293</v>
       </c>
       <c r="D18" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A18,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A18,Fontes!$J$2:$J$45)</f>
         <v>40.7</v>
       </c>
       <c r="E18" s="13"/>
@@ -8141,7 +8735,7 @@
         <v>134</v>
       </c>
       <c r="D19" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A19,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A19,Fontes!$J$2:$J$45)</f>
         <v>4.36</v>
       </c>
       <c r="E19" s="13"/>
@@ -8163,7 +8757,7 @@
         <v>293</v>
       </c>
       <c r="D20" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A20,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A20,Fontes!$J$2:$J$45)</f>
         <v>28.52</v>
       </c>
       <c r="E20" s="13"/>
@@ -8185,7 +8779,7 @@
         <v>162</v>
       </c>
       <c r="D21" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A21,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A21,Fontes!$J$2:$J$45)</f>
         <v>769.32</v>
       </c>
       <c r="E21" s="13"/>
@@ -8206,7 +8800,7 @@
       <c r="C22" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="D22" s="32" t="n">
+      <c r="D22" s="34" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="13"/>
@@ -8228,7 +8822,7 @@
         <v>162</v>
       </c>
       <c r="D23" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A23,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A23,'Fontes RFID'!$J$2:$J$12)</f>
         <v>2.3741</v>
       </c>
       <c r="E23" s="13"/>
@@ -8250,7 +8844,7 @@
         <v>162</v>
       </c>
       <c r="D24" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A24,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A24,'Fontes RFID'!$J$2:$J$12)</f>
         <v>0.0063</v>
       </c>
       <c r="E24" s="13"/>
@@ -8272,7 +8866,7 @@
         <v>162</v>
       </c>
       <c r="D25" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A25,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A25,'Fontes RFID'!$J$2:$J$12)</f>
         <v>29.89</v>
       </c>
       <c r="E25" s="13"/>
@@ -8294,7 +8888,7 @@
         <v>162</v>
       </c>
       <c r="D26" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A26,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A26,'Fontes RFID'!$J$2:$J$12)</f>
         <v>42.65</v>
       </c>
       <c r="E26" s="13"/>
@@ -8316,7 +8910,7 @@
         <v>293</v>
       </c>
       <c r="D27" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A27,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A27,'Fontes RFID'!$J$2:$J$12)</f>
         <v>34.05</v>
       </c>
       <c r="E27" s="13"/>
@@ -8338,7 +8932,7 @@
         <v>162</v>
       </c>
       <c r="D28" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A28,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A28,'Fontes RFID'!$J$2:$J$12)</f>
         <v>6.507</v>
       </c>
       <c r="E28" s="13"/>
@@ -8387,13 +8981,13 @@
         <f aca="false">E30*Premissas!$B$2*Premissas!$B$3</f>
         <v>622.08185</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="35" t="n">
         <v>65</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G30" s="33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8411,13 +9005,13 @@
         <f aca="false">E31*Premissas!$B$2*Premissas!$B$3</f>
         <v>2105.5078</v>
       </c>
-      <c r="E31" s="33" t="n">
+      <c r="E31" s="35" t="n">
         <v>220</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="G31" s="34" t="s">
+      <c r="G31" s="33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8435,13 +9029,13 @@
         <f aca="false">E32*Premissas!$B$2*Premissas!$B$3</f>
         <v>86.13441</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="35" t="n">
         <v>9</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="G32" s="33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8459,13 +9053,13 @@
         <f aca="false">E33*Premissas!$B$2*Premissas!$B$3</f>
         <v>210.55078</v>
       </c>
-      <c r="E33" s="33" t="n">
+      <c r="E33" s="35" t="n">
         <v>22</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="G33" s="34" t="s">
+      <c r="G33" s="33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8483,13 +9077,13 @@
         <f aca="false">E34*Premissas!$B$2*Premissas!$B$3</f>
         <v>334.96715</v>
       </c>
-      <c r="E34" s="33" t="n">
+      <c r="E34" s="35" t="n">
         <v>35</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="G34" s="34" t="s">
+      <c r="G34" s="33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8503,14 +9097,14 @@
       <c r="C35" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="36" t="n">
         <v>15000</v>
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="G35" s="34" t="s">
+      <c r="G35" s="33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -8549,7 +9143,7 @@
         <v>134</v>
       </c>
       <c r="D37" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A37,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A37,Fontes!$J$2:$J$45)</f>
         <v>9.2378</v>
       </c>
       <c r="E37" s="13"/>
@@ -8571,7 +9165,7 @@
         <v>162</v>
       </c>
       <c r="D38" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A38,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A38,Fontes!$J$2:$J$45)</f>
         <v>6.495</v>
       </c>
       <c r="E38" s="13"/>
@@ -8593,7 +9187,7 @@
         <v>162</v>
       </c>
       <c r="D39" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A39,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A39,Fontes!$J$2:$J$45)</f>
         <v>64</v>
       </c>
       <c r="E39" s="13"/>
@@ -8615,7 +9209,7 @@
         <v>293</v>
       </c>
       <c r="D40" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A40,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A40,Fontes!$J$2:$J$45)</f>
         <v>285.99</v>
       </c>
       <c r="E40" s="13"/>
@@ -8637,7 +9231,7 @@
         <v>293</v>
       </c>
       <c r="D41" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A41,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A41,Fontes!$J$2:$J$45)</f>
         <v>705.69</v>
       </c>
       <c r="E41" s="13"/>
@@ -8659,7 +9253,7 @@
         <v>162</v>
       </c>
       <c r="D42" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A42,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A42,Fontes!$J$2:$J$45)</f>
         <v>368.1</v>
       </c>
       <c r="E42" s="13"/>
@@ -8681,7 +9275,7 @@
         <v>293</v>
       </c>
       <c r="D43" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A43,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A43,Fontes!$J$2:$J$45)</f>
         <v>431.08</v>
       </c>
       <c r="E43" s="13"/>
@@ -8703,7 +9297,7 @@
         <v>162</v>
       </c>
       <c r="D44" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A44,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF('Fontes RFID'!$A$2:$A$12,A44,'Fontes RFID'!$J$2:$J$12)</f>
         <v>27.4</v>
       </c>
       <c r="E44" s="13"/>
@@ -8724,15 +9318,15 @@
       <c r="C45" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="D45" s="36" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A45,Fontes!$J$2:$J$56)</f>
+      <c r="D45" s="32" t="n">
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A45,Fontes!$J$2:$J$45)</f>
         <v>350</v>
       </c>
       <c r="E45" s="13"/>
       <c r="F45" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="G45" s="34" t="s">
+      <c r="G45" s="33" t="s">
         <v>380</v>
       </c>
     </row>
@@ -8747,7 +9341,7 @@
         <v>293</v>
       </c>
       <c r="D46" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A46,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A46,Fontes!$J$2:$J$45)</f>
         <v>66.66</v>
       </c>
       <c r="E46" s="13"/>
@@ -8769,7 +9363,7 @@
         <v>162</v>
       </c>
       <c r="D47" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A47,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A47,Fontes!$J$2:$J$45)</f>
         <v>93.63</v>
       </c>
       <c r="E47" s="13"/>
@@ -8791,7 +9385,7 @@
         <v>162</v>
       </c>
       <c r="D48" s="30" t="n">
-        <f aca="false">SUMIF(Fontes!$A$2:$A$56,A48,Fontes!$J$2:$J$56)</f>
+        <f aca="false">SUMIF(Fontes!$A$2:$A$45,A48,Fontes!$J$2:$J$45)</f>
         <v>25.611</v>
       </c>
       <c r="E48" s="13"/>
@@ -8818,7 +9412,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -8888,7 +9482,7 @@
       <c r="E2" s="37" t="s">
         <v>404</v>
       </c>
-      <c r="F2" s="32" t="n">
+      <c r="F2" s="34" t="n">
         <v>10.97</v>
       </c>
       <c r="G2" s="13" t="s">
@@ -8927,7 +9521,7 @@
       <c r="E3" s="37" t="s">
         <v>410</v>
       </c>
-      <c r="F3" s="32" t="n">
+      <c r="F3" s="34" t="n">
         <v>20.17</v>
       </c>
       <c r="G3" s="13" t="s">
@@ -8966,7 +9560,7 @@
       <c r="E4" s="37" t="s">
         <v>415</v>
       </c>
-      <c r="F4" s="32" t="n">
+      <c r="F4" s="34" t="n">
         <v>37.9</v>
       </c>
       <c r="G4" s="13" t="s">
@@ -9005,7 +9599,7 @@
       <c r="E5" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="34" t="n">
         <v>8.9</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -9083,7 +9677,7 @@
       <c r="E7" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="34" t="n">
         <v>189.98</v>
       </c>
       <c r="G7" s="13" t="s">
@@ -9122,7 +9716,7 @@
       <c r="E8" s="37" t="s">
         <v>437</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="34" t="n">
         <v>591.68</v>
       </c>
       <c r="G8" s="13" t="s">
@@ -9161,7 +9755,7 @@
       <c r="E9" s="37" t="s">
         <v>441</v>
       </c>
-      <c r="F9" s="32" t="n">
+      <c r="F9" s="34" t="n">
         <v>10.9</v>
       </c>
       <c r="G9" s="13" t="s">
@@ -9200,7 +9794,7 @@
       <c r="E10" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="34" t="n">
         <v>20.75</v>
       </c>
       <c r="G10" s="13" t="s">
@@ -9239,7 +9833,7 @@
       <c r="E11" s="37" t="s">
         <v>450</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="34" t="n">
         <v>4.5</v>
       </c>
       <c r="G11" s="13" t="s">
@@ -9278,7 +9872,7 @@
       <c r="E12" s="37" t="s">
         <v>455</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="34" t="n">
         <v>70.99</v>
       </c>
       <c r="G12" s="13" t="s">
@@ -9317,7 +9911,7 @@
       <c r="E13" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="34" t="n">
         <v>799.9</v>
       </c>
       <c r="G13" s="13" t="s">
@@ -9340,7 +9934,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>279</v>
       </c>
@@ -9348,19 +9942,19 @@
         <v>461</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>402</v>
+        <v>282</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="F14" s="32" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>405</v>
+      <c r="F14" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>464</v>
       </c>
       <c r="H14" s="18" t="n">
         <v>1</v>
@@ -9370,36 +9964,36 @@
       </c>
       <c r="J14" s="30" t="n">
         <f aca="false">F14/H14*I14</f>
-        <v>12.34</v>
+        <v>5</v>
       </c>
       <c r="K14" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L14" s="38" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>402</v>
-      </c>
       <c r="D15" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>467</v>
-      </c>
-      <c r="F15" s="32" t="n">
-        <v>28.17</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>405</v>
+        <v>462</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>464</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>1</v>
@@ -9409,13 +10003,13 @@
       </c>
       <c r="J15" s="30" t="n">
         <f aca="false">F15/H15*I15</f>
-        <v>28.17</v>
+        <v>15</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L15" s="38" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9423,18 +10017,18 @@
         <v>285</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="37" t="s">
         <v>471</v>
       </c>
-      <c r="E16" s="37" t="s">
-        <v>472</v>
-      </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="34" t="n">
         <v>2.38</v>
       </c>
       <c r="G16" s="13" t="s">
@@ -9454,7 +10048,7 @@
         <v>406</v>
       </c>
       <c r="L16" s="38" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9462,18 +10056,18 @@
         <v>285</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="37" t="s">
         <v>476</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="34" t="n">
         <v>1.17</v>
       </c>
       <c r="G17" s="13" t="s">
@@ -9493,7 +10087,7 @@
         <v>406</v>
       </c>
       <c r="L17" s="38" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9501,18 +10095,18 @@
         <v>288</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>402</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="E18" s="37" t="s">
-        <v>481</v>
-      </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="34" t="n">
         <v>166.12</v>
       </c>
       <c r="G18" s="13" t="s">
@@ -9532,7 +10126,7 @@
         <v>406</v>
       </c>
       <c r="L18" s="38" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9540,18 +10134,18 @@
         <v>288</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>402</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="E19" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="E19" s="37" t="s">
-        <v>485</v>
-      </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="34" t="n">
         <v>15.57</v>
       </c>
       <c r="G19" s="13" t="s">
@@ -9571,7 +10165,7 @@
         <v>406</v>
       </c>
       <c r="L19" s="38" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,18 +10173,18 @@
         <v>288</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>402</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="E20" s="37" t="s">
-        <v>489</v>
-      </c>
-      <c r="F20" s="32" t="n">
+      <c r="F20" s="34" t="n">
         <v>5.83</v>
       </c>
       <c r="G20" s="13" t="s">
@@ -9610,7 +10204,7 @@
         <v>406</v>
       </c>
       <c r="L20" s="38" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9618,18 +10212,18 @@
         <v>291</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>402</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="E21" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="34" t="n">
         <v>3.96</v>
       </c>
       <c r="G21" s="13" t="s">
@@ -9649,7 +10243,7 @@
         <v>406</v>
       </c>
       <c r="L21" s="38" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9657,22 +10251,22 @@
         <v>291</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="37" t="s">
         <v>497</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="F22" s="34" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G22" s="13" t="s">
         <v>498</v>
-      </c>
-      <c r="F22" s="32" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>499</v>
       </c>
       <c r="H22" s="18" t="n">
         <v>1</v>
@@ -9688,7 +10282,7 @@
         <v>406</v>
       </c>
       <c r="L22" s="38" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9696,18 +10290,18 @@
         <v>291</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="37" t="s">
         <v>476</v>
       </c>
-      <c r="E23" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="34" t="n">
         <v>1.17</v>
       </c>
       <c r="G23" s="13" t="s">
@@ -9727,7 +10321,7 @@
         <v>406</v>
       </c>
       <c r="L23" s="38" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9735,18 +10329,18 @@
         <v>295</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="37" t="s">
         <v>504</v>
       </c>
-      <c r="E24" s="37" t="s">
-        <v>505</v>
-      </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="34" t="n">
         <v>8.72</v>
       </c>
       <c r="G24" s="13" t="s">
@@ -9766,7 +10360,7 @@
         <v>406</v>
       </c>
       <c r="L24" s="38" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9774,22 +10368,22 @@
         <v>298</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" s="37" t="s">
         <v>508</v>
       </c>
-      <c r="E25" s="37" t="s">
-        <v>509</v>
-      </c>
-      <c r="F25" s="32" t="n">
+      <c r="F25" s="34" t="n">
         <v>15.52</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>1</v>
@@ -9805,7 +10399,7 @@
         <v>406</v>
       </c>
       <c r="L25" s="38" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9813,22 +10407,22 @@
         <v>298</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="E26" s="37" t="s">
         <v>513</v>
       </c>
-      <c r="E26" s="37" t="s">
-        <v>514</v>
-      </c>
-      <c r="F26" s="32" t="n">
+      <c r="F26" s="34" t="n">
         <v>91</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H26" s="18" t="n">
         <v>1400</v>
@@ -9844,7 +10438,7 @@
         <v>406</v>
       </c>
       <c r="L26" s="38" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9852,18 +10446,18 @@
         <v>301</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>453</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="E27" s="37" t="s">
         <v>517</v>
       </c>
-      <c r="E27" s="37" t="s">
-        <v>518</v>
-      </c>
-      <c r="F27" s="32" t="n">
+      <c r="F27" s="34" t="n">
         <v>769.32</v>
       </c>
       <c r="G27" s="13" t="s">
@@ -9883,108 +10477,108 @@
         <v>406</v>
       </c>
       <c r="L27" s="38" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="C28" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="E28" s="37" t="s">
         <v>521</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>523</v>
-      </c>
-      <c r="F28" s="32" t="n">
-        <v>237.41</v>
+      <c r="F28" s="34" t="n">
+        <v>461.89</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>524</v>
+        <v>405</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I28" s="18" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="30" t="n">
         <f aca="false">F28/H28*I28</f>
-        <v>2.3741</v>
+        <v>9.2378</v>
       </c>
       <c r="K28" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L28" s="38" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>528</v>
-      </c>
-      <c r="F29" s="32" t="n">
-        <v>18.9</v>
+        <v>525</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>64.95</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>3000</v>
+        <v>10</v>
       </c>
       <c r="I29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="30" t="n">
         <f aca="false">F29/H29*I29</f>
-        <v>0.0063</v>
+        <v>6.495</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L29" s="38" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="E30" s="37" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>532</v>
-      </c>
-      <c r="F30" s="32" t="n">
-        <v>29.89</v>
+      <c r="F30" s="34" t="n">
+        <v>64</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="H30" s="18" t="n">
         <v>1</v>
@@ -9994,33 +10588,33 @@
       </c>
       <c r="J30" s="30" t="n">
         <f aca="false">F30/H30*I30</f>
-        <v>29.89</v>
+        <v>64</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L30" s="38" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="E31" s="37" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>536</v>
-      </c>
-      <c r="F31" s="32" t="n">
-        <v>42.65</v>
+      <c r="F31" s="34" t="n">
+        <v>285.99</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>405</v>
@@ -10033,36 +10627,36 @@
       </c>
       <c r="J31" s="30" t="n">
         <f aca="false">F31/H31*I31</f>
-        <v>42.65</v>
+        <v>285.99</v>
       </c>
       <c r="K31" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L31" s="38" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="E32" s="37" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>539</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>541</v>
-      </c>
-      <c r="F32" s="35" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>542</v>
+      <c r="F32" s="34" t="n">
+        <v>487.9</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>498</v>
       </c>
       <c r="H32" s="18" t="n">
         <v>1</v>
@@ -10072,33 +10666,33 @@
       </c>
       <c r="J32" s="30" t="n">
         <f aca="false">F32/H32*I32</f>
-        <v>25</v>
+        <v>487.9</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L32" s="38" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>546</v>
-      </c>
-      <c r="F33" s="32" t="n">
-        <v>4.66</v>
+        <v>541</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>57.79</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>405</v>
@@ -10111,36 +10705,36 @@
       </c>
       <c r="J33" s="30" t="n">
         <f aca="false">F33/H33*I33</f>
-        <v>4.66</v>
+        <v>57.79</v>
       </c>
       <c r="K33" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L33" s="38" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>550</v>
-      </c>
-      <c r="F34" s="32" t="n">
-        <v>4.18</v>
+        <v>545</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>160</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="H34" s="18" t="n">
         <v>1</v>
@@ -10150,33 +10744,33 @@
       </c>
       <c r="J34" s="30" t="n">
         <f aca="false">F34/H34*I34</f>
-        <v>4.18</v>
+        <v>160</v>
       </c>
       <c r="K34" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L34" s="38" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E35" s="37" t="s">
-        <v>554</v>
-      </c>
-      <c r="F35" s="32" t="n">
-        <v>0.21</v>
+        <v>549</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <v>368.1</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>405</v>
@@ -10189,36 +10783,36 @@
       </c>
       <c r="J35" s="30" t="n">
         <f aca="false">F35/H35*I35</f>
-        <v>0.21</v>
+        <v>368.1</v>
       </c>
       <c r="K35" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L35" s="38" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>558</v>
-      </c>
-      <c r="F36" s="32" t="n">
-        <v>5.94</v>
+        <v>553</v>
+      </c>
+      <c r="F36" s="34" t="n">
+        <v>342.95</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="H36" s="18" t="n">
         <v>1</v>
@@ -10228,153 +10822,153 @@
       </c>
       <c r="J36" s="30" t="n">
         <f aca="false">F36/H36*I36</f>
-        <v>5.94</v>
+        <v>342.95</v>
       </c>
       <c r="K36" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L36" s="38" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>496</v>
+        <v>453</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>562</v>
-      </c>
-      <c r="F37" s="32" t="n">
-        <v>18.9</v>
+        <v>557</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>72.99</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>499</v>
+        <v>405</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J37" s="30" t="n">
         <f aca="false">F37/H37*I37</f>
-        <v>0.567</v>
+        <v>72.99</v>
       </c>
       <c r="K37" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L37" s="38" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>453</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>566</v>
-      </c>
-      <c r="F38" s="32" t="n">
-        <v>461.89</v>
+        <v>561</v>
+      </c>
+      <c r="F38" s="34" t="n">
+        <v>7.57</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>405</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="30" t="n">
         <f aca="false">F38/H38*I38</f>
-        <v>9.2378</v>
+        <v>15.14</v>
       </c>
       <c r="K38" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L38" s="38" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>564</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="F39" s="36" t="n">
+        <v>350</v>
+      </c>
+      <c r="G39" s="33" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="E39" s="37" t="s">
-        <v>570</v>
-      </c>
-      <c r="F39" s="32" t="n">
-        <v>64.95</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>499</v>
-      </c>
       <c r="H39" s="18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I39" s="18" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="30" t="n">
         <f aca="false">F39/H39*I39</f>
-        <v>6.495</v>
+        <v>350</v>
       </c>
       <c r="K39" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L39" s="38" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B40" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="E40" s="37" t="s">
         <v>572</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>574</v>
-      </c>
-      <c r="F40" s="32" t="n">
-        <v>64</v>
+      <c r="F40" s="34" t="n">
+        <v>9.5</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>499</v>
+        <v>405</v>
       </c>
       <c r="H40" s="18" t="n">
         <v>1</v>
@@ -10384,33 +10978,33 @@
       </c>
       <c r="J40" s="30" t="n">
         <f aca="false">F40/H40*I40</f>
-        <v>64</v>
+        <v>9.5</v>
       </c>
       <c r="K40" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L40" s="38" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B41" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="E41" s="37" t="s">
         <v>576</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>578</v>
-      </c>
-      <c r="F41" s="32" t="n">
-        <v>285.99</v>
+      <c r="F41" s="34" t="n">
+        <v>30.91</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>405</v>
@@ -10419,76 +11013,76 @@
         <v>1</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" s="30" t="n">
         <f aca="false">F41/H41*I41</f>
-        <v>285.99</v>
+        <v>15.455</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L41" s="38" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="B42" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="E42" s="37" t="s">
         <v>580</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>582</v>
-      </c>
-      <c r="F42" s="32" t="n">
-        <v>487.9</v>
+      <c r="F42" s="34" t="n">
+        <v>3.28</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>499</v>
+        <v>405</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="30" t="n">
         <f aca="false">F42/H42*I42</f>
-        <v>487.9</v>
+        <v>0.656</v>
       </c>
       <c r="K42" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L42" s="38" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="B43" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="E43" s="37" t="s">
         <v>585</v>
       </c>
-      <c r="E43" s="37" t="s">
-        <v>586</v>
-      </c>
-      <c r="F43" s="32" t="n">
-        <v>57.79</v>
+      <c r="F43" s="34" t="n">
+        <v>35.75</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>405</v>
@@ -10501,36 +11095,36 @@
       </c>
       <c r="J43" s="30" t="n">
         <f aca="false">F43/H43*I43</f>
-        <v>57.79</v>
+        <v>35.75</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L43" s="38" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>588</v>
-      </c>
       <c r="C44" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>590</v>
-      </c>
-      <c r="F44" s="32" t="n">
-        <v>160</v>
+        <v>576</v>
+      </c>
+      <c r="F44" s="34" t="n">
+        <v>30.91</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>499</v>
+        <v>405</v>
       </c>
       <c r="H44" s="18" t="n">
         <v>1</v>
@@ -10540,33 +11134,33 @@
       </c>
       <c r="J44" s="30" t="n">
         <f aca="false">F44/H44*I44</f>
-        <v>160</v>
+        <v>30.91</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L44" s="38" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>453</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>594</v>
-      </c>
-      <c r="F45" s="32" t="n">
-        <v>368.1</v>
+        <v>591</v>
+      </c>
+      <c r="F45" s="34" t="n">
+        <v>93.63</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>405</v>
@@ -10579,442 +11173,13 @@
       </c>
       <c r="J45" s="30" t="n">
         <f aca="false">F45/H45*I45</f>
-        <v>368.1</v>
+        <v>93.63</v>
       </c>
       <c r="K45" s="13" t="s">
         <v>406</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>598</v>
-      </c>
-      <c r="F46" s="32" t="n">
-        <v>342.95</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H46" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="30" t="n">
-        <f aca="false">F46/H46*I46</f>
-        <v>342.95</v>
-      </c>
-      <c r="K46" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L46" s="38" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>602</v>
-      </c>
-      <c r="F47" s="32" t="n">
-        <v>72.99</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H47" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="30" t="n">
-        <f aca="false">F47/H47*I47</f>
-        <v>72.99</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L47" s="38" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>606</v>
-      </c>
-      <c r="F48" s="32" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H48" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="30" t="n">
-        <f aca="false">F48/H48*I48</f>
-        <v>15.14</v>
-      </c>
-      <c r="K48" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L48" s="38" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>610</v>
-      </c>
-      <c r="F49" s="32" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H49" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="30" t="n">
-        <f aca="false">F49/H49*I49</f>
-        <v>27.4</v>
-      </c>
-      <c r="K49" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L49" s="38" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>613</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="F50" s="35" t="n">
-        <v>350</v>
-      </c>
-      <c r="G50" s="34" t="s">
-        <v>616</v>
-      </c>
-      <c r="H50" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="30" t="n">
-        <f aca="false">F50/H50*I50</f>
-        <v>350</v>
-      </c>
-      <c r="K50" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L50" s="38" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>619</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>621</v>
-      </c>
-      <c r="F51" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H51" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="30" t="n">
-        <f aca="false">F51/H51*I51</f>
-        <v>9.5</v>
-      </c>
-      <c r="K51" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L51" s="38" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>625</v>
-      </c>
-      <c r="F52" s="32" t="n">
-        <v>30.91</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H52" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J52" s="30" t="n">
-        <f aca="false">F52/H52*I52</f>
-        <v>15.455</v>
-      </c>
-      <c r="K52" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L52" s="38" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>629</v>
-      </c>
-      <c r="F53" s="32" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H53" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="30" t="n">
-        <f aca="false">F53/H53*I53</f>
-        <v>0.656</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L53" s="38" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>632</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>634</v>
-      </c>
-      <c r="F54" s="32" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H54" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="30" t="n">
-        <f aca="false">F54/H54*I54</f>
-        <v>35.75</v>
-      </c>
-      <c r="K54" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L54" s="38" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>625</v>
-      </c>
-      <c r="F55" s="32" t="n">
-        <v>30.91</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H55" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="30" t="n">
-        <f aca="false">F55/H55*I55</f>
-        <v>30.91</v>
-      </c>
-      <c r="K55" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L55" s="38" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>639</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>640</v>
-      </c>
-      <c r="F56" s="32" t="n">
-        <v>93.63</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="H56" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="30" t="n">
-        <f aca="false">F56/H56*I56</f>
-        <v>93.63</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="L56" s="38" t="s">
-        <v>641</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -11031,48 +11196,35 @@
     <hyperlink ref="E11" r:id="rId10" display="https://www.multcomercial.com.br/conector-jack-rj45-femea-com-8-vias-blindado-90-pci-jl46057.html"/>
     <hyperlink ref="E12" r:id="rId11" display="https://www.kabum.com.br/produto/328777/plug-conector-rj45-macho-cat-5e-8-vias-crimpar-100-unidades-"/>
     <hyperlink ref="E13" r:id="rId12" display="https://www.kabum.com.br/produto/114681/cabo-de-rede-cat-5e-furukawa-305-metros-branco-23200101"/>
-    <hyperlink ref="E14" r:id="rId13" display="https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-075-para-montagem-36-x-60-x-75-mm-4390.html"/>
-    <hyperlink ref="E15" r:id="rId14" display="https://www.usinainfo.com.br/caixas-patola/caixa-patola-case-para-montagem-53-x-85-x-124-mm-pb-112-3879.html"/>
-    <hyperlink ref="E16" r:id="rId15" display="https://www.eletrogate.com/placa-fenolite-perfurada-7x5cm"/>
-    <hyperlink ref="E17" r:id="rId16" display="https://www.baudaeletronica.com.br/produto/borne-kre-kf128-2-vias-verde.html"/>
-    <hyperlink ref="E18" r:id="rId17" display="https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-22070-para-montagem-71-x-228-x-190-mm-4383.html"/>
-    <hyperlink ref="E19" r:id="rId18" display="https://www.usinainfo.com.br/coolers-para-pc/cooler-pc-40x40mm-fan-12v-3041.html"/>
-    <hyperlink ref="E20" r:id="rId19" display="https://www.usinainfo.com.br/coolers-para-pc/grade-para-cooler-40mm-metalica-8398.html"/>
-    <hyperlink ref="E21" r:id="rId20" display="https://www.usinainfo.com.br/caixas-patola/trilho-din-patola-fdo-037-para-projetos-8532.html"/>
-    <hyperlink ref="E22" r:id="rId21" display="https://www.leroymerlin.com.br/minidisjuntor-unipolar-2a-mdwp-c2a-weg_1572704659"/>
-    <hyperlink ref="E23" r:id="rId22" display="https://www.baudaeletronica.com.br/produto/borne-kre-kf128-2-vias-verde.html"/>
-    <hyperlink ref="E24" r:id="rId23" display="https://www.telhanorte.com.br/canaleta-pvc-20x10mm-2m-com-adesivo-preto-forceline-2633671/p"/>
-    <hyperlink ref="E25" r:id="rId24" display="https://www.leroymerlin.com.br/abracadeira-de-nylon-200x2,5mm-preta-com-100-pecas-vonder_1567218483"/>
-    <hyperlink ref="E26" r:id="rId25" display="https://www.kalunga.com.br/prod/etiqueta-ink-jet-laser-carta-33-9x101-6-6182-pimaco-pt-1400-un/278998"/>
-    <hyperlink ref="E27" r:id="rId26" display="https://www.kabum.com.br/produto/429922/switch-tp-link-tl-sg1024de-24-portas-10-100-1000-gigabit-gerenciavel-rack"/>
-    <hyperlink ref="E28" r:id="rId27" display="https://loja.lojarfid.com.br/13-56-mhz-mf/etiquetas/etiqueta-rfid-13-56-mhz-nfc-ntag213-branca-100-unidades"/>
-    <hyperlink ref="E29" r:id="rId28" display="https://www.kalunga.com.br/prod/fita-adesiva-transparente-pp-45mm-x-45m-stick-tape-pt-4-un/305591"/>
-    <hyperlink ref="E30" r:id="rId29" display="https://www.usinainfo.com.br/esp32/esp32-c3-super-mini-com-wifi-e-bluetooth-com-usb-c-8967.html"/>
-    <hyperlink ref="E31" r:id="rId30" display="https://www.makerhero.com/produto/kit-modulo-leitor-rfid-nfc-pn532/"/>
-    <hyperlink ref="E32" r:id="rId31" display="https://www.robocore.net/loja/baterias/bateria-lipo-1s-530mah-30c"/>
-    <hyperlink ref="E33" r:id="rId32" display="https://www.eletrogate.com/modulo-carregador-de-baterias-de-litio-tp4056-com-protecao-usb-c"/>
-    <hyperlink ref="E34" r:id="rId33" display="https://www.eletrogate.com/micro-motor-de-vibracao-vibracall"/>
-    <hyperlink ref="E35" r:id="rId34" display="https://www.eletrogate.com/push-button-chave-tactil-6x6x6mm"/>
-    <hyperlink ref="E36" r:id="rId35" display="https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-060-para-montagem-29-x-52-x-64-mm-8284.html"/>
-    <hyperlink ref="E37" r:id="rId36" display="https://www.leroymerlin.com.br/fita-fecho-de-contato-%7C-organizador-de-cabos-preto-%7C-rolo-10m-x-10mm_1571751164"/>
-    <hyperlink ref="E38" r:id="rId37" display="https://www.kabum.com.br/produto/722927/cabo-pp-3x1-00-mm-eletrico-flexivel-preto-50-metros"/>
-    <hyperlink ref="E39" r:id="rId38" display="https://www.leroymerlin.com.br/pino-plug-macho-ilumi-prensa-cabo-2p-t-10a-embalagem-com-10-unidades_1568301310"/>
-    <hyperlink ref="E40" r:id="rId39" display="https://www.leroymerlin.com.br/protetor-de-surto-dps-classe-ii-iii-20ka-275vca-fase_1570251308"/>
-    <hyperlink ref="E41" r:id="rId40" display="https://www.kabum.com.br/produto/386101/kit-cabo-de-rede-nexans-40-metros-alicate-testador-10xrj45-cat5e"/>
-    <hyperlink ref="E42" r:id="rId41" display="https://www.leroymerlin.com.br/estacao-de-solda-analogica-60w-220v-hk936a-preta-hikari_1566757438"/>
-    <hyperlink ref="E43" r:id="rId42" display="https://www.usinainfo.com.br/multimetros/multimetro-digital-hikari-hm-1001-cat-i-1000v-5502.html"/>
-    <hyperlink ref="E44" r:id="rId43" display="https://www.leroymerlin.com.br/solda-estanho-cobix-1-0mm-60x40-500g_1566817011"/>
-    <hyperlink ref="E45" r:id="rId44" display="https://www.kabum.com.br/produto/229971/nobreak-intelbras-xnb-720va-bivolt-4822010"/>
-    <hyperlink ref="E46" r:id="rId45" display="https://www.kabum.com.br/produto/291255/mini-rack-05u-x-19p-x-370mm-montado-mrm-537-preto-intelbras"/>
-    <hyperlink ref="E47" r:id="rId46" display="https://www.kabum.com.br/produto/235380/organizador-de-cabos-intelbras-para-rack-1u-40-mm-och1u-40"/>
-    <hyperlink ref="E48" r:id="rId47" display="https://www.kabum.com.br/produto/233241/cabo-de-rede-md9-patch-cord-1-5m-azul-cat5e"/>
-    <hyperlink ref="E49" r:id="rId48" display="https://www.kabum.com.br/produto/394690/carregador-de-tomada-universal-usb-kaidi-carregador-domestico-2-portas-branco-kd-301"/>
-    <hyperlink ref="E51" r:id="rId49" display="https://www.luzautomacao.com.br/produto/sinaleiro-led-22mm-12v-amarelo-metaltex"/>
-    <hyperlink ref="E52" r:id="rId50" display="https://www.leroymerlin.com.br/perfil-aluminio-preto-l-013-cantoneira-1-pol-25mm-acabamento-canto-parede-barra-1-mt_1572585517"/>
-    <hyperlink ref="E53" r:id="rId51" display="https://www.usinainfo.com.br/transistor-bc/transistor-bc337-para-projetos-kit-com-5-unidades-2998.html"/>
-    <hyperlink ref="E54" r:id="rId52" display="https://www.keymoveis.com.br/plano-de-mdf-cru-120x60"/>
-    <hyperlink ref="E55" r:id="rId53" display="https://www.leroymerlin.com.br/perfil-aluminio-preto-l-013-cantoneira-1-pol-25mm-acabamento-canto-parede-barra-1-mt_1572585517"/>
-    <hyperlink ref="E56" r:id="rId54" display="https://www.kabum.com.br/produto/205611/switch-5-portas-10-100-1000-gigabit-mesa-tl-sg1005d-tp-link"/>
+    <hyperlink ref="E16" r:id="rId13" display="https://www.eletrogate.com/placa-fenolite-perfurada-7x5cm"/>
+    <hyperlink ref="E17" r:id="rId14" display="https://www.baudaeletronica.com.br/produto/borne-kre-kf128-2-vias-verde.html"/>
+    <hyperlink ref="E18" r:id="rId15" display="https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-22070-para-montagem-71-x-228-x-190-mm-4383.html"/>
+    <hyperlink ref="E19" r:id="rId16" display="https://www.usinainfo.com.br/coolers-para-pc/cooler-pc-40x40mm-fan-12v-3041.html"/>
+    <hyperlink ref="E20" r:id="rId17" display="https://www.usinainfo.com.br/coolers-para-pc/grade-para-cooler-40mm-metalica-8398.html"/>
+    <hyperlink ref="E21" r:id="rId18" display="https://www.usinainfo.com.br/caixas-patola/trilho-din-patola-fdo-037-para-projetos-8532.html"/>
+    <hyperlink ref="E22" r:id="rId19" display="https://www.leroymerlin.com.br/minidisjuntor-unipolar-2a-mdwp-c2a-weg_1572704659"/>
+    <hyperlink ref="E23" r:id="rId20" display="https://www.baudaeletronica.com.br/produto/borne-kre-kf128-2-vias-verde.html"/>
+    <hyperlink ref="E24" r:id="rId21" display="https://www.telhanorte.com.br/canaleta-pvc-20x10mm-2m-com-adesivo-preto-forceline-2633671/p"/>
+    <hyperlink ref="E25" r:id="rId22" display="https://www.leroymerlin.com.br/abracadeira-de-nylon-200x2,5mm-preta-com-100-pecas-vonder_1567218483"/>
+    <hyperlink ref="E26" r:id="rId23" display="https://www.kalunga.com.br/prod/etiqueta-ink-jet-laser-carta-33-9x101-6-6182-pimaco-pt-1400-un/278998"/>
+    <hyperlink ref="E27" r:id="rId24" display="https://www.kabum.com.br/produto/429922/switch-tp-link-tl-sg1024de-24-portas-10-100-1000-gigabit-gerenciavel-rack"/>
+    <hyperlink ref="E28" r:id="rId25" display="https://www.kabum.com.br/produto/722927/cabo-pp-3x1-00-mm-eletrico-flexivel-preto-50-metros"/>
+    <hyperlink ref="E29" r:id="rId26" display="https://www.leroymerlin.com.br/pino-plug-macho-ilumi-prensa-cabo-2p-t-10a-embalagem-com-10-unidades_1568301310"/>
+    <hyperlink ref="E30" r:id="rId27" display="https://www.leroymerlin.com.br/protetor-de-surto-dps-classe-ii-iii-20ka-275vca-fase_1570251308"/>
+    <hyperlink ref="E31" r:id="rId28" display="https://www.kabum.com.br/produto/386101/kit-cabo-de-rede-nexans-40-metros-alicate-testador-10xrj45-cat5e"/>
+    <hyperlink ref="E32" r:id="rId29" display="https://www.leroymerlin.com.br/estacao-de-solda-analogica-60w-220v-hk936a-preta-hikari_1566757438"/>
+    <hyperlink ref="E33" r:id="rId30" display="https://www.usinainfo.com.br/multimetros/multimetro-digital-hikari-hm-1001-cat-i-1000v-5502.html"/>
+    <hyperlink ref="E34" r:id="rId31" display="https://www.leroymerlin.com.br/solda-estanho-cobix-1-0mm-60x40-500g_1566817011"/>
+    <hyperlink ref="E35" r:id="rId32" display="https://www.kabum.com.br/produto/229971/nobreak-intelbras-xnb-720va-bivolt-4822010"/>
+    <hyperlink ref="E36" r:id="rId33" display="https://www.kabum.com.br/produto/291255/mini-rack-05u-x-19p-x-370mm-montado-mrm-537-preto-intelbras"/>
+    <hyperlink ref="E37" r:id="rId34" display="https://www.kabum.com.br/produto/235380/organizador-de-cabos-intelbras-para-rack-1u-40-mm-och1u-40"/>
+    <hyperlink ref="E38" r:id="rId35" display="https://www.kabum.com.br/produto/233241/cabo-de-rede-md9-patch-cord-1-5m-azul-cat5e"/>
+    <hyperlink ref="E40" r:id="rId36" display="https://www.luzautomacao.com.br/produto/sinaleiro-led-22mm-12v-amarelo-metaltex"/>
+    <hyperlink ref="E41" r:id="rId37" display="https://www.leroymerlin.com.br/perfil-aluminio-preto-l-013-cantoneira-1-pol-25mm-acabamento-canto-parede-barra-1-mt_1572585517"/>
+    <hyperlink ref="E42" r:id="rId38" display="https://www.usinainfo.com.br/transistor-bc/transistor-bc337-para-projetos-kit-com-5-unidades-2998.html"/>
+    <hyperlink ref="E43" r:id="rId39" display="https://www.keymoveis.com.br/plano-de-mdf-cru-120x60"/>
+    <hyperlink ref="E44" r:id="rId40" display="https://www.leroymerlin.com.br/perfil-aluminio-preto-l-013-cantoneira-1-pol-25mm-acabamento-canto-parede-barra-1-mt_1572585517"/>
+    <hyperlink ref="E45" r:id="rId41" display="https://www.kabum.com.br/produto/205611/switch-5-portas-10-100-1000-gigabit-mesa-tl-sg1005d-tp-link"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11089,6 +11241,518 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>596</v>
+      </c>
+      <c r="F2" s="34" t="n">
+        <v>237.41</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="30" t="n">
+        <f aca="false">F2/H2*I2</f>
+        <v>2.3741</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>601</v>
+      </c>
+      <c r="F3" s="34" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="30" t="n">
+        <f aca="false">F3/H3*I3</f>
+        <v>0.0063</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>605</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="30" t="n">
+        <f aca="false">F4/H4*I4</f>
+        <v>29.89</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L4" s="38" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>609</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="30" t="n">
+        <f aca="false">F5/H5*I5</f>
+        <v>42.65</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L5" s="38" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>612</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>614</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>615</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <f aca="false">F6/H6*I6</f>
+        <v>25</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L6" s="38" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>619</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <f aca="false">F7/H7*I7</f>
+        <v>4.66</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L7" s="38" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <f aca="false">F8/H8*I8</f>
+        <v>4.18</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L8" s="38" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>627</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="30" t="n">
+        <f aca="false">F9/H9*I9</f>
+        <v>0.21</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L9" s="38" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>631</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <f aca="false">F10/H10*I10</f>
+        <v>5.94</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L10" s="38" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>635</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <f aca="false">F11/H11*I11</f>
+        <v>0.567</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L11" s="38" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>639</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <f aca="false">F12/H12*I12</f>
+        <v>27.4</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="L12" s="38" t="s">
+        <v>640</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://loja.lojarfid.com.br/13-56-mhz-mf/etiquetas/etiqueta-rfid-13-56-mhz-nfc-ntag213-branca-100-unidades"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://www.kalunga.com.br/prod/fita-adesiva-transparente-pp-45mm-x-45m-stick-tape-pt-4-un/305591"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://www.usinainfo.com.br/esp32/esp32-c3-super-mini-com-wifi-e-bluetooth-com-usb-c-8967.html"/>
+    <hyperlink ref="E5" r:id="rId4" display="https://www.makerhero.com/produto/kit-modulo-leitor-rfid-nfc-pn532/"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://www.robocore.net/loja/baterias/bateria-lipo-1s-530mah-30c"/>
+    <hyperlink ref="E7" r:id="rId6" display="https://www.eletrogate.com/modulo-carregador-de-baterias-de-litio-tp4056-com-protecao-usb-c"/>
+    <hyperlink ref="E8" r:id="rId7" display="https://www.eletrogate.com/micro-motor-de-vibracao-vibracall"/>
+    <hyperlink ref="E9" r:id="rId8" display="https://www.eletrogate.com/push-button-chave-tactil-6x6x6mm"/>
+    <hyperlink ref="E10" r:id="rId9" display="https://www.usinainfo.com.br/caixas-patola/caixa-patola-pb-060-para-montagem-29-x-52-x-64-mm-8284.html"/>
+    <hyperlink ref="E11" r:id="rId10" display="https://www.leroymerlin.com.br/fita-fecho-de-contato-%7C-organizador-de-cabos-preto-%7C-rolo-10m-x-10mm_1571751164"/>
+    <hyperlink ref="E12" r:id="rId11" display="https://www.kabum.com.br/produto/394690/carregador-de-tomada-universal-usb-kaidi-carregador-domestico-2-portas-branco-kd-301"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -11101,7 +11765,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>236</v>
@@ -11110,18 +11774,18 @@
         <v>237</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>644</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>242</v>
@@ -11144,7 +11808,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>267</v>
@@ -11167,30 +11831,30 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>279</v>
       </c>
       <c r="C4" s="39" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B4,Preços!$A:$A,0))</f>
-        <v>Carcaça do Módulo Q (caixa Patola PB-075, 36 × 60 × 75 mm)</v>
+        <v>Carcaça do Módulo Q (impressão 3D, medida padrão compacta)</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="40" t="n">
         <f aca="false">INDEX(Preços!$D:$D,MATCH(B4,Preços!$A:$A,0))</f>
-        <v>12.34</v>
+        <v>5</v>
       </c>
       <c r="F4" s="30" t="n">
         <f aca="false">D4*E4</f>
-        <v>12.34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>270</v>
@@ -11213,7 +11877,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>276</v>
@@ -11236,7 +11900,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>273</v>
@@ -11259,7 +11923,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -11267,12 +11931,12 @@
       <c r="E8" s="16"/>
       <c r="F8" s="41" t="n">
         <f aca="false">SUM(F2:F7)</f>
-        <v>55.2250459016394</v>
+        <v>47.8850459016393</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>249</v>
@@ -11295,7 +11959,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>252</v>
@@ -11318,7 +11982,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>264</v>
@@ -11341,7 +12005,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>285</v>
@@ -11364,7 +12028,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>270</v>
@@ -11387,30 +12051,30 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C15" s="39" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B15,Preços!$A:$A,0))</f>
-        <v>Carcaça do Módulo E+Q / Nó de coluna (caixa Patola PB-112, 53 × 85 × 124 mm)</v>
+        <v>Carcaça do Módulo E+Q / Nó de coluna (impressão 3D, medida padrão compacta)</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="40" t="n">
         <f aca="false">INDEX(Preços!$D:$D,MATCH(B15,Preços!$A:$A,0))</f>
-        <v>28.17</v>
+        <v>15</v>
       </c>
       <c r="F15" s="30" t="n">
         <f aca="false">D15*E15</f>
-        <v>28.17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -11418,12 +12082,12 @@
       <c r="E16" s="16"/>
       <c r="F16" s="41" t="n">
         <f aca="false">SUM(F10:F15)</f>
-        <v>117.59</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>246</v>
@@ -11446,7 +12110,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>242</v>
@@ -11469,7 +12133,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>249</v>
@@ -11492,7 +12156,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>252</v>
@@ -11515,7 +12179,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>264</v>
@@ -11538,7 +12202,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>267</v>
@@ -11561,7 +12225,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>270</v>
@@ -11584,30 +12248,30 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C25" s="39" t="str">
         <f aca="false">INDEX(Preços!$B:$B,MATCH(B25,Preços!$A:$A,0))</f>
-        <v>Carcaça do Módulo E+Q / Nó de coluna (caixa Patola PB-112, 53 × 85 × 124 mm)</v>
+        <v>Carcaça do Módulo E+Q / Nó de coluna (impressão 3D, medida padrão compacta)</v>
       </c>
       <c r="D25" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="40" t="n">
         <f aca="false">INDEX(Preços!$D:$D,MATCH(B25,Preços!$A:$A,0))</f>
-        <v>28.17</v>
+        <v>15</v>
       </c>
       <c r="F25" s="30" t="n">
         <f aca="false">D25*E25</f>
-        <v>28.17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>285</v>
@@ -11630,7 +12294,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -11638,12 +12302,12 @@
       <c r="E27" s="16"/>
       <c r="F27" s="41" t="n">
         <f aca="false">SUM(F18:F26)</f>
-        <v>151.48</v>
+        <v>138.31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>255</v>
@@ -11666,7 +12330,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>252</v>
@@ -11689,7 +12353,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>258</v>
@@ -11712,7 +12376,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>264</v>
@@ -11735,7 +12399,7 @@
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>288</v>
@@ -11758,7 +12422,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>291</v>
@@ -11781,7 +12445,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>270</v>
@@ -11804,7 +12468,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>353</v>
@@ -11827,7 +12491,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>356</v>
@@ -11850,7 +12514,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>359</v>
@@ -11873,7 +12537,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -11886,7 +12550,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>255</v>
@@ -11909,7 +12573,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>252</v>
@@ -11932,7 +12596,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>261</v>
@@ -11955,7 +12619,7 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>288</v>
@@ -11978,7 +12642,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>291</v>
@@ -12001,7 +12665,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>270</v>
@@ -12024,7 +12688,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>353</v>
@@ -12047,7 +12711,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>356</v>
@@ -12070,7 +12734,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>359</v>
@@ -12093,7 +12757,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -12106,7 +12770,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>315</v>
@@ -12129,7 +12793,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>318</v>
@@ -12152,7 +12816,7 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B54" s="13" t="s">
         <v>321</v>
@@ -12175,7 +12839,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>325</v>
@@ -12198,7 +12862,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
@@ -12211,7 +12875,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>309</v>
@@ -12234,7 +12898,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>312</v>
@@ -12257,7 +12921,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -12270,12 +12934,12 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -12289,7 +12953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -12311,35 +12975,35 @@
         <v>237</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>662</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>665</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>668</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>669</v>
       </c>
       <c r="C3" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
@@ -12351,23 +13015,23 @@
       </c>
       <c r="E3" s="40" t="n">
         <f aca="false">Composição!$F$8</f>
-        <v>55.2250459016394</v>
+        <v>47.8850459016393</v>
       </c>
       <c r="F3" s="30" t="n">
         <f aca="false">C3*E3</f>
-        <v>3920.97825901639</v>
+        <v>3399.83825901639</v>
       </c>
       <c r="G3" s="30" t="n">
         <f aca="false">D3*E3</f>
-        <v>77756.8646295082</v>
+        <v>67422.1446295082</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>670</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>671</v>
       </c>
       <c r="C4" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$K$44*(1+Premissas!$B$26),0)</f>
@@ -12379,23 +13043,23 @@
       </c>
       <c r="E4" s="40" t="n">
         <f aca="false">Composição!$F$16</f>
-        <v>117.59</v>
+        <v>104.42</v>
       </c>
       <c r="F4" s="30" t="n">
         <f aca="false">C4*E4</f>
-        <v>2586.98</v>
+        <v>2297.24</v>
       </c>
       <c r="G4" s="30" t="n">
         <f aca="false">D4*E4</f>
-        <v>51739.6</v>
+        <v>45944.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>672</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>673</v>
       </c>
       <c r="C5" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
@@ -12407,23 +13071,23 @@
       </c>
       <c r="E5" s="40" t="n">
         <f aca="false">Composição!$F$27</f>
-        <v>151.48</v>
+        <v>138.31</v>
       </c>
       <c r="F5" s="30" t="n">
         <f aca="false">C5*E5</f>
-        <v>2120.72</v>
+        <v>1936.34</v>
       </c>
       <c r="G5" s="30" t="n">
         <f aca="false">D5*E5</f>
-        <v>41959.96</v>
+        <v>38311.87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>674</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>675</v>
       </c>
       <c r="C6" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
@@ -12448,10 +13112,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>676</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>677</v>
       </c>
       <c r="C7" s="42" t="n">
         <f aca="false">Estações!$N$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
@@ -12476,10 +13140,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>678</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>679</v>
       </c>
       <c r="C8" s="42" t="n">
         <f aca="false">Estações!$N$44*2+Estações!$O$44*4</f>
@@ -12504,10 +13168,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>680</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>681</v>
       </c>
       <c r="C9" s="42" t="n">
         <f aca="false">Estações!$K$44*(Premissas!$B$31*Premissas!$B$32+Premissas!$B$33)+Estações!$O$44*2*Premissas!$B$34+Estações!$O$44*Premissas!$B$35</f>
@@ -12532,10 +13196,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>682</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>683</v>
       </c>
       <c r="C10" s="42" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -12560,10 +13224,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>684</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>685</v>
       </c>
       <c r="C11" s="42" t="n">
         <f aca="false">Estações!$O$44</f>
@@ -12588,10 +13252,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>687</v>
       </c>
       <c r="C12" s="42" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$36</f>
@@ -12616,10 +13280,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>688</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>689</v>
       </c>
       <c r="C13" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44/Premissas!$B$37,0)</f>
@@ -12644,10 +13308,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>690</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>691</v>
       </c>
       <c r="C14" s="42" t="n">
         <f aca="false">C13</f>
@@ -12672,10 +13336,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C15" s="42" t="n">
         <f aca="false">C13</f>
@@ -12700,10 +13364,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>693</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>694</v>
       </c>
       <c r="C16" s="42" t="n">
         <f aca="false">C13*Premissas!$B$38</f>
@@ -12728,10 +13392,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>695</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>696</v>
       </c>
       <c r="C17" s="42" t="n">
         <f aca="false">ROUNDUP(Estações!$O$44*Premissas!$B$39,0)</f>
@@ -12756,10 +13420,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>697</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>698</v>
       </c>
       <c r="C18" s="42" t="n">
         <f aca="false">1</f>
@@ -12784,10 +13448,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C19" s="42" t="n">
         <f aca="false">1</f>
@@ -12812,10 +13476,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>700</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>701</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -12825,16 +13489,16 @@
       </c>
       <c r="F20" s="30" t="n">
         <f aca="false">E20*SUM(F3:F19)</f>
-        <v>737.083925963115</v>
+        <v>687.320925963115</v>
       </c>
       <c r="G20" s="30" t="n">
         <f aca="false">E20*SUM(G3:G19)</f>
-        <v>11609.3632371311</v>
+        <v>10620.4827371311</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -12842,24 +13506,24 @@
       <c r="E21" s="16"/>
       <c r="F21" s="41" t="n">
         <f aca="false">SUM(F3:F20)</f>
-        <v>15478.7624452254</v>
+        <v>14433.7394452254</v>
       </c>
       <c r="G21" s="41" t="n">
         <f aca="false">SUM(G3:G20)</f>
-        <v>243796.627979754</v>
+        <v>223030.137479754</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>704</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>705</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">C3*Premissas!$B$12</f>
@@ -12884,10 +13548,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>706</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>707</v>
       </c>
       <c r="C25" s="21" t="n">
         <f aca="false">C4*Premissas!$B$13</f>
@@ -12912,10 +13576,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C26" s="21" t="n">
         <f aca="false">C5*Premissas!$B$14</f>
@@ -12940,10 +13604,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>709</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>710</v>
       </c>
       <c r="C27" s="21" t="n">
         <f aca="false">C6*Premissas!$B$15</f>
@@ -12968,10 +13632,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>711</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>712</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$K$44*Premissas!$B$18+Estações!$M$44*Premissas!$B$19+C9*Premissas!$B$20)*Premissas!$B$22</f>
@@ -12996,10 +13660,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>713</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>714</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$21*Premissas!$B$22</f>
@@ -13024,10 +13688,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>715</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>716</v>
       </c>
       <c r="C30" s="21" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$23*Premissas!$B$24</f>
@@ -13052,10 +13716,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>717</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>718</v>
       </c>
       <c r="C31" s="21" t="n">
         <f aca="false">Premissas!$B$25</f>
@@ -13080,7 +13744,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="44" t="n">
@@ -13103,7 +13767,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -13111,24 +13775,24 @@
       <c r="E34" s="16"/>
       <c r="F34" s="41" t="n">
         <f aca="false">F21+F32</f>
-        <v>20179.6189016671</v>
+        <v>19134.5959016671</v>
       </c>
       <c r="G34" s="41" t="n">
         <f aca="false">G21+G32</f>
-        <v>326069.232212883</v>
+        <v>305302.741712883</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>722</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>723</v>
       </c>
       <c r="C37" s="42" t="n">
         <f aca="false">-(C4+C5+C6)</f>
@@ -13153,10 +13817,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>724</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>725</v>
       </c>
       <c r="C38" s="42" t="n">
         <f aca="false">C6</f>
@@ -13181,10 +13845,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C39" s="42" t="n">
         <f aca="false">Estações!$O$44*Premissas!$B$42</f>
@@ -13209,7 +13873,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -13217,607 +13881,11 @@
       <c r="E40" s="16"/>
       <c r="F40" s="41" t="n">
         <f aca="false">F21+SUM(F37:F39)</f>
-        <v>16813.0304452254</v>
+        <v>15768.0074452254</v>
       </c>
       <c r="G40" s="41" t="n">
         <f aca="false">G21+SUM(G37:G39)</f>
-        <v>264261.887979754</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>662</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>663</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>664</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>644</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="C3" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
-        <v>71</v>
-      </c>
-      <c r="D3" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$F$43*(1+Premissas!$B$26),0)</f>
-        <v>1408</v>
-      </c>
-      <c r="E3" s="40" t="n">
-        <f aca="false">Preços!$D$32+Preços!$D$14</f>
-        <v>98.47441</v>
-      </c>
-      <c r="F3" s="30" t="n">
-        <f aca="false">C3*E3</f>
-        <v>6991.68311</v>
-      </c>
-      <c r="G3" s="30" t="n">
-        <f aca="false">D3*E3</f>
-        <v>138651.96928</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="C4" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
-        <v>14</v>
-      </c>
-      <c r="D4" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
-        <v>277</v>
-      </c>
-      <c r="E4" s="40" t="n">
-        <f aca="false">Preços!$D$33+Preços!$D$15+Preços!$D$10</f>
-        <v>259.47078</v>
-      </c>
-      <c r="F4" s="30" t="n">
-        <f aca="false">C4*E4</f>
-        <v>3632.59092</v>
-      </c>
-      <c r="G4" s="30" t="n">
-        <f aca="false">D4*E4</f>
-        <v>71873.40606</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="C5" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$O$44*(1+Premissas!$B$26),0)</f>
-        <v>3</v>
-      </c>
-      <c r="D5" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$O$43*(1+Premissas!$B$26),0)</f>
-        <v>44</v>
-      </c>
-      <c r="E5" s="40" t="n">
-        <f aca="false">Preços!$D$34+Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$37*3+Preços!$D$38*1+Preços!$D$39*1</f>
-        <v>851.37555</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <f aca="false">C5*E5</f>
-        <v>2554.12665</v>
-      </c>
-      <c r="G5" s="30" t="n">
-        <f aca="false">D5*E5</f>
-        <v>37460.5242</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="C6" s="42" t="n">
-        <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
-        <v>124</v>
-      </c>
-      <c r="D6" s="42" t="n">
-        <f aca="false">Estações!$F$43*Premissas!$B$43+Estações!$M$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
-        <v>2513</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <f aca="false">Preços!$D$13</f>
-        <v>2.62262295081967</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <f aca="false">C6*E6</f>
-        <v>325.205245901639</v>
-      </c>
-      <c r="G6" s="30" t="n">
-        <f aca="false">D6*E6</f>
-        <v>6590.65147540984</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="C7" s="42" t="n">
-        <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
-        <v>160</v>
-      </c>
-      <c r="D7" s="42" t="n">
-        <f aca="false">(Estações!$F$43+Estações!$M$43)*2+Estações!$O$43*4</f>
-        <v>3222</v>
-      </c>
-      <c r="E7" s="40" t="n">
-        <f aca="false">Preços!$D$12</f>
-        <v>0.7099</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <f aca="false">C7*E7</f>
-        <v>113.584</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <f aca="false">D7*E7</f>
-        <v>2287.2978</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!F9:F19)</f>
-        <v>3725.95413114754</v>
-      </c>
-      <c r="G8" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!G9:G19)</f>
-        <v>23667.5855737705</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="C9" s="42" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <f aca="false">1</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="40" t="n">
-        <f aca="false">Preços!$D$35</f>
-        <v>15000</v>
-      </c>
-      <c r="F9" s="30" t="n">
-        <f aca="false">C9*E9</f>
-        <v>15000</v>
-      </c>
-      <c r="G9" s="30" t="n">
-        <f aca="false">D9*E9</f>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <f aca="false">(C3+C4+C5)*Premissas!$B$44</f>
-        <v>8.8</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <f aca="false">(D3+D4+D5)*Premissas!$B$44</f>
-        <v>172.9</v>
-      </c>
-      <c r="E10" s="40" t="n">
-        <f aca="false">Premissas!$B$9</f>
-        <v>34.9305521472393</v>
-      </c>
-      <c r="F10" s="30" t="n">
-        <f aca="false">C10*E10</f>
-        <v>307.388858895706</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <f aca="false">D10*E10</f>
-        <v>6039.49246625767</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>51.18</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>1029.375</v>
-      </c>
-      <c r="E11" s="40" t="n">
-        <f aca="false">Premissas!$B$9</f>
-        <v>34.9305521472393</v>
-      </c>
-      <c r="F11" s="30" t="n">
-        <f aca="false">C11*E11</f>
-        <v>1787.74565889571</v>
-      </c>
-      <c r="G11" s="30" t="n">
-        <f aca="false">D11*E11</f>
-        <v>35956.6371165644</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!F30:F31)</f>
-        <v>756.149202453988</v>
-      </c>
-      <c r="G12" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!G30:G31)</f>
-        <v>4504.09619631902</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>745</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="41" t="n">
-        <f aca="false">SUM(F3:F12)</f>
-        <v>35194.4277772946</v>
-      </c>
-      <c r="G13" s="41" t="n">
-        <f aca="false">SUM(G3:G12)</f>
-        <v>342031.660168321</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>748</v>
-      </c>
-      <c r="C16" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$F$44*(1+Premissas!$B$26),0)</f>
-        <v>71</v>
-      </c>
-      <c r="D16" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$F$43*(1+Premissas!$B$26),0)</f>
-        <v>1408</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <f aca="false">Preços!$D$29</f>
-        <v>287.1147</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <f aca="false">C16*E16</f>
-        <v>20385.1437</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <f aca="false">D16*E16</f>
-        <v>404257.4976</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="C17" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$M$44*(1+Premissas!$B$26),0)</f>
-        <v>14</v>
-      </c>
-      <c r="D17" s="42" t="n">
-        <f aca="false">ROUNDUP(Estações!$M$43*(1+Premissas!$B$26),0)</f>
-        <v>277</v>
-      </c>
-      <c r="E17" s="40" t="n">
-        <f aca="false">Preços!$D$30</f>
-        <v>622.08185</v>
-      </c>
-      <c r="F17" s="30" t="n">
-        <f aca="false">C17*E17</f>
-        <v>8709.1459</v>
-      </c>
-      <c r="G17" s="30" t="n">
-        <f aca="false">D17*E17</f>
-        <v>172316.67245</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C18" s="42" t="n">
-        <f aca="false">Estações!$O$44</f>
-        <v>2</v>
-      </c>
-      <c r="D18" s="42" t="n">
-        <f aca="false">Estações!$O$43</f>
-        <v>40</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <f aca="false">Preços!$D$31</f>
-        <v>2105.5078</v>
-      </c>
-      <c r="F18" s="30" t="n">
-        <f aca="false">C18*E18</f>
-        <v>4211.0156</v>
-      </c>
-      <c r="G18" s="30" t="n">
-        <f aca="false">D18*E18</f>
-        <v>84220.312</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C19" s="42" t="n">
-        <f aca="false">Estações!$O$44</f>
-        <v>2</v>
-      </c>
-      <c r="D19" s="42" t="n">
-        <f aca="false">Estações!$O$43</f>
-        <v>40</v>
-      </c>
-      <c r="E19" s="40" t="n">
-        <f aca="false">Preços!$D$7+Preços!$D$17+Preços!$D$18+Preços!$D$37*3+Preços!$D$38*1+Preços!$D$39*1</f>
-        <v>516.4084</v>
-      </c>
-      <c r="F19" s="30" t="n">
-        <f aca="false">C19*E19</f>
-        <v>1032.8168</v>
-      </c>
-      <c r="G19" s="30" t="n">
-        <f aca="false">D19*E19</f>
-        <v>20656.336</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>733</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="C20" s="42" t="n">
-        <f aca="false">Estações!$F$44*Premissas!$B$43+Estações!$M$44*Premissas!$B$29+Estações!$O$44*2*Premissas!$B$30</f>
-        <v>124</v>
-      </c>
-      <c r="D20" s="42" t="n">
-        <f aca="false">Estações!$F$43*Premissas!$B$43+Estações!$M$43*Premissas!$B$29+Estações!$O$43*2*Premissas!$B$30</f>
-        <v>2513</v>
-      </c>
-      <c r="E20" s="40" t="n">
-        <f aca="false">Preços!$D$13</f>
-        <v>2.62262295081967</v>
-      </c>
-      <c r="F20" s="30" t="n">
-        <f aca="false">C20*E20</f>
-        <v>325.205245901639</v>
-      </c>
-      <c r="G20" s="30" t="n">
-        <f aca="false">D20*E20</f>
-        <v>6590.65147540984</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="C21" s="42" t="n">
-        <f aca="false">(Estações!$F$44+Estações!$M$44)*2+Estações!$O$44*4</f>
-        <v>160</v>
-      </c>
-      <c r="D21" s="42" t="n">
-        <f aca="false">(Estações!$F$43+Estações!$M$43)*2+Estações!$O$43*4</f>
-        <v>3222</v>
-      </c>
-      <c r="E21" s="40" t="n">
-        <f aca="false">Preços!$D$12</f>
-        <v>0.7099</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <f aca="false">C21*E21</f>
-        <v>113.584</v>
-      </c>
-      <c r="G21" s="30" t="n">
-        <f aca="false">D21*E21</f>
-        <v>2287.2978</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!F9:F19)</f>
-        <v>3725.95413114754</v>
-      </c>
-      <c r="G22" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!G9:G19)</f>
-        <v>23667.5855737705</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <f aca="false">(Estações!$O$44*Premissas!$B$16+Estações!$F$44*Premissas!$B$17+Estações!$M$44*Premissas!$B$19+'A-Interno'!C9*Premissas!$B$20+Estações!$O$44*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>51.18</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <f aca="false">(Estações!$O$43*Premissas!$B$16+Estações!$F$43*Premissas!$B$17+Estações!$M$43*Premissas!$B$19+'A-Interno'!D9*Premissas!$B$20+Estações!$O$43*Premissas!$B$21)*Premissas!$B$22</f>
-        <v>1029.375</v>
-      </c>
-      <c r="E23" s="40" t="n">
-        <f aca="false">Premissas!$B$9</f>
-        <v>34.9305521472393</v>
-      </c>
-      <c r="F23" s="30" t="n">
-        <f aca="false">C23*E23</f>
-        <v>1787.74565889571</v>
-      </c>
-      <c r="G23" s="30" t="n">
-        <f aca="false">D23*E23</f>
-        <v>35956.6371165644</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!F30:F31)</f>
-        <v>756.149202453988</v>
-      </c>
-      <c r="G24" s="40" t="n">
-        <f aca="false">SUM('A-Interno'!G30:G31)</f>
-        <v>4504.09619631902</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
-        <v>752</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="41" t="n">
-        <f aca="false">SUM(F16:F24)</f>
-        <v>41046.7602383989</v>
-      </c>
-      <c r="G25" s="41" t="n">
-        <f aca="false">SUM(G16:G24)</f>
-        <v>754457.086212064</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>753</v>
+        <v>243495.397479754</v>
       </c>
     </row>
   </sheetData>
